--- a/AMS/002-Park-Rose/Park_Rose_Provisional_2025-26_V2.xlsx
+++ b/AMS/002-Park-Rose/Park_Rose_Provisional_2025-26_V2.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\BHARAT\2025-2026\AMS\002-Park-Rose\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BHARAT\2025-2026\BCB\AMS\002-Park-Rose\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E596D5EC-A375-4AD3-9F78-784BA6EFA757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="783" activeTab="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="783" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BS" sheetId="1" r:id="rId1"/>
@@ -23,14 +24,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Interest on FD'!$A$2:$F$36</definedName>
-    <definedName name="_xlcn.WorksheetConnection_InterestonFDA2F371" hidden="1">'Interest on FD'!$A$2:$F$36</definedName>
+    <definedName name="_xlcn.WorksheetConnection_InterestonFDA2F37" hidden="1">'Interest on FD'!$A$2:$F$36</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">BS!$A$1:$H$58</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">IE!$A$1:$H$62</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Sch I - FD'!$A$1:$L$42</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'Sch I - FD (2)'!$A$1:$L$28</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Sch II to IV - Vendors &amp; Mem.'!$A$1:$D$45</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId9"/>
   </pivotCaches>
@@ -52,6 +53,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -62,8 +65,8 @@
 </file>
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
-<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <connection id="1" keepAlive="1" name="ThisWorkbookDataModel" description="Data Model" type="5" refreshedVersion="7" minRefreshableVersion="5" background="1">
+<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
+  <connection id="1" xr16:uid="{00000000-0015-0000-FFFF-FFFF00000000}" keepAlive="1" name="ThisWorkbookDataModel" description="Data Model" type="5" refreshedVersion="7" minRefreshableVersion="5" background="1">
     <dbPr connection="Data Model Connection" command="Model" commandType="1"/>
     <olapPr sendLocale="1" rowDrillCount="1000"/>
     <extLst>
@@ -72,11 +75,11 @@
       </ext>
     </extLst>
   </connection>
-  <connection id="2" name="WorksheetConnection_Interest on FD!$A$2:$F$37" type="102" refreshedVersion="7" minRefreshableVersion="5">
+  <connection id="2" xr16:uid="{00000000-0015-0000-FFFF-FFFF01000000}" name="WorksheetConnection_Interest on FD!$A$2:$F$37" type="102" refreshedVersion="7" minRefreshableVersion="5">
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="Range" autoDelete="1">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_InterestonFDA2F371"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_InterestonFDA2F37"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -85,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="377">
   <si>
     <t>LIABILITIES</t>
   </si>
@@ -378,9 +381,6 @@
     <t>Add: Member's contribution for the year</t>
   </si>
   <si>
-    <t>Add: 25% Surplus carried from I&amp;E</t>
-  </si>
-  <si>
     <t>(iv) Lift Repair Fund</t>
   </si>
   <si>
@@ -1182,9 +1182,6 @@
     <t>Advance Locality Maintenance FY 2024-25</t>
   </si>
   <si>
-    <t>R&amp;M - Parking &amp; Stack Parking</t>
-  </si>
-  <si>
     <t>Ex-Gratia to Security &amp; HK Staff</t>
   </si>
   <si>
@@ -1209,9 +1206,6 @@
     <t>Govt. Certified Panel Auditor</t>
   </si>
   <si>
-    <t>[Panel No.: Mumbai-4/B2/1011404]</t>
-  </si>
-  <si>
     <t>Total :-</t>
   </si>
   <si>
@@ -1219,12 +1213,18 @@
   </si>
   <si>
     <t>Share Cap</t>
+  </si>
+  <si>
+    <t>`</t>
+  </si>
+  <si>
+    <t>[Panel No.: Mumbai-4/C1/1011404]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
@@ -1918,7 +1918,7 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="202">
+  <cellXfs count="195">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2070,23 +2070,17 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="43" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2162,7 +2156,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2174,10 +2168,10 @@
     <xf numFmtId="1" fontId="20" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="21" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2195,28 +2189,28 @@
     <xf numFmtId="43" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2225,34 +2219,34 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2261,13 +2255,13 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2276,22 +2270,22 @@
     <xf numFmtId="43" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2300,16 +2294,9 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2326,10 +2313,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="40" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2338,6 +2325,15 @@
     <xf numFmtId="43" fontId="2" fillId="0" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="168" fontId="21" fillId="0" borderId="34" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2401,6 +2397,24 @@
     <xf numFmtId="43" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2413,24 +2427,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2438,21 +2434,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal_BSPL 2004 NS" xfId="3"/>
-    <cellStyle name="Normal_FY 2003-2004  2 2" xfId="2"/>
+    <cellStyle name="Normal_BSPL 2004 NS" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Normal_FY 2003-2004  2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2467,12 +2454,8 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" saveData="0" refreshedBy="AMS" refreshedDate="46166.152295601853" backgroundQuery="1" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="AMS" refreshedDate="46166.152295601853" backgroundQuery="1" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
   <cacheSource type="external" connectionId="1"/>
   <cacheFields count="3">
     <cacheField name="[Range].[Fund].[Fund]" caption="Fund" numFmtId="0" hierarchy="4" level="1">
@@ -2551,7 +2534,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0800-000000000000}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="H3:K12" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -2916,117 +2899,117 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q58"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" style="10" customWidth="1"/>
-    <col min="2" max="2" width="41.140625" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" style="10" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="18" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="10" customWidth="1"/>
-    <col min="6" max="6" width="37.140625" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="10" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="18" customWidth="1"/>
-    <col min="9" max="9" width="12.28515625" style="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.7109375" style="10"/>
+    <col min="1" max="1" width="14.6640625" style="10" customWidth="1"/>
+    <col min="2" max="2" width="41.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" style="10" customWidth="1"/>
+    <col min="4" max="4" width="14.6640625" style="18" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" style="10" customWidth="1"/>
+    <col min="6" max="6" width="37.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.6640625" style="10" customWidth="1"/>
+    <col min="8" max="8" width="14.6640625" style="18" customWidth="1"/>
+    <col min="9" max="9" width="12.33203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.6640625" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="169" t="s">
+    <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.3">
+      <c r="A1" s="165" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="170"/>
-      <c r="C1" s="170"/>
-      <c r="D1" s="170"/>
-      <c r="E1" s="170"/>
-      <c r="F1" s="170"/>
-      <c r="G1" s="170"/>
-      <c r="H1" s="171"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="172" t="s">
+      <c r="B1" s="166"/>
+      <c r="C1" s="166"/>
+      <c r="D1" s="166"/>
+      <c r="E1" s="166"/>
+      <c r="F1" s="166"/>
+      <c r="G1" s="166"/>
+      <c r="H1" s="167"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" s="168" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="173"/>
-      <c r="C2" s="173"/>
-      <c r="D2" s="173"/>
-      <c r="E2" s="173"/>
-      <c r="F2" s="173"/>
-      <c r="G2" s="173"/>
-      <c r="H2" s="174"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="172" t="s">
+      <c r="B2" s="169"/>
+      <c r="C2" s="169"/>
+      <c r="D2" s="169"/>
+      <c r="E2" s="169"/>
+      <c r="F2" s="169"/>
+      <c r="G2" s="169"/>
+      <c r="H2" s="170"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" s="168" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="173"/>
-      <c r="C3" s="173"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="173"/>
-      <c r="F3" s="173"/>
-      <c r="G3" s="173"/>
-      <c r="H3" s="174"/>
-    </row>
-    <row r="4" spans="1:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="175" t="s">
-        <v>260</v>
-      </c>
-      <c r="B4" s="176"/>
-      <c r="C4" s="176"/>
-      <c r="D4" s="176"/>
-      <c r="E4" s="176"/>
-      <c r="F4" s="176"/>
-      <c r="G4" s="176"/>
-      <c r="H4" s="177"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="99"/>
-      <c r="B5" s="100"/>
-      <c r="C5" s="100"/>
-      <c r="D5" s="100"/>
-      <c r="E5" s="100"/>
-      <c r="F5" s="100"/>
-      <c r="G5" s="100"/>
-      <c r="H5" s="101" t="s">
+      <c r="B3" s="169"/>
+      <c r="C3" s="169"/>
+      <c r="D3" s="169"/>
+      <c r="E3" s="169"/>
+      <c r="F3" s="169"/>
+      <c r="G3" s="169"/>
+      <c r="H3" s="170"/>
+    </row>
+    <row r="4" spans="1:13" ht="18" x14ac:dyDescent="0.3">
+      <c r="A4" s="171" t="s">
+        <v>259</v>
+      </c>
+      <c r="B4" s="172"/>
+      <c r="C4" s="172"/>
+      <c r="D4" s="172"/>
+      <c r="E4" s="172"/>
+      <c r="F4" s="172"/>
+      <c r="G4" s="172"/>
+      <c r="H4" s="173"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" s="95"/>
+      <c r="B5" s="96"/>
+      <c r="C5" s="96"/>
+      <c r="D5" s="96"/>
+      <c r="E5" s="96"/>
+      <c r="F5" s="96"/>
+      <c r="G5" s="96"/>
+      <c r="H5" s="97" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:13" s="11" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" s="11" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="57" t="s">
-        <v>150</v>
-      </c>
-      <c r="B6" s="178" t="s">
+        <v>149</v>
+      </c>
+      <c r="B6" s="174" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="179"/>
-      <c r="D6" s="83" t="s">
-        <v>197</v>
-      </c>
-      <c r="E6" s="81" t="str">
+      <c r="C6" s="175"/>
+      <c r="D6" s="79" t="s">
+        <v>196</v>
+      </c>
+      <c r="E6" s="77" t="str">
         <f>A6</f>
         <v>March 31, 2025</v>
       </c>
-      <c r="F6" s="178" t="s">
+      <c r="F6" s="174" t="s">
         <v>1</v>
       </c>
-      <c r="G6" s="179"/>
+      <c r="G6" s="175"/>
       <c r="H6" s="56" t="str">
         <f>D6</f>
         <v>March 31, 2026</v>
       </c>
       <c r="I6" s="58"/>
     </row>
-    <row r="7" spans="1:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A7" s="12"/>
       <c r="B7" s="22" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="7"/>
-      <c r="D7" s="84"/>
+      <c r="D7" s="80"/>
       <c r="E7" s="7"/>
       <c r="F7" s="22" t="s">
         <v>43</v>
@@ -3034,7 +3017,7 @@
       <c r="G7" s="7"/>
       <c r="H7" s="13"/>
     </row>
-    <row r="8" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="14">
         <v>100000</v>
       </c>
@@ -3042,25 +3025,25 @@
         <v>48</v>
       </c>
       <c r="C8" s="7"/>
-      <c r="D8" s="85">
+      <c r="D8" s="81">
         <v>100000</v>
       </c>
       <c r="E8" s="7">
         <v>72</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G8" s="7">
         <v>1143</v>
       </c>
       <c r="H8" s="13"/>
     </row>
-    <row r="9" spans="1:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12"/>
       <c r="B9" s="15"/>
       <c r="C9" s="7"/>
-      <c r="D9" s="84"/>
+      <c r="D9" s="80"/>
       <c r="E9" s="7">
         <v>31330.73</v>
       </c>
@@ -3073,13 +3056,13 @@
       </c>
       <c r="H9" s="13"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
       <c r="B10" s="22" t="s">
         <v>42</v>
       </c>
       <c r="C10" s="7"/>
-      <c r="D10" s="84"/>
+      <c r="D10" s="80"/>
       <c r="E10" s="7">
         <v>150063.76999999999</v>
       </c>
@@ -3095,15 +3078,15 @@
         <v>102585.74</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="12">
         <v>17000</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C11" s="7"/>
-      <c r="D11" s="84">
+      <c r="D11" s="80">
         <v>17000</v>
       </c>
       <c r="E11" s="7"/>
@@ -3111,13 +3094,13 @@
       <c r="G11" s="7"/>
       <c r="H11" s="13"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
       <c r="B12" s="22" t="s">
         <v>45</v>
       </c>
       <c r="C12" s="7"/>
-      <c r="D12" s="84"/>
+      <c r="D12" s="80"/>
       <c r="E12" s="7">
         <v>100</v>
       </c>
@@ -3130,19 +3113,19 @@
       </c>
       <c r="M12" s="17"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
       <c r="B13" s="22" t="s">
         <v>47</v>
       </c>
       <c r="C13" s="7"/>
-      <c r="D13" s="84"/>
+      <c r="D13" s="80"/>
       <c r="E13" s="7"/>
       <c r="F13" s="15"/>
       <c r="G13" s="7"/>
       <c r="H13" s="13"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="12">
         <v>149173</v>
       </c>
@@ -3152,12 +3135,12 @@
       <c r="C14" s="7">
         <v>190162</v>
       </c>
-      <c r="D14" s="84"/>
+      <c r="D14" s="80"/>
       <c r="E14" s="7">
         <v>1368664</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G14" s="7">
         <f>'Sch I - FD'!F41</f>
@@ -3165,7 +3148,7 @@
       </c>
       <c r="H14" s="13"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="12">
         <v>3700</v>
       </c>
@@ -3176,12 +3159,12 @@
         <f>25000+500+200</f>
         <v>25700</v>
       </c>
-      <c r="D15" s="84"/>
+      <c r="D15" s="80"/>
       <c r="E15" s="7">
         <v>44076</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G15" s="6">
         <f>'Sch I - FD'!I41</f>
@@ -3192,7 +3175,7 @@
         <v>2428003</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="12">
         <v>7171</v>
       </c>
@@ -3203,24 +3186,24 @@
         <f>IE!G29</f>
         <v>9473</v>
       </c>
-      <c r="D16" s="84"/>
+      <c r="D16" s="80"/>
       <c r="E16" s="7"/>
       <c r="F16" s="15"/>
       <c r="G16" s="7"/>
       <c r="H16" s="13"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="12">
         <v>30118</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>97</v>
+        <v>375</v>
       </c>
       <c r="C17" s="6">
         <f>IE!D50</f>
         <v>42015</v>
       </c>
-      <c r="D17" s="84">
+      <c r="D17" s="80">
         <f>SUM(C14:C17)</f>
         <v>267350</v>
       </c>
@@ -3228,26 +3211,26 @@
         <v>27.98</v>
       </c>
       <c r="F17" s="22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="12"/>
       <c r="B18" s="22" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C18" s="7"/>
-      <c r="D18" s="84"/>
+      <c r="D18" s="80"/>
       <c r="E18" s="7"/>
       <c r="F18" s="15"/>
       <c r="G18" s="7"/>
       <c r="H18" s="13"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="12">
         <v>116623</v>
       </c>
@@ -3258,7 +3241,7 @@
         <f>A19+A20+A21</f>
         <v>257478</v>
       </c>
-      <c r="D19" s="84"/>
+      <c r="D19" s="80"/>
       <c r="E19" s="7"/>
       <c r="F19" s="22" t="s">
         <v>20</v>
@@ -3266,7 +3249,7 @@
       <c r="G19" s="7"/>
       <c r="H19" s="13"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="12">
         <v>125856</v>
       </c>
@@ -3276,12 +3259,12 @@
       <c r="C20" s="7">
         <v>125856</v>
       </c>
-      <c r="D20" s="84"/>
+      <c r="D20" s="80"/>
       <c r="E20" s="7">
         <v>151098</v>
       </c>
       <c r="F20" s="22" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G20" s="7">
         <f>'Sch II to IV - Vendors &amp; Mem.'!D44</f>
@@ -3289,7 +3272,7 @@
       </c>
       <c r="H20" s="13"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="12">
         <v>14999</v>
       </c>
@@ -3300,7 +3283,7 @@
         <f>IE!G25</f>
         <v>25739</v>
       </c>
-      <c r="D21" s="84">
+      <c r="D21" s="80">
         <f>SUM(C19:C21)</f>
         <v>409073</v>
       </c>
@@ -3308,7 +3291,7 @@
         <v>7214</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G21" s="7">
         <f>7214</f>
@@ -3316,18 +3299,18 @@
       </c>
       <c r="H21" s="13"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="12"/>
       <c r="B22" s="22" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C22" s="7"/>
-      <c r="D22" s="84"/>
+      <c r="D22" s="80"/>
       <c r="E22" s="7">
         <v>0</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G22" s="7">
         <f>10183</f>
@@ -3335,7 +3318,7 @@
       </c>
       <c r="H22" s="13"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="12">
         <v>350534</v>
       </c>
@@ -3346,7 +3329,7 @@
         <f>A23+A24+A25</f>
         <v>761795</v>
       </c>
-      <c r="D23" s="84"/>
+      <c r="D23" s="80"/>
       <c r="E23" s="7">
         <v>13210</v>
       </c>
@@ -3361,7 +3344,7 @@
         <v>187550</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="12">
         <v>377316</v>
       </c>
@@ -3371,13 +3354,13 @@
       <c r="C24" s="7">
         <v>377316</v>
       </c>
-      <c r="D24" s="84"/>
+      <c r="D24" s="80"/>
       <c r="E24" s="7"/>
       <c r="F24" s="16"/>
       <c r="G24" s="7"/>
       <c r="H24" s="13"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="12">
         <v>33945</v>
       </c>
@@ -3388,36 +3371,36 @@
         <f>IE!G26</f>
         <v>74672</v>
       </c>
-      <c r="D25" s="84">
+      <c r="D25" s="80">
         <f>SUM(C23:C25)</f>
         <v>1213783</v>
       </c>
       <c r="E25" s="7"/>
       <c r="F25" s="22" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G25" s="7"/>
       <c r="H25" s="13"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="12"/>
       <c r="B26" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C26" s="7"/>
-      <c r="D26" s="84"/>
+      <c r="D26" s="80"/>
       <c r="E26" s="7">
         <v>5202</v>
       </c>
       <c r="F26" s="22" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G26" s="7">
         <v>5202</v>
       </c>
       <c r="H26" s="13"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="12">
         <v>117524</v>
       </c>
@@ -3428,19 +3411,19 @@
         <f>A27+A28+A29</f>
         <v>257538</v>
       </c>
-      <c r="D27" s="84"/>
+      <c r="D27" s="80"/>
       <c r="E27" s="7">
         <v>0</v>
       </c>
       <c r="F27" s="16" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G27" s="7">
         <v>0</v>
       </c>
       <c r="H27" s="13"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="12">
         <v>125856</v>
       </c>
@@ -3450,12 +3433,12 @@
       <c r="C28" s="7">
         <v>125856</v>
       </c>
-      <c r="D28" s="84"/>
+      <c r="D28" s="80"/>
       <c r="E28" s="7">
         <v>0</v>
       </c>
       <c r="F28" s="16" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G28" s="6">
         <f>ROUND((+G27+G26)*0.15,0)</f>
@@ -3466,7 +3449,7 @@
         <v>4422</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="12">
         <v>14158</v>
       </c>
@@ -3477,7 +3460,7 @@
         <f>IE!G28</f>
         <v>15754</v>
       </c>
-      <c r="D29" s="84">
+      <c r="D29" s="80">
         <f>SUM(C27:C29)</f>
         <v>399148</v>
       </c>
@@ -3486,25 +3469,25 @@
       <c r="G29" s="7"/>
       <c r="H29" s="13"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="12"/>
       <c r="B30" s="22" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C30" s="7"/>
-      <c r="D30" s="84"/>
+      <c r="D30" s="80"/>
       <c r="E30" s="7">
         <v>23640</v>
       </c>
       <c r="F30" s="22" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G30" s="7">
         <v>23640</v>
       </c>
       <c r="H30" s="13"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="12">
         <v>3747</v>
       </c>
@@ -3515,34 +3498,34 @@
         <f>A31+A33+A34</f>
         <v>8100</v>
       </c>
-      <c r="D31" s="84"/>
+      <c r="D31" s="80"/>
       <c r="E31" s="7">
         <v>0</v>
       </c>
       <c r="F31" s="16" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G31" s="7">
         <v>0</v>
       </c>
       <c r="H31" s="13"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="12">
         <v>0</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C32" s="7">
         <v>-8260</v>
       </c>
-      <c r="D32" s="84"/>
+      <c r="D32" s="80"/>
       <c r="E32" s="7">
         <v>0</v>
       </c>
       <c r="F32" s="16" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G32" s="6">
         <f>ROUND((+G31+G30)*0.1,0)</f>
@@ -3553,7 +3536,7 @@
         <v>21276</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="12">
         <v>4080</v>
       </c>
@@ -3563,13 +3546,13 @@
       <c r="C33" s="7">
         <v>4080</v>
       </c>
-      <c r="D33" s="84"/>
+      <c r="D33" s="80"/>
       <c r="E33" s="7"/>
       <c r="F33" s="16"/>
       <c r="G33" s="7"/>
       <c r="H33" s="13"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="12">
         <v>273</v>
       </c>
@@ -3580,7 +3563,7 @@
         <f>IE!G27</f>
         <v>573</v>
       </c>
-      <c r="D34" s="84">
+      <c r="D34" s="80">
         <f>SUM(C31:C34)</f>
         <v>4493</v>
       </c>
@@ -3588,41 +3571,41 @@
         <v>6480</v>
       </c>
       <c r="F34" s="22" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G34" s="7">
         <v>6480</v>
       </c>
       <c r="H34" s="13"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="12"/>
       <c r="B35" s="17"/>
       <c r="C35" s="7"/>
-      <c r="D35" s="84"/>
+      <c r="D35" s="80"/>
       <c r="E35" s="7">
         <v>0</v>
       </c>
       <c r="F35" s="16" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G35" s="7">
         <v>0</v>
       </c>
       <c r="H35" s="13"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="12"/>
       <c r="B36" s="22" t="s">
         <v>16</v>
       </c>
       <c r="C36" s="7"/>
-      <c r="D36" s="84"/>
+      <c r="D36" s="80"/>
       <c r="E36" s="7">
         <v>0</v>
       </c>
       <c r="F36" s="16" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G36" s="6">
         <f>ROUND((+G35+G34)*0.1,0)</f>
@@ -3633,80 +3616,80 @@
         <v>5832</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="12">
         <v>25352</v>
       </c>
       <c r="B37" s="22" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C37" s="7">
         <f>'Sch II to IV - Vendors &amp; Mem.'!D11</f>
         <v>33311</v>
       </c>
-      <c r="D37" s="84"/>
+      <c r="D37" s="80"/>
       <c r="E37" s="7"/>
       <c r="F37" s="34"/>
       <c r="G37" s="7"/>
       <c r="H37" s="13"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="12">
         <v>650</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C38" s="7">
         <v>0</v>
       </c>
-      <c r="D38" s="84"/>
+      <c r="D38" s="80"/>
       <c r="E38" s="7">
         <v>0</v>
       </c>
       <c r="F38" s="22" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="G38" s="7">
         <v>0</v>
       </c>
       <c r="H38" s="13"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="12">
         <v>10000</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C39" s="7">
         <v>10000</v>
       </c>
-      <c r="D39" s="84"/>
+      <c r="D39" s="80"/>
       <c r="E39" s="7">
         <v>0</v>
       </c>
       <c r="F39" s="16" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G39" s="7">
         <v>27500</v>
       </c>
       <c r="H39" s="13"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="12">
         <f>'Sch II to IV - Vendors &amp; Mem.'!B19</f>
-        <v>18641</v>
+        <v>12041</v>
       </c>
       <c r="B40" s="22" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C40" s="6">
         <f>'Sch II to IV - Vendors &amp; Mem.'!D19</f>
         <v>29450</v>
       </c>
-      <c r="D40" s="84">
+      <c r="D40" s="80">
         <f>SUM(C37:C40)</f>
         <v>72761</v>
       </c>
@@ -3714,7 +3697,7 @@
         <v>0</v>
       </c>
       <c r="F40" s="16" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G40" s="6">
         <f>ROUND((+G39+G38)*0.1,0)</f>
@@ -3725,37 +3708,37 @@
         <v>24750</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="12"/>
       <c r="B41" s="16"/>
       <c r="C41" s="7"/>
-      <c r="D41" s="84"/>
+      <c r="D41" s="80"/>
       <c r="E41" s="7"/>
       <c r="F41" s="16"/>
       <c r="G41" s="7"/>
       <c r="H41" s="13"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="12"/>
       <c r="B42" s="22" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C42" s="7"/>
-      <c r="D42" s="84"/>
+      <c r="D42" s="80"/>
       <c r="E42" s="7"/>
       <c r="F42" s="22"/>
       <c r="G42" s="7"/>
       <c r="H42" s="13"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="12">
         <v>33564</v>
       </c>
       <c r="B43" s="22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C43" s="7"/>
-      <c r="D43" s="84">
+      <c r="D43" s="80">
         <f>'Sch II to IV - Vendors &amp; Mem.'!D30</f>
         <v>43968</v>
       </c>
@@ -3764,29 +3747,29 @@
       <c r="G43" s="7"/>
       <c r="H43" s="13"/>
     </row>
-    <row r="44" spans="1:8" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="12"/>
       <c r="B44" s="16"/>
       <c r="C44" s="7"/>
-      <c r="D44" s="84"/>
+      <c r="D44" s="80"/>
       <c r="E44" s="7"/>
       <c r="F44" s="16"/>
       <c r="G44" s="7"/>
       <c r="H44" s="13"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="12"/>
       <c r="B45" s="22" t="s">
         <v>17</v>
       </c>
       <c r="C45" s="7"/>
-      <c r="D45" s="84"/>
+      <c r="D45" s="80"/>
       <c r="E45" s="7"/>
       <c r="F45" s="16"/>
       <c r="G45" s="7"/>
       <c r="H45" s="13"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="12">
         <v>130545.52000000002</v>
       </c>
@@ -3797,24 +3780,24 @@
         <f>SUM(A46:A47)</f>
         <v>220898.47999999998</v>
       </c>
-      <c r="D46" s="84"/>
+      <c r="D46" s="80"/>
       <c r="E46" s="7"/>
       <c r="F46" s="16"/>
       <c r="G46" s="7"/>
       <c r="H46" s="13"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="12">
         <v>90352.959999999963</v>
       </c>
       <c r="B47" s="23" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C47" s="6">
         <f>IE!D51</f>
         <v>126044.26000000001</v>
       </c>
-      <c r="D47" s="84">
+      <c r="D47" s="80">
         <f>SUM(C46:C47)</f>
         <v>346942.74</v>
       </c>
@@ -3823,46 +3806,46 @@
       <c r="G47" s="7"/>
       <c r="H47" s="13"/>
     </row>
-    <row r="48" spans="1:8" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="12"/>
       <c r="B48" s="23"/>
       <c r="C48" s="7"/>
-      <c r="D48" s="84"/>
+      <c r="D48" s="80"/>
       <c r="E48" s="7"/>
       <c r="F48" s="16"/>
       <c r="G48" s="7"/>
       <c r="H48" s="13"/>
     </row>
-    <row r="49" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="21">
         <f>SUM(A11:A48)</f>
-        <v>1801178.48</v>
-      </c>
-      <c r="B49" s="178" t="s">
+        <v>1794578.48</v>
+      </c>
+      <c r="B49" s="174" t="s">
         <v>15</v>
       </c>
-      <c r="C49" s="179"/>
-      <c r="D49" s="86">
+      <c r="C49" s="175"/>
+      <c r="D49" s="82">
         <f>SUM(D11:D47)</f>
         <v>2774518.74</v>
       </c>
-      <c r="E49" s="82">
+      <c r="E49" s="78">
         <f>SUM(E7:E48)</f>
         <v>1801178.48</v>
       </c>
-      <c r="F49" s="178" t="s">
+      <c r="F49" s="174" t="s">
         <v>15</v>
       </c>
-      <c r="G49" s="179"/>
+      <c r="G49" s="175"/>
       <c r="H49" s="21">
         <f>SUM(H7:H48)</f>
         <v>2774518.74</v>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="9.9499999999999993" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="112">
+    <row r="50" spans="1:17" ht="9.9" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="108">
         <f>A49-E49</f>
-        <v>0</v>
+        <v>-6600</v>
       </c>
       <c r="B50" s="54"/>
       <c r="C50" s="54"/>
@@ -3870,82 +3853,82 @@
       <c r="E50" s="20"/>
       <c r="F50" s="19"/>
       <c r="G50" s="19"/>
-      <c r="H50" s="90">
+      <c r="H50" s="86">
         <f>H49-D49</f>
         <v>0</v>
       </c>
       <c r="J50" s="17"/>
       <c r="L50" s="17"/>
     </row>
-    <row r="51" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A51" s="104" t="s">
-        <v>194</v>
-      </c>
-      <c r="B51" s="105"/>
-      <c r="C51" s="105"/>
+    <row r="51" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A51" s="100" t="s">
+        <v>193</v>
+      </c>
+      <c r="B51" s="101"/>
+      <c r="C51" s="101"/>
       <c r="D51" s="53"/>
-      <c r="E51" s="180" t="str">
+      <c r="E51" s="176" t="str">
         <f>"For "&amp;A1</f>
         <v>For PARK ROSE CO-OPERATIVE HOUSING SOCIETY LTD.</v>
       </c>
-      <c r="F51" s="180"/>
-      <c r="G51" s="180"/>
-      <c r="H51" s="181"/>
+      <c r="F51" s="176"/>
+      <c r="G51" s="176"/>
+      <c r="H51" s="177"/>
       <c r="J51" s="17"/>
       <c r="L51" s="17"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A52" s="106"/>
-      <c r="B52" s="105"/>
-      <c r="C52" s="105"/>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A52" s="102"/>
+      <c r="B52" s="101"/>
+      <c r="C52" s="101"/>
       <c r="D52" s="53"/>
       <c r="E52" s="17"/>
       <c r="F52" s="17"/>
       <c r="G52" s="17"/>
-      <c r="H52" s="90"/>
+      <c r="H52" s="86"/>
       <c r="J52" s="17"/>
       <c r="L52" s="17"/>
       <c r="P52" s="17"/>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A53" s="107"/>
-      <c r="B53" s="105"/>
-      <c r="C53" s="105"/>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A53" s="103"/>
+      <c r="B53" s="101"/>
+      <c r="C53" s="101"/>
       <c r="D53" s="53"/>
       <c r="E53" s="17"/>
       <c r="F53" s="17"/>
       <c r="G53" s="17"/>
-      <c r="H53" s="90"/>
+      <c r="H53" s="86"/>
       <c r="J53" s="17"/>
       <c r="N53" s="17"/>
       <c r="O53" s="17"/>
       <c r="P53" s="17"/>
       <c r="Q53" s="17"/>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A54" s="106"/>
-      <c r="B54" s="105"/>
-      <c r="C54" s="105"/>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A54" s="102"/>
+      <c r="B54" s="101"/>
+      <c r="C54" s="101"/>
       <c r="D54" s="53"/>
       <c r="E54" s="17"/>
       <c r="F54" s="17"/>
       <c r="G54" s="17"/>
-      <c r="H54" s="90"/>
+      <c r="H54" s="86"/>
       <c r="I54" s="17"/>
       <c r="O54" s="17"/>
       <c r="Q54" s="17"/>
     </row>
-    <row r="55" spans="1:17" s="17" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A55" s="108" t="s">
-        <v>372</v>
-      </c>
-      <c r="B55" s="109"/>
-      <c r="C55" s="110"/>
+    <row r="55" spans="1:17" s="17" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A55" s="104" t="s">
+        <v>370</v>
+      </c>
+      <c r="B55" s="105"/>
+      <c r="C55" s="106"/>
       <c r="D55" s="53"/>
-      <c r="E55" s="167"/>
-      <c r="F55" s="167"/>
-      <c r="G55" s="167"/>
-      <c r="H55" s="168"/>
+      <c r="E55" s="163"/>
+      <c r="F55" s="163"/>
+      <c r="G55" s="163"/>
+      <c r="H55" s="164"/>
       <c r="J55" s="10"/>
       <c r="K55" s="10"/>
       <c r="L55" s="10"/>
@@ -3955,43 +3938,43 @@
       <c r="P55" s="10"/>
       <c r="Q55" s="10"/>
     </row>
-    <row r="56" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A56" s="111" t="s">
-        <v>373</v>
-      </c>
-      <c r="B56" s="109"/>
-      <c r="C56" s="110"/>
+    <row r="56" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A56" s="107" t="s">
+        <v>371</v>
+      </c>
+      <c r="B56" s="105"/>
+      <c r="C56" s="106"/>
       <c r="D56" s="53"/>
-      <c r="E56" s="167" t="s">
-        <v>195</v>
-      </c>
-      <c r="F56" s="167"/>
-      <c r="G56" s="167"/>
-      <c r="H56" s="168"/>
-    </row>
-    <row r="57" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A57" s="111" t="s">
-        <v>374</v>
-      </c>
-      <c r="B57" s="109"/>
-      <c r="C57" s="110"/>
+      <c r="E56" s="163" t="s">
+        <v>194</v>
+      </c>
+      <c r="F56" s="163"/>
+      <c r="G56" s="163"/>
+      <c r="H56" s="164"/>
+    </row>
+    <row r="57" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A57" s="107" t="s">
+        <v>376</v>
+      </c>
+      <c r="B57" s="105"/>
+      <c r="C57" s="106"/>
       <c r="D57" s="53"/>
       <c r="E57" s="17"/>
       <c r="F57" s="17"/>
       <c r="G57" s="17"/>
-      <c r="H57" s="90"/>
-    </row>
-    <row r="58" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A58" s="165">
-        <v>46185</v>
-      </c>
-      <c r="B58" s="166"/>
-      <c r="C58" s="166"/>
-      <c r="D58" s="113"/>
-      <c r="E58" s="114"/>
-      <c r="F58" s="114"/>
-      <c r="G58" s="114"/>
-      <c r="H58" s="115"/>
+      <c r="H57" s="86"/>
+    </row>
+    <row r="58" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A58" s="161">
+        <v>46215</v>
+      </c>
+      <c r="B58" s="162"/>
+      <c r="C58" s="162"/>
+      <c r="D58" s="109"/>
+      <c r="E58" s="110"/>
+      <c r="F58" s="110"/>
+      <c r="G58" s="110"/>
+      <c r="H58" s="111"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -4015,185 +3998,184 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M62"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" style="10" customWidth="1"/>
-    <col min="2" max="2" width="39.5703125" style="10" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" style="42" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="10" customWidth="1"/>
-    <col min="6" max="6" width="29.7109375" style="10" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="10" customWidth="1"/>
-    <col min="9" max="9" width="9.5703125" style="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.28515625" style="71" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.28515625" style="71" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="8.7109375" style="71"/>
-    <col min="14" max="16384" width="8.7109375" style="10"/>
+    <col min="1" max="1" width="14.6640625" style="10" customWidth="1"/>
+    <col min="2" max="2" width="39.5546875" style="10" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" style="42" customWidth="1"/>
+    <col min="4" max="5" width="14.6640625" style="10" customWidth="1"/>
+    <col min="6" max="6" width="29.6640625" style="10" customWidth="1"/>
+    <col min="7" max="8" width="14.6640625" style="10" customWidth="1"/>
+    <col min="9" max="9" width="9.5546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.6640625" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="169" t="s">
+    <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.3">
+      <c r="A1" s="165" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="170"/>
-      <c r="C1" s="170"/>
-      <c r="D1" s="170"/>
-      <c r="E1" s="170"/>
-      <c r="F1" s="170"/>
-      <c r="G1" s="170"/>
-      <c r="H1" s="171"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="172" t="s">
+      <c r="B1" s="166"/>
+      <c r="C1" s="166"/>
+      <c r="D1" s="166"/>
+      <c r="E1" s="166"/>
+      <c r="F1" s="166"/>
+      <c r="G1" s="166"/>
+      <c r="H1" s="167"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" s="168" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="173"/>
-      <c r="C2" s="173"/>
-      <c r="D2" s="173"/>
-      <c r="E2" s="173"/>
-      <c r="F2" s="173"/>
-      <c r="G2" s="173"/>
-      <c r="H2" s="174"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="172" t="s">
+      <c r="B2" s="169"/>
+      <c r="C2" s="169"/>
+      <c r="D2" s="169"/>
+      <c r="E2" s="169"/>
+      <c r="F2" s="169"/>
+      <c r="G2" s="169"/>
+      <c r="H2" s="170"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" s="168" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="173"/>
-      <c r="C3" s="173"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="173"/>
-      <c r="F3" s="173"/>
-      <c r="G3" s="173"/>
-      <c r="H3" s="174"/>
-    </row>
-    <row r="4" spans="1:13" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="175" t="s">
-        <v>259</v>
-      </c>
-      <c r="B4" s="176"/>
-      <c r="C4" s="176"/>
-      <c r="D4" s="176"/>
-      <c r="E4" s="176"/>
-      <c r="F4" s="176"/>
-      <c r="G4" s="176"/>
-      <c r="H4" s="177"/>
-    </row>
-    <row r="5" spans="1:13" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="99"/>
-      <c r="B5" s="100"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="100"/>
-      <c r="E5" s="100"/>
-      <c r="F5" s="100"/>
-      <c r="G5" s="100"/>
-      <c r="H5" s="103" t="s">
+      <c r="B3" s="169"/>
+      <c r="C3" s="169"/>
+      <c r="D3" s="169"/>
+      <c r="E3" s="169"/>
+      <c r="F3" s="169"/>
+      <c r="G3" s="169"/>
+      <c r="H3" s="170"/>
+    </row>
+    <row r="4" spans="1:13" ht="18" x14ac:dyDescent="0.3">
+      <c r="A4" s="171" t="s">
+        <v>258</v>
+      </c>
+      <c r="B4" s="172"/>
+      <c r="C4" s="172"/>
+      <c r="D4" s="172"/>
+      <c r="E4" s="172"/>
+      <c r="F4" s="172"/>
+      <c r="G4" s="172"/>
+      <c r="H4" s="173"/>
+    </row>
+    <row r="5" spans="1:13" ht="14.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="95"/>
+      <c r="B5" s="96"/>
+      <c r="C5" s="98"/>
+      <c r="D5" s="96"/>
+      <c r="E5" s="96"/>
+      <c r="F5" s="96"/>
+      <c r="G5" s="96"/>
+      <c r="H5" s="99" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:13" s="37" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="96" t="str">
+    <row r="6" spans="1:13" s="37" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="92" t="str">
         <f>BS!A6</f>
         <v>March 31, 2025</v>
       </c>
-      <c r="B6" s="182" t="s">
+      <c r="B6" s="178" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="183"/>
-      <c r="D6" s="97" t="str">
+      <c r="C6" s="179"/>
+      <c r="D6" s="93" t="str">
         <f>BS!D6</f>
         <v>March 31, 2026</v>
       </c>
-      <c r="E6" s="98" t="str">
+      <c r="E6" s="94" t="str">
         <f>A6</f>
         <v>March 31, 2025</v>
       </c>
-      <c r="F6" s="182" t="s">
+      <c r="F6" s="178" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="183"/>
-      <c r="H6" s="96" t="str">
+      <c r="G6" s="179"/>
+      <c r="H6" s="92" t="str">
         <f>D6</f>
         <v>March 31, 2026</v>
       </c>
-      <c r="J6" s="71"/>
-      <c r="K6" s="71"/>
-      <c r="L6" s="71"/>
-      <c r="M6" s="71"/>
-    </row>
-    <row r="7" spans="1:13" s="11" customFormat="1" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="J6"/>
+      <c r="K6"/>
+      <c r="L6"/>
+      <c r="M6"/>
+    </row>
+    <row r="7" spans="1:13" s="11" customFormat="1" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A7" s="38"/>
-      <c r="B7" s="91" t="s">
+      <c r="B7" s="87" t="s">
         <v>61</v>
       </c>
       <c r="C7" s="35"/>
-      <c r="D7" s="92"/>
-      <c r="E7" s="87"/>
-      <c r="F7" s="91" t="s">
-        <v>185</v>
+      <c r="D7" s="88"/>
+      <c r="E7" s="83"/>
+      <c r="F7" s="87" t="s">
+        <v>184</v>
       </c>
       <c r="G7" s="19"/>
       <c r="H7" s="38"/>
-      <c r="J7" s="71"/>
-      <c r="K7" s="71"/>
-      <c r="L7" s="71"/>
-      <c r="M7" s="71"/>
-    </row>
-    <row r="8" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J7"/>
+      <c r="K7"/>
+      <c r="L7"/>
+      <c r="M7"/>
+    </row>
+    <row r="8" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="39">
         <v>27324</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C8" s="35">
         <v>30148</v>
       </c>
-      <c r="D8" s="92"/>
-      <c r="E8" s="88">
+      <c r="D8" s="88"/>
+      <c r="E8" s="84">
         <v>27216</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G8" s="35">
         <v>27216</v>
       </c>
       <c r="H8" s="38"/>
-      <c r="J8" s="71"/>
-      <c r="K8" s="71"/>
-      <c r="L8" s="71"/>
-      <c r="M8" s="71"/>
-    </row>
-    <row r="9" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J8"/>
+      <c r="K8"/>
+      <c r="L8"/>
+      <c r="M8"/>
+    </row>
+    <row r="9" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="39">
         <v>1032</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C9" s="35">
         <f>1032</f>
         <v>1032</v>
       </c>
-      <c r="D9" s="92"/>
-      <c r="E9" s="88">
+      <c r="D9" s="88"/>
+      <c r="E9" s="84">
         <v>1224</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G9" s="35">
         <v>1224</v>
       </c>
       <c r="H9" s="38"/>
-      <c r="J9" s="71"/>
-      <c r="K9" s="71"/>
-      <c r="L9" s="71"/>
-      <c r="M9" s="71"/>
-    </row>
-    <row r="10" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J9"/>
+      <c r="K9"/>
+      <c r="L9"/>
+      <c r="M9"/>
+    </row>
+    <row r="10" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="39">
         <v>190560</v>
       </c>
@@ -4204,8 +4186,8 @@
         <f>205730</f>
         <v>205730</v>
       </c>
-      <c r="D10" s="92"/>
-      <c r="E10" s="88">
+      <c r="D10" s="88"/>
+      <c r="E10" s="84">
         <v>179928</v>
       </c>
       <c r="F10" s="17" t="s">
@@ -4216,12 +4198,12 @@
         <v>179928</v>
       </c>
       <c r="H10" s="38"/>
-      <c r="J10" s="71"/>
-      <c r="K10" s="71"/>
-      <c r="L10" s="71"/>
-      <c r="M10" s="71"/>
-    </row>
-    <row r="11" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J10"/>
+      <c r="K10"/>
+      <c r="L10"/>
+      <c r="M10"/>
+    </row>
+    <row r="11" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="39">
         <v>67725</v>
       </c>
@@ -4232,8 +4214,8 @@
         <f>Workings!D10</f>
         <v>68650</v>
       </c>
-      <c r="D11" s="92"/>
-      <c r="E11" s="88">
+      <c r="D11" s="88"/>
+      <c r="E11" s="84">
         <v>75480</v>
       </c>
       <c r="F11" s="17" t="s">
@@ -4244,12 +4226,12 @@
         <v>75480</v>
       </c>
       <c r="H11" s="38"/>
-      <c r="J11" s="71"/>
-      <c r="K11" s="71"/>
-      <c r="L11" s="71"/>
-      <c r="M11" s="71"/>
-    </row>
-    <row r="12" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J11"/>
+      <c r="K11"/>
+      <c r="L11"/>
+      <c r="M11"/>
+    </row>
+    <row r="12" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="39">
         <v>18588</v>
       </c>
@@ -4260,11 +4242,11 @@
         <f>Workings!D47</f>
         <v>19218</v>
       </c>
-      <c r="D12" s="92">
+      <c r="D12" s="88">
         <f>SUM(C8:C12)</f>
         <v>324778</v>
       </c>
-      <c r="E12" s="88">
+      <c r="E12" s="84">
         <v>20040</v>
       </c>
       <c r="F12" s="17" t="s">
@@ -4277,17 +4259,17 @@
       <c r="H12" s="38"/>
       <c r="J12" s="41"/>
       <c r="K12" s="41"/>
-      <c r="L12" s="71"/>
-      <c r="M12" s="71"/>
-    </row>
-    <row r="13" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L12"/>
+      <c r="M12"/>
+    </row>
+    <row r="13" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="39"/>
-      <c r="B13" s="91" t="s">
+      <c r="B13" s="87" t="s">
         <v>65</v>
       </c>
       <c r="C13" s="35"/>
-      <c r="D13" s="92"/>
-      <c r="E13" s="88">
+      <c r="D13" s="88"/>
+      <c r="E13" s="84">
         <v>212784</v>
       </c>
       <c r="F13" s="17" t="s">
@@ -4300,10 +4282,10 @@
       <c r="H13" s="38"/>
       <c r="J13" s="41"/>
       <c r="K13" s="41"/>
-      <c r="L13" s="71"/>
-      <c r="M13" s="71"/>
-    </row>
-    <row r="14" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L13"/>
+      <c r="M13"/>
+    </row>
+    <row r="14" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="39">
         <v>5900</v>
       </c>
@@ -4313,8 +4295,8 @@
       <c r="C14" s="35">
         <v>0</v>
       </c>
-      <c r="D14" s="92"/>
-      <c r="E14" s="88">
+      <c r="D14" s="88"/>
+      <c r="E14" s="84">
         <v>983246</v>
       </c>
       <c r="F14" s="17" t="s">
@@ -4325,23 +4307,23 @@
         <v>983280</v>
       </c>
       <c r="H14" s="38"/>
-      <c r="J14" s="71"/>
-      <c r="K14" s="71"/>
-      <c r="L14" s="71"/>
-      <c r="M14" s="71"/>
-    </row>
-    <row r="15" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J14"/>
+      <c r="K14"/>
+      <c r="L14"/>
+      <c r="M14"/>
+    </row>
+    <row r="15" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="39">
         <v>11600</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C15" s="35">
         <v>0</v>
       </c>
-      <c r="D15" s="92"/>
-      <c r="E15" s="88">
+      <c r="D15" s="88"/>
+      <c r="E15" s="84">
         <v>22130</v>
       </c>
       <c r="F15" s="17" t="s">
@@ -4351,23 +4333,23 @@
         <v>23940</v>
       </c>
       <c r="H15" s="38"/>
-      <c r="J15" s="71"/>
-      <c r="K15" s="71"/>
-      <c r="L15" s="71"/>
-      <c r="M15" s="71"/>
-    </row>
-    <row r="16" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J15"/>
+      <c r="K15"/>
+      <c r="L15"/>
+      <c r="M15"/>
+    </row>
+    <row r="16" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="39">
         <v>0</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C16" s="35">
         <v>6000</v>
       </c>
-      <c r="D16" s="92"/>
-      <c r="E16" s="88">
+      <c r="D16" s="88"/>
+      <c r="E16" s="84">
         <v>0</v>
       </c>
       <c r="F16" s="17" t="s">
@@ -4378,24 +4360,24 @@
         <v>8070</v>
       </c>
       <c r="H16" s="38"/>
-      <c r="J16" s="71"/>
-      <c r="K16" s="71"/>
-      <c r="L16" s="71"/>
-      <c r="M16" s="71"/>
-    </row>
-    <row r="17" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J16"/>
+      <c r="K16"/>
+      <c r="L16"/>
+      <c r="M16"/>
+    </row>
+    <row r="17" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="39">
         <v>0</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="C17" s="35">
         <f>1425+730</f>
         <v>2155</v>
       </c>
-      <c r="D17" s="92"/>
-      <c r="E17" s="88">
+      <c r="D17" s="88"/>
+      <c r="E17" s="84">
         <v>357</v>
       </c>
       <c r="F17" s="17" t="s">
@@ -4408,12 +4390,12 @@
         <f>SUM(G8:G17)</f>
         <v>1535868</v>
       </c>
-      <c r="J17" s="71"/>
-      <c r="K17" s="71"/>
-      <c r="L17" s="71"/>
-      <c r="M17" s="71"/>
-    </row>
-    <row r="18" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J17"/>
+      <c r="K17"/>
+      <c r="L17"/>
+      <c r="M17"/>
+    </row>
+    <row r="18" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="39">
         <v>6160</v>
       </c>
@@ -4423,17 +4405,17 @@
       <c r="C18" s="35">
         <v>300</v>
       </c>
-      <c r="D18" s="92"/>
-      <c r="E18" s="88"/>
+      <c r="D18" s="88"/>
+      <c r="E18" s="84"/>
       <c r="F18" s="17"/>
       <c r="G18" s="35"/>
       <c r="H18" s="38"/>
-      <c r="J18" s="71"/>
-      <c r="K18" s="71"/>
-      <c r="L18" s="71"/>
-      <c r="M18" s="71"/>
-    </row>
-    <row r="19" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J18"/>
+      <c r="K18"/>
+      <c r="L18"/>
+      <c r="M18"/>
+    </row>
+    <row r="19" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="39">
         <v>31535</v>
       </c>
@@ -4444,19 +4426,19 @@
         <f>18346.76+2750</f>
         <v>21096.76</v>
       </c>
-      <c r="D19" s="92"/>
-      <c r="E19" s="88"/>
-      <c r="F19" s="91" t="s">
-        <v>187</v>
+      <c r="D19" s="88"/>
+      <c r="E19" s="84"/>
+      <c r="F19" s="87" t="s">
+        <v>186</v>
       </c>
       <c r="G19" s="35"/>
       <c r="H19" s="38"/>
-      <c r="J19" s="71"/>
-      <c r="K19" s="71"/>
-      <c r="L19" s="71"/>
-      <c r="M19" s="71"/>
-    </row>
-    <row r="20" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J19"/>
+      <c r="K19"/>
+      <c r="L19"/>
+      <c r="M19"/>
+    </row>
+    <row r="20" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="39">
         <v>57555</v>
       </c>
@@ -4467,24 +4449,24 @@
         <f>40335.24-1500</f>
         <v>38835.24</v>
       </c>
-      <c r="D20" s="92"/>
-      <c r="E20" s="88">
+      <c r="D20" s="88"/>
+      <c r="E20" s="84">
         <v>5000</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G20" s="35"/>
       <c r="H20" s="38">
         <f>SUM(G20:G20)</f>
         <v>0</v>
       </c>
-      <c r="J20" s="71"/>
-      <c r="K20" s="71"/>
-      <c r="L20" s="71"/>
-      <c r="M20" s="71"/>
-    </row>
-    <row r="21" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J20"/>
+      <c r="K20"/>
+      <c r="L20"/>
+      <c r="M20"/>
+    </row>
+    <row r="21" spans="1:13" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="39">
         <v>7550</v>
       </c>
@@ -4494,35 +4476,35 @@
       <c r="C21" s="35">
         <v>10500</v>
       </c>
-      <c r="D21" s="92"/>
-      <c r="E21" s="88"/>
+      <c r="D21" s="88"/>
+      <c r="E21" s="84"/>
       <c r="F21" s="17"/>
       <c r="G21" s="35"/>
       <c r="H21" s="38"/>
-      <c r="J21" s="71"/>
-      <c r="K21" s="71"/>
-      <c r="L21" s="71"/>
-      <c r="M21" s="71"/>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J21"/>
+      <c r="K21"/>
+      <c r="L21"/>
+      <c r="M21"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="39">
         <v>6700</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C22" s="35">
         <v>0</v>
       </c>
-      <c r="D22" s="92"/>
-      <c r="E22" s="88"/>
-      <c r="F22" s="91" t="s">
-        <v>186</v>
-      </c>
-      <c r="G22" s="93"/>
+      <c r="D22" s="88"/>
+      <c r="E22" s="84"/>
+      <c r="F22" s="87" t="s">
+        <v>185</v>
+      </c>
+      <c r="G22" s="89"/>
       <c r="H22" s="12"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="39">
         <v>109647</v>
       </c>
@@ -4533,8 +4515,8 @@
         <f>Workings!D16</f>
         <v>119816</v>
       </c>
-      <c r="D23" s="92"/>
-      <c r="E23" s="89">
+      <c r="D23" s="88"/>
+      <c r="E23" s="85">
         <v>6866</v>
       </c>
       <c r="F23" s="17" t="s">
@@ -4544,22 +4526,22 @@
       <c r="H23" s="13">
         <v>8000</v>
       </c>
-      <c r="J23" s="73"/>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J23" s="71"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="39">
         <f>6344+6678</f>
         <v>13022</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C24" s="35">
         <f>Workings!D22+Workings!D40</f>
         <v>12237</v>
       </c>
-      <c r="D24" s="92"/>
-      <c r="E24" s="89">
+      <c r="D24" s="88"/>
+      <c r="E24" s="85">
         <v>72051</v>
       </c>
       <c r="F24" s="17" t="s">
@@ -4571,18 +4553,18 @@
       </c>
       <c r="H24" s="12"/>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="39">
         <v>35700</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C25" s="35">
         <f>Workings!D28</f>
         <v>14744</v>
       </c>
-      <c r="D25" s="92"/>
+      <c r="D25" s="88"/>
       <c r="E25" s="7">
         <v>-14999</v>
       </c>
@@ -4595,7 +4577,7 @@
       </c>
       <c r="H25" s="12"/>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="39">
         <v>64412</v>
       </c>
@@ -4606,7 +4588,7 @@
         <f>Workings!D34</f>
         <v>74336</v>
       </c>
-      <c r="D26" s="92">
+      <c r="D26" s="88">
         <f>SUM(C14:C26)</f>
         <v>300020</v>
       </c>
@@ -4622,18 +4604,18 @@
       </c>
       <c r="H26" s="12"/>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="39"/>
-      <c r="B27" s="91" t="s">
+      <c r="B27" s="87" t="s">
         <v>74</v>
       </c>
       <c r="C27" s="35"/>
-      <c r="D27" s="92"/>
+      <c r="D27" s="88"/>
       <c r="E27" s="7">
         <v>-273</v>
       </c>
       <c r="F27" s="17" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G27" s="17">
         <f>573</f>
@@ -4641,7 +4623,7 @@
       </c>
       <c r="H27" s="12"/>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="39">
         <v>300000</v>
       </c>
@@ -4652,12 +4634,12 @@
         <f>305000+5000</f>
         <v>310000</v>
       </c>
-      <c r="D28" s="92"/>
+      <c r="D28" s="88"/>
       <c r="E28" s="7">
         <v>-14158</v>
       </c>
       <c r="F28" s="17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G28" s="17">
         <f>15754</f>
@@ -4665,7 +4647,7 @@
       </c>
       <c r="H28" s="12"/>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="39">
         <v>93200</v>
       </c>
@@ -4676,12 +4658,12 @@
         <f>86000+8000</f>
         <v>94000</v>
       </c>
-      <c r="D29" s="92"/>
+      <c r="D29" s="88"/>
       <c r="E29" s="7">
         <v>-7171</v>
       </c>
       <c r="F29" s="17" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G29" s="6">
         <f>9473</f>
@@ -4692,7 +4674,7 @@
         <v>1973</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="39">
         <v>6363</v>
       </c>
@@ -4702,14 +4684,14 @@
       <c r="C30" s="35">
         <v>3682</v>
       </c>
-      <c r="D30" s="92"/>
+      <c r="D30" s="88"/>
       <c r="E30" s="7"/>
       <c r="F30" s="17"/>
       <c r="G30" s="17"/>
       <c r="H30" s="12"/>
       <c r="L30" s="41"/>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="39">
         <v>120000</v>
       </c>
@@ -4719,16 +4701,16 @@
       <c r="C31" s="35">
         <v>115500</v>
       </c>
-      <c r="D31" s="92"/>
-      <c r="E31" s="89"/>
-      <c r="F31" s="91" t="s">
+      <c r="D31" s="88"/>
+      <c r="E31" s="85"/>
+      <c r="F31" s="87" t="s">
         <v>31</v>
       </c>
       <c r="G31" s="17"/>
       <c r="H31" s="12"/>
       <c r="L31" s="41"/>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="12">
         <v>23288</v>
       </c>
@@ -4738,11 +4720,11 @@
       <c r="C32" s="36">
         <v>22488</v>
       </c>
-      <c r="D32" s="92">
+      <c r="D32" s="88">
         <f>SUM(C28:C32)</f>
         <v>545670</v>
       </c>
-      <c r="E32" s="88">
+      <c r="E32" s="84">
         <v>451</v>
       </c>
       <c r="F32" s="17" t="s">
@@ -4754,19 +4736,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="12"/>
-      <c r="B33" s="91" t="s">
+      <c r="B33" s="87" t="s">
         <v>32</v>
       </c>
-      <c r="C33" s="93"/>
-      <c r="D33" s="94"/>
-      <c r="E33" s="88"/>
+      <c r="C33" s="89"/>
+      <c r="D33" s="90"/>
+      <c r="E33" s="84"/>
       <c r="F33" s="17"/>
       <c r="G33" s="17"/>
       <c r="H33" s="13"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="12">
         <v>4265</v>
       </c>
@@ -4777,233 +4759,233 @@
         <f>BS!G28+BS!G32+BS!G36+BS!G40+BS!G44</f>
         <v>6542</v>
       </c>
-      <c r="D34" s="94"/>
-      <c r="E34" s="89"/>
+      <c r="D34" s="90"/>
+      <c r="E34" s="85"/>
       <c r="F34" s="17"/>
       <c r="G34" s="17"/>
       <c r="H34" s="13"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="12">
         <v>120000</v>
       </c>
       <c r="B35" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="C35" s="93">
+      <c r="C35" s="89">
         <v>120000</v>
       </c>
-      <c r="D35" s="94"/>
-      <c r="E35" s="89"/>
+      <c r="D35" s="90"/>
+      <c r="E35" s="85"/>
       <c r="F35" s="17"/>
       <c r="G35" s="17"/>
       <c r="H35" s="13"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="12">
         <v>36000</v>
       </c>
       <c r="B36" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C36" s="93">
+      <c r="C36" s="89">
         <v>39600</v>
       </c>
-      <c r="D36" s="94"/>
-      <c r="E36" s="89"/>
+      <c r="D36" s="90"/>
+      <c r="E36" s="85"/>
       <c r="F36" s="17"/>
       <c r="G36" s="17"/>
       <c r="H36" s="13"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="12">
         <v>3400</v>
       </c>
       <c r="B37" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C37" s="93">
+      <c r="C37" s="89">
         <v>3400</v>
       </c>
-      <c r="D37" s="94"/>
-      <c r="E37" s="90"/>
+      <c r="D37" s="90"/>
+      <c r="E37" s="86"/>
       <c r="F37" s="17"/>
       <c r="G37" s="17"/>
       <c r="H37" s="13"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="12">
         <v>826</v>
       </c>
       <c r="B38" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="C38" s="93">
+      <c r="C38" s="89">
         <v>826</v>
       </c>
-      <c r="D38" s="94"/>
+      <c r="D38" s="90"/>
       <c r="E38" s="7"/>
       <c r="F38" s="17"/>
       <c r="G38" s="17"/>
       <c r="H38" s="13"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="12">
         <v>6705</v>
       </c>
       <c r="B39" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="C39" s="93">
+      <c r="C39" s="89">
         <v>2328</v>
       </c>
-      <c r="D39" s="94"/>
+      <c r="D39" s="90"/>
       <c r="E39" s="7"/>
       <c r="F39" s="17"/>
       <c r="G39" s="17"/>
       <c r="H39" s="13"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="12">
         <v>8323</v>
       </c>
       <c r="B40" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="C40" s="93">
+      <c r="C40" s="89">
         <v>8024</v>
       </c>
-      <c r="D40" s="94"/>
+      <c r="D40" s="90"/>
       <c r="E40" s="7"/>
       <c r="F40" s="17"/>
       <c r="G40" s="17"/>
       <c r="H40" s="13"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="12">
         <v>200</v>
       </c>
       <c r="B41" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="C41" s="93">
+      <c r="C41" s="89">
         <v>412</v>
       </c>
-      <c r="D41" s="94"/>
+      <c r="D41" s="90"/>
       <c r="E41" s="7"/>
       <c r="F41" s="17"/>
       <c r="G41" s="17"/>
       <c r="H41" s="13"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="12">
         <v>0</v>
       </c>
       <c r="B42" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="C42" s="89">
         <v>262</v>
       </c>
-      <c r="C42" s="93">
-        <v>262</v>
-      </c>
-      <c r="D42" s="94"/>
+      <c r="D42" s="90"/>
       <c r="E42" s="7"/>
       <c r="F42" s="17"/>
       <c r="G42" s="17"/>
       <c r="H42" s="13"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="12">
         <v>505.03999999999996</v>
       </c>
       <c r="B43" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="C43" s="93">
+      <c r="C43" s="89">
         <v>145.74</v>
       </c>
-      <c r="D43" s="94"/>
+      <c r="D43" s="90"/>
       <c r="E43" s="7"/>
       <c r="F43" s="17"/>
       <c r="G43" s="17"/>
       <c r="H43" s="13"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="12">
         <v>1856</v>
       </c>
       <c r="B44" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="C44" s="93">
+      <c r="C44" s="89">
         <v>3195</v>
       </c>
-      <c r="D44" s="94"/>
+      <c r="D44" s="90"/>
       <c r="E44" s="7"/>
       <c r="F44" s="17"/>
       <c r="G44" s="17"/>
       <c r="H44" s="13"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="12">
         <v>11435</v>
       </c>
       <c r="B45" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="C45" s="93">
+        <v>158</v>
+      </c>
+      <c r="C45" s="89">
         <v>0</v>
       </c>
-      <c r="D45" s="94"/>
+      <c r="D45" s="90"/>
       <c r="E45" s="7"/>
       <c r="F45" s="17"/>
       <c r="G45" s="17"/>
       <c r="H45" s="13"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="12">
         <v>1800</v>
       </c>
       <c r="B46" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="C46" s="93">
+      <c r="C46" s="89">
         <f>500-1</f>
         <v>499</v>
       </c>
-      <c r="D46" s="94"/>
+      <c r="D46" s="90"/>
       <c r="E46" s="7"/>
       <c r="F46" s="17"/>
       <c r="G46" s="17"/>
       <c r="H46" s="13"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="12">
         <v>18500</v>
       </c>
       <c r="B47" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="C47" s="93">
+        <v>145</v>
+      </c>
+      <c r="C47" s="89">
         <f>18000</f>
         <v>18000</v>
       </c>
-      <c r="D47" s="94"/>
+      <c r="D47" s="90"/>
       <c r="E47" s="7"/>
       <c r="F47" s="17"/>
       <c r="G47" s="17"/>
       <c r="H47" s="13"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="12">
         <v>4080</v>
       </c>
-      <c r="B48" s="95" t="s">
+      <c r="B48" s="91" t="s">
         <v>93</v>
       </c>
       <c r="C48" s="43">
         <v>4080</v>
       </c>
-      <c r="D48" s="94">
+      <c r="D48" s="90">
         <f>SUM(C34:C48)</f>
         <v>207313.74</v>
       </c>
@@ -5012,26 +4994,26 @@
       <c r="G48" s="17"/>
       <c r="H48" s="13"/>
     </row>
-    <row r="49" spans="1:13" ht="8.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" ht="8.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="12"/>
       <c r="B49" s="17"/>
-      <c r="C49" s="93"/>
-      <c r="D49" s="94"/>
+      <c r="C49" s="89"/>
+      <c r="D49" s="90"/>
       <c r="E49" s="7"/>
       <c r="F49" s="17"/>
       <c r="G49" s="17"/>
       <c r="H49" s="13"/>
-      <c r="J49" s="73"/>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J49" s="71"/>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" s="12">
         <v>30118</v>
       </c>
       <c r="B50" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="C50" s="93"/>
-      <c r="D50" s="94">
+      <c r="C50" s="89"/>
+      <c r="D50" s="90">
         <f>ROUND((H53-SUM(D7:D49))*25%,)</f>
         <v>42015</v>
       </c>
@@ -5039,17 +5021,17 @@
       <c r="F50" s="17"/>
       <c r="G50" s="17"/>
       <c r="H50" s="13"/>
-      <c r="J50" s="73"/>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J50" s="71"/>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="12">
         <v>90352.959999999963</v>
       </c>
       <c r="B51" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="C51" s="93"/>
-      <c r="D51" s="94">
+      <c r="C51" s="89"/>
+      <c r="D51" s="90">
         <f>H53-SUM(D7:D50)</f>
         <v>126044.26000000001</v>
       </c>
@@ -5057,165 +5039,165 @@
       <c r="F51" s="17"/>
       <c r="G51" s="17"/>
       <c r="H51" s="12"/>
-      <c r="J51" s="73"/>
-    </row>
-    <row r="52" spans="1:13" ht="8.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J51" s="71"/>
+    </row>
+    <row r="52" spans="1:13" ht="8.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="12"/>
       <c r="B52" s="20"/>
-      <c r="C52" s="93"/>
-      <c r="D52" s="94"/>
+      <c r="C52" s="89"/>
+      <c r="D52" s="90"/>
       <c r="E52" s="7"/>
       <c r="F52" s="17"/>
       <c r="G52" s="17"/>
       <c r="H52" s="12"/>
-      <c r="J52" s="73"/>
-    </row>
-    <row r="53" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J52" s="71"/>
+    </row>
+    <row r="53" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="21">
         <f>SUM(A7:A51)</f>
         <v>1536227</v>
       </c>
-      <c r="B53" s="178" t="s">
+      <c r="B53" s="174" t="s">
         <v>92</v>
       </c>
-      <c r="C53" s="179"/>
-      <c r="D53" s="86">
+      <c r="C53" s="175"/>
+      <c r="D53" s="82">
         <f>SUM(D7:D51)</f>
         <v>1545841</v>
       </c>
-      <c r="E53" s="82">
+      <c r="E53" s="78">
         <f>SUM(E7:E51)</f>
         <v>1536227</v>
       </c>
-      <c r="F53" s="178" t="s">
+      <c r="F53" s="174" t="s">
         <v>92</v>
       </c>
-      <c r="G53" s="179"/>
+      <c r="G53" s="175"/>
       <c r="H53" s="21">
         <f>SUM(H7:H51)</f>
         <v>1545841</v>
       </c>
     </row>
-    <row r="54" spans="1:13" ht="8.1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="112"/>
+    <row r="54" spans="1:13" ht="8.1" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="108"/>
       <c r="B54" s="54"/>
       <c r="C54" s="55"/>
       <c r="D54" s="53"/>
       <c r="E54" s="53"/>
       <c r="F54" s="19"/>
       <c r="G54" s="19"/>
-      <c r="H54" s="90"/>
-    </row>
-    <row r="55" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="104" t="s">
-        <v>194</v>
-      </c>
-      <c r="B55" s="105"/>
-      <c r="C55" s="105"/>
+      <c r="H54" s="86"/>
+    </row>
+    <row r="55" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="100" t="s">
+        <v>193</v>
+      </c>
+      <c r="B55" s="101"/>
+      <c r="C55" s="101"/>
       <c r="D55" s="53"/>
-      <c r="E55" s="180" t="str">
+      <c r="E55" s="176" t="str">
         <f>"For "&amp;A1</f>
         <v>For PARK ROSE CO-OPERATIVE HOUSING SOCIETY LTD.</v>
       </c>
-      <c r="F55" s="180"/>
-      <c r="G55" s="180"/>
-      <c r="H55" s="181"/>
-    </row>
-    <row r="56" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="106"/>
-      <c r="B56" s="105"/>
-      <c r="C56" s="105"/>
+      <c r="F55" s="176"/>
+      <c r="G55" s="176"/>
+      <c r="H55" s="177"/>
+    </row>
+    <row r="56" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="102"/>
+      <c r="B56" s="101"/>
+      <c r="C56" s="101"/>
       <c r="D56" s="53"/>
       <c r="E56" s="17"/>
       <c r="F56" s="17"/>
       <c r="G56" s="17"/>
-      <c r="H56" s="90"/>
-    </row>
-    <row r="57" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="107"/>
-      <c r="B57" s="105"/>
-      <c r="C57" s="105"/>
+      <c r="H56" s="86"/>
+    </row>
+    <row r="57" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="103"/>
+      <c r="B57" s="101"/>
+      <c r="C57" s="101"/>
       <c r="D57" s="53"/>
       <c r="E57" s="17"/>
       <c r="F57" s="17"/>
       <c r="G57" s="17"/>
-      <c r="H57" s="90"/>
-    </row>
-    <row r="58" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="106"/>
-      <c r="B58" s="105"/>
-      <c r="C58" s="105"/>
+      <c r="H57" s="86"/>
+    </row>
+    <row r="58" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="102"/>
+      <c r="B58" s="101"/>
+      <c r="C58" s="101"/>
       <c r="D58" s="53"/>
       <c r="E58" s="17"/>
       <c r="F58" s="17"/>
       <c r="G58" s="17"/>
-      <c r="H58" s="90"/>
+      <c r="H58" s="86"/>
       <c r="J58" s="10"/>
       <c r="K58" s="10"/>
       <c r="L58" s="10"/>
       <c r="M58" s="10"/>
     </row>
-    <row r="59" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="108" t="s">
-        <v>372</v>
-      </c>
-      <c r="B59" s="109"/>
-      <c r="C59" s="110"/>
+    <row r="59" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="104" t="s">
+        <v>370</v>
+      </c>
+      <c r="B59" s="105"/>
+      <c r="C59" s="106"/>
       <c r="D59" s="53"/>
-      <c r="E59" s="167"/>
-      <c r="F59" s="167"/>
-      <c r="G59" s="167"/>
-      <c r="H59" s="168"/>
+      <c r="E59" s="163"/>
+      <c r="F59" s="163"/>
+      <c r="G59" s="163"/>
+      <c r="H59" s="164"/>
       <c r="J59" s="10"/>
       <c r="K59" s="10"/>
       <c r="L59" s="10"/>
       <c r="M59" s="10"/>
     </row>
-    <row r="60" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="111" t="s">
-        <v>373</v>
-      </c>
-      <c r="B60" s="109"/>
-      <c r="C60" s="110"/>
+    <row r="60" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="107" t="s">
+        <v>371</v>
+      </c>
+      <c r="B60" s="105"/>
+      <c r="C60" s="106"/>
       <c r="D60" s="53"/>
-      <c r="E60" s="167" t="s">
-        <v>195</v>
-      </c>
-      <c r="F60" s="167"/>
-      <c r="G60" s="167"/>
-      <c r="H60" s="168"/>
+      <c r="E60" s="163" t="s">
+        <v>194</v>
+      </c>
+      <c r="F60" s="163"/>
+      <c r="G60" s="163"/>
+      <c r="H60" s="164"/>
       <c r="J60" s="10"/>
       <c r="K60" s="10"/>
       <c r="L60" s="10"/>
       <c r="M60" s="10"/>
     </row>
-    <row r="61" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="111" t="s">
-        <v>374</v>
-      </c>
-      <c r="B61" s="109"/>
-      <c r="C61" s="110"/>
+    <row r="61" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="107" t="s">
+        <v>376</v>
+      </c>
+      <c r="B61" s="105"/>
+      <c r="C61" s="106"/>
       <c r="D61" s="53"/>
       <c r="E61" s="17"/>
       <c r="F61" s="17"/>
       <c r="G61" s="17"/>
-      <c r="H61" s="90"/>
+      <c r="H61" s="86"/>
       <c r="J61" s="10"/>
       <c r="K61" s="10"/>
       <c r="L61" s="10"/>
       <c r="M61" s="10"/>
     </row>
-    <row r="62" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="165">
-        <v>46185</v>
-      </c>
-      <c r="B62" s="166"/>
-      <c r="C62" s="166"/>
-      <c r="D62" s="113"/>
-      <c r="E62" s="114"/>
-      <c r="F62" s="114"/>
-      <c r="G62" s="114"/>
-      <c r="H62" s="115"/>
+    <row r="62" spans="1:13" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="161">
+        <v>46215</v>
+      </c>
+      <c r="B62" s="162"/>
+      <c r="C62" s="162"/>
+      <c r="D62" s="109"/>
+      <c r="E62" s="110"/>
+      <c r="F62" s="110"/>
+      <c r="G62" s="110"/>
+      <c r="H62" s="111"/>
       <c r="J62" s="10"/>
       <c r="K62" s="10"/>
       <c r="L62" s="10"/>
@@ -5238,51 +5220,51 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.39370078740157483" bottom="0.19685039370078741" header="0.39370078740157483" footer="0.39370078740157483"/>
-  <pageSetup paperSize="9" scale="60" fitToHeight="0" orientation="landscape" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="60" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Y42"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.28515625" style="72" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" style="143" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.28515625" style="72" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.28515625" style="72" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.28515625" style="72" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.33203125" style="70" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.44140625" style="139" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.33203125" style="70" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.33203125" style="70" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.33203125" style="70" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5546875" style="10" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="10" style="10" customWidth="1"/>
-    <col min="10" max="10" width="12.5703125" style="10" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.28515625" style="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.7109375" style="72" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="8.7109375" style="116" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="9.28515625" style="116"/>
-    <col min="16" max="17" width="7" style="116" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="5" style="116" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.7109375" style="116" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.28515625" style="116"/>
+    <col min="10" max="10" width="12.5546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" style="70" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="8.6640625" style="112" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="9.33203125" style="112"/>
+    <col min="16" max="17" width="7" style="112" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="5" style="112" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.6640625" style="112" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.33203125" style="112"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B1" s="184" t="s">
+    <row r="1" spans="1:25" ht="18" x14ac:dyDescent="0.3">
+      <c r="B1" s="180" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="184"/>
-      <c r="H1" s="184"/>
-      <c r="I1" s="184"/>
-      <c r="J1" s="184"/>
-      <c r="K1" s="184"/>
-      <c r="L1" s="184"/>
-    </row>
-    <row r="2" spans="1:25" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="72" t="s">
+      <c r="C1" s="180"/>
+      <c r="D1" s="180"/>
+      <c r="E1" s="180"/>
+      <c r="F1" s="180"/>
+      <c r="G1" s="180"/>
+      <c r="H1" s="180"/>
+      <c r="I1" s="180"/>
+      <c r="J1" s="180"/>
+      <c r="K1" s="180"/>
+      <c r="L1" s="180"/>
+    </row>
+    <row r="2" spans="1:25" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="70" t="s">
         <v>39</v>
       </c>
       <c r="B2" s="19"/>
@@ -5297,29 +5279,29 @@
       <c r="K2" s="19"/>
       <c r="L2" s="19"/>
     </row>
-    <row r="3" spans="1:25" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A3" s="185" t="s">
-        <v>204</v>
-      </c>
-      <c r="B3" s="185"/>
-      <c r="C3" s="185"/>
-      <c r="D3" s="185"/>
-      <c r="E3" s="185"/>
-      <c r="F3" s="185"/>
-      <c r="G3" s="185"/>
-      <c r="H3" s="185"/>
-      <c r="I3" s="185"/>
-      <c r="J3" s="185"/>
-      <c r="K3" s="185"/>
-      <c r="L3" s="185"/>
-      <c r="U3" s="116">
+    <row r="3" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A3" s="181" t="s">
+        <v>203</v>
+      </c>
+      <c r="B3" s="181"/>
+      <c r="C3" s="181"/>
+      <c r="D3" s="181"/>
+      <c r="E3" s="181"/>
+      <c r="F3" s="181"/>
+      <c r="G3" s="181"/>
+      <c r="H3" s="181"/>
+      <c r="I3" s="181"/>
+      <c r="J3" s="181"/>
+      <c r="K3" s="181"/>
+      <c r="L3" s="181"/>
+      <c r="U3" s="112">
         <v>4998</v>
       </c>
-      <c r="V3" s="116" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V3" s="112" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="40"/>
       <c r="C4" s="40"/>
       <c r="D4" s="40"/>
@@ -5330,51 +5312,51 @@
       <c r="I4" s="40"/>
       <c r="J4" s="40"/>
       <c r="K4" s="44"/>
-      <c r="L4" s="80" t="s">
+      <c r="L4" s="76" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:25" s="72" customFormat="1" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="161" t="s">
+    <row r="5" spans="1:25" s="70" customFormat="1" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="154" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="162" t="s">
+      <c r="B5" s="155" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="162" t="s">
+      <c r="C5" s="155" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="162" t="s">
+      <c r="D5" s="155" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="162" t="s">
+      <c r="E5" s="155" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="163" t="s">
+      <c r="F5" s="156" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="163" t="s">
-        <v>161</v>
-      </c>
-      <c r="H5" s="163" t="s">
-        <v>217</v>
-      </c>
-      <c r="I5" s="163" t="s">
-        <v>221</v>
-      </c>
-      <c r="J5" s="163" t="s">
+      <c r="G5" s="156" t="s">
+        <v>160</v>
+      </c>
+      <c r="H5" s="156" t="s">
+        <v>216</v>
+      </c>
+      <c r="I5" s="156" t="s">
+        <v>220</v>
+      </c>
+      <c r="J5" s="156" t="s">
         <v>10</v>
       </c>
-      <c r="K5" s="162" t="s">
+      <c r="K5" s="155" t="s">
         <v>6</v>
       </c>
-      <c r="L5" s="164" t="s">
+      <c r="L5" s="157" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="117"/>
-      <c r="B6" s="118" t="s">
+    <row r="6" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="113"/>
+      <c r="B6" s="114" t="s">
         <v>85</v>
       </c>
       <c r="F6" s="17"/>
@@ -5382,75 +5364,75 @@
       <c r="H6" s="17"/>
       <c r="I6" s="17"/>
       <c r="J6" s="17"/>
-      <c r="K6" s="72"/>
-      <c r="L6" s="119"/>
-    </row>
-    <row r="7" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="120">
+      <c r="K6" s="70"/>
+      <c r="L6" s="115"/>
+    </row>
+    <row r="7" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="116">
         <v>1</v>
       </c>
-      <c r="B7" s="121" t="s">
+      <c r="B7" s="117" t="s">
+        <v>222</v>
+      </c>
+      <c r="C7" s="118">
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="D7" s="119" t="s">
+        <v>86</v>
+      </c>
+      <c r="E7" s="119" t="s">
         <v>223</v>
       </c>
-      <c r="C7" s="122">
-        <v>6.0999999999999999E-2</v>
-      </c>
-      <c r="D7" s="123" t="s">
-        <v>86</v>
-      </c>
-      <c r="E7" s="123" t="s">
-        <v>224</v>
-      </c>
-      <c r="F7" s="124">
+      <c r="F7" s="120">
         <v>17000</v>
       </c>
-      <c r="G7" s="124">
+      <c r="G7" s="120">
         <v>0</v>
       </c>
-      <c r="H7" s="124">
+      <c r="H7" s="120">
         <v>0</v>
       </c>
-      <c r="I7" s="124">
+      <c r="I7" s="120">
         <f>SUM(G7:H7)</f>
         <v>0</v>
       </c>
-      <c r="J7" s="124">
+      <c r="J7" s="120">
         <f>F7+I7</f>
         <v>17000</v>
       </c>
-      <c r="K7" s="123" t="s">
-        <v>225</v>
-      </c>
-      <c r="L7" s="125">
+      <c r="K7" s="119" t="s">
+        <v>224</v>
+      </c>
+      <c r="L7" s="121">
         <v>17000</v>
       </c>
-      <c r="P7" s="116">
+      <c r="P7" s="112">
         <f>18099</f>
         <v>18099</v>
       </c>
-      <c r="Q7" s="116">
+      <c r="Q7" s="112">
         <f>18130</f>
         <v>18130</v>
       </c>
-      <c r="R7" s="116">
+      <c r="R7" s="112">
         <f>Q7-P7</f>
         <v>31</v>
       </c>
-      <c r="S7" s="116">
+      <c r="S7" s="112">
         <f>ROUND(R7/90%,0)</f>
         <v>34</v>
       </c>
-      <c r="T7" s="116">
+      <c r="T7" s="112">
         <f>S7-R7</f>
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="126"/>
-      <c r="B8" s="127"/>
-      <c r="C8" s="128"/>
-      <c r="D8" s="128"/>
-      <c r="E8" s="128"/>
+    <row r="8" spans="1:25" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="122"/>
+      <c r="B8" s="123"/>
+      <c r="C8" s="124"/>
+      <c r="D8" s="124"/>
+      <c r="E8" s="124"/>
       <c r="F8" s="21">
         <f>SUM(F7)</f>
         <v>17000</v>
@@ -5471,30 +5453,30 @@
         <f t="shared" si="0"/>
         <v>17000</v>
       </c>
-      <c r="K8" s="128"/>
-      <c r="L8" s="129">
+      <c r="K8" s="124"/>
+      <c r="L8" s="125">
         <f t="shared" si="0"/>
         <v>17000</v>
       </c>
-      <c r="P8" s="130"/>
-      <c r="S8" s="116">
+      <c r="P8" s="126"/>
+      <c r="S8" s="112">
         <f>1221-S7</f>
         <v>1187</v>
       </c>
-      <c r="T8" s="116">
+      <c r="T8" s="112">
         <f>T7-124</f>
         <v>-121</v>
       </c>
-      <c r="V8" s="116">
+      <c r="V8" s="112">
         <v>6992</v>
       </c>
-      <c r="W8" s="116">
+      <c r="W8" s="112">
         <v>701</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="20.100000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="117"/>
-      <c r="B9" s="118" t="s">
+    <row r="9" spans="1:25" ht="20.100000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="113"/>
+      <c r="B9" s="114" t="s">
         <v>87</v>
       </c>
       <c r="F9" s="17"/>
@@ -5502,216 +5484,216 @@
       <c r="H9" s="17"/>
       <c r="I9" s="17"/>
       <c r="J9" s="17"/>
-      <c r="K9" s="72"/>
-      <c r="L9" s="119"/>
-      <c r="V9" s="116">
+      <c r="K9" s="70"/>
+      <c r="L9" s="115"/>
+      <c r="V9" s="112">
         <f>V8-W21</f>
         <v>1154</v>
       </c>
-      <c r="W9" s="116">
+      <c r="W9" s="112">
         <f>W8-V17</f>
         <v>117</v>
       </c>
-      <c r="X9" s="116">
+      <c r="X9" s="112">
         <f>V9-W9</f>
         <v>1037</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="120">
+    <row r="10" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="116">
         <v>2</v>
       </c>
-      <c r="B10" s="121" t="s">
-        <v>226</v>
-      </c>
-      <c r="C10" s="131">
+      <c r="B10" s="117" t="s">
+        <v>225</v>
+      </c>
+      <c r="C10" s="127">
         <v>0.06</v>
       </c>
-      <c r="D10" s="123" t="s">
+      <c r="D10" s="119" t="s">
         <v>86</v>
       </c>
-      <c r="E10" s="123" t="s">
-        <v>181</v>
-      </c>
-      <c r="F10" s="124">
+      <c r="E10" s="119" t="s">
+        <v>180</v>
+      </c>
+      <c r="F10" s="120">
         <v>85162</v>
       </c>
-      <c r="G10" s="124">
+      <c r="G10" s="120">
         <v>0</v>
       </c>
-      <c r="H10" s="124">
+      <c r="H10" s="120">
         <f>1548-157</f>
         <v>1391</v>
       </c>
-      <c r="I10" s="124">
+      <c r="I10" s="120">
         <f t="shared" ref="I10:I13" si="1">SUM(G10:H10)</f>
         <v>1391</v>
       </c>
-      <c r="J10" s="124">
+      <c r="J10" s="120">
         <f>F10+I10</f>
         <v>86553</v>
       </c>
-      <c r="K10" s="123" t="s">
-        <v>227</v>
-      </c>
-      <c r="L10" s="125">
+      <c r="K10" s="119" t="s">
+        <v>226</v>
+      </c>
+      <c r="L10" s="121">
         <v>90388</v>
       </c>
-      <c r="P10" s="116">
+      <c r="P10" s="112">
         <v>80004</v>
       </c>
-      <c r="Q10" s="116">
+      <c r="Q10" s="112">
         <v>81530</v>
       </c>
-      <c r="R10" s="116">
+      <c r="R10" s="112">
         <f>Q10-P10</f>
         <v>1526</v>
       </c>
-      <c r="S10" s="116">
+      <c r="S10" s="112">
         <f>ROUND(R10/90%,0)</f>
         <v>1696</v>
       </c>
-      <c r="T10" s="116">
+      <c r="T10" s="112">
         <f>S10-R10</f>
         <v>170</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="120">
+    <row r="11" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="116">
         <v>3</v>
       </c>
-      <c r="B11" s="121" t="s">
-        <v>163</v>
-      </c>
-      <c r="C11" s="132">
+      <c r="B11" s="117" t="s">
+        <v>162</v>
+      </c>
+      <c r="C11" s="128">
         <v>5.8500000000000003E-2</v>
       </c>
-      <c r="D11" s="123" t="s">
+      <c r="D11" s="119" t="s">
         <v>86</v>
       </c>
-      <c r="E11" s="123" t="s">
-        <v>182</v>
-      </c>
-      <c r="F11" s="124">
+      <c r="E11" s="119" t="s">
+        <v>181</v>
+      </c>
+      <c r="F11" s="120">
         <v>45393</v>
       </c>
-      <c r="G11" s="124">
+      <c r="G11" s="120">
         <v>0</v>
       </c>
-      <c r="H11" s="124">
+      <c r="H11" s="120">
         <f>533-50</f>
         <v>483</v>
       </c>
-      <c r="I11" s="124">
+      <c r="I11" s="120">
         <f t="shared" si="1"/>
         <v>483</v>
       </c>
-      <c r="J11" s="124">
+      <c r="J11" s="120">
         <f>F11+I11</f>
         <v>45876</v>
       </c>
-      <c r="K11" s="123" t="s">
-        <v>229</v>
-      </c>
-      <c r="L11" s="125">
+      <c r="K11" s="119" t="s">
+        <v>228</v>
+      </c>
+      <c r="L11" s="121">
         <v>48107</v>
       </c>
-      <c r="S11" s="116">
+      <c r="S11" s="112">
         <f>5490-S10</f>
         <v>3794</v>
       </c>
-      <c r="T11" s="116">
+      <c r="T11" s="112">
         <f>T10-550</f>
         <v>-380</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="120">
+    <row r="12" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="116">
         <v>4</v>
       </c>
-      <c r="B12" s="133" t="s">
-        <v>232</v>
-      </c>
-      <c r="C12" s="122">
+      <c r="B12" s="129" t="s">
+        <v>231</v>
+      </c>
+      <c r="C12" s="118">
         <v>6.6000000000000003E-2</v>
       </c>
-      <c r="D12" s="123" t="s">
+      <c r="D12" s="119" t="s">
         <v>86</v>
       </c>
-      <c r="E12" s="123" t="s">
-        <v>180</v>
-      </c>
-      <c r="F12" s="124">
+      <c r="E12" s="119" t="s">
+        <v>179</v>
+      </c>
+      <c r="F12" s="120">
         <v>134058</v>
       </c>
-      <c r="G12" s="124">
+      <c r="G12" s="120">
         <v>0</v>
       </c>
-      <c r="H12" s="124">
+      <c r="H12" s="120">
         <f>6522-648</f>
         <v>5874</v>
       </c>
-      <c r="I12" s="124">
+      <c r="I12" s="120">
         <f t="shared" si="1"/>
         <v>5874</v>
       </c>
-      <c r="J12" s="124">
+      <c r="J12" s="120">
         <f>F12+I12</f>
         <v>139932</v>
       </c>
-      <c r="K12" s="123" t="s">
-        <v>233</v>
-      </c>
-      <c r="L12" s="125">
+      <c r="K12" s="119" t="s">
+        <v>232</v>
+      </c>
+      <c r="L12" s="121">
         <v>142906</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="134">
+    <row r="13" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="130">
         <v>5</v>
       </c>
-      <c r="B13" s="133">
+      <c r="B13" s="129">
         <v>163971</v>
       </c>
-      <c r="C13" s="132">
+      <c r="C13" s="128">
         <v>7.2499999999999995E-2</v>
       </c>
-      <c r="D13" s="123" t="s">
+      <c r="D13" s="119" t="s">
+        <v>244</v>
+      </c>
+      <c r="E13" s="131" t="s">
         <v>245</v>
       </c>
-      <c r="E13" s="135" t="s">
-        <v>246</v>
-      </c>
-      <c r="F13" s="136">
+      <c r="F13" s="132">
         <v>126000</v>
       </c>
-      <c r="G13" s="124">
+      <c r="G13" s="120">
         <v>0</v>
       </c>
-      <c r="H13" s="136">
+      <c r="H13" s="132">
         <v>5180</v>
       </c>
-      <c r="I13" s="124">
+      <c r="I13" s="120">
         <f t="shared" si="1"/>
         <v>5180</v>
       </c>
-      <c r="J13" s="124">
+      <c r="J13" s="120">
         <f>F13+I13</f>
         <v>131180</v>
       </c>
-      <c r="K13" s="135" t="s">
-        <v>247</v>
-      </c>
-      <c r="L13" s="137">
+      <c r="K13" s="131" t="s">
+        <v>246</v>
+      </c>
+      <c r="L13" s="133">
         <v>135386</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="126"/>
-      <c r="B14" s="127"/>
-      <c r="C14" s="128"/>
-      <c r="D14" s="128"/>
-      <c r="E14" s="128"/>
+    <row r="14" spans="1:25" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="122"/>
+      <c r="B14" s="123"/>
+      <c r="C14" s="124"/>
+      <c r="D14" s="124"/>
+      <c r="E14" s="124"/>
       <c r="F14" s="21">
         <f t="shared" ref="F14:L14" si="2">SUM(F10:F13)</f>
         <v>390613</v>
@@ -5732,16 +5714,16 @@
         <f t="shared" si="2"/>
         <v>403541</v>
       </c>
-      <c r="K14" s="128"/>
+      <c r="K14" s="124"/>
       <c r="L14" s="21">
         <f t="shared" si="2"/>
         <v>416787</v>
       </c>
-      <c r="P14" s="130"/>
-    </row>
-    <row r="15" spans="1:25" ht="20.100000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="117"/>
-      <c r="B15" s="118" t="s">
+      <c r="P14" s="126"/>
+    </row>
+    <row r="15" spans="1:25" ht="20.100000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="113"/>
+      <c r="B15" s="114" t="s">
         <v>88</v>
       </c>
       <c r="F15" s="17"/>
@@ -5749,302 +5731,302 @@
       <c r="H15" s="17"/>
       <c r="I15" s="17"/>
       <c r="J15" s="17"/>
-      <c r="K15" s="72"/>
-      <c r="L15" s="119"/>
-      <c r="X15" s="116" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="120">
+      <c r="K15" s="70"/>
+      <c r="L15" s="115"/>
+      <c r="X15" s="112" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="116">
         <v>6</v>
       </c>
-      <c r="B16" s="121" t="s">
-        <v>218</v>
-      </c>
-      <c r="C16" s="132">
+      <c r="B16" s="117" t="s">
+        <v>217</v>
+      </c>
+      <c r="C16" s="128">
         <v>5.8500000000000003E-2</v>
       </c>
-      <c r="D16" s="123" t="s">
+      <c r="D16" s="119" t="s">
         <v>86</v>
       </c>
-      <c r="E16" s="123" t="s">
-        <v>176</v>
-      </c>
-      <c r="F16" s="124">
+      <c r="E16" s="119" t="s">
+        <v>175</v>
+      </c>
+      <c r="F16" s="120">
         <v>136004</v>
       </c>
-      <c r="G16" s="124">
+      <c r="G16" s="120">
         <v>0</v>
       </c>
-      <c r="H16" s="124">
+      <c r="H16" s="120">
         <f>221-25</f>
         <v>196</v>
       </c>
-      <c r="I16" s="124">
+      <c r="I16" s="120">
         <f t="shared" ref="I16:I20" si="3">SUM(G16:H16)</f>
         <v>196</v>
       </c>
-      <c r="J16" s="124">
+      <c r="J16" s="120">
         <f>F16+I16</f>
         <v>136200</v>
       </c>
-      <c r="K16" s="123" t="s">
-        <v>219</v>
-      </c>
-      <c r="L16" s="125">
+      <c r="K16" s="119" t="s">
+        <v>218</v>
+      </c>
+      <c r="L16" s="121">
         <v>144136</v>
       </c>
-      <c r="P16" s="116">
+      <c r="P16" s="112">
         <v>127766</v>
       </c>
-      <c r="Q16" s="116">
+      <c r="Q16" s="112">
         <v>127986</v>
       </c>
-      <c r="R16" s="116">
+      <c r="R16" s="112">
         <f>Q16-P16</f>
         <v>220</v>
       </c>
-      <c r="S16" s="116">
+      <c r="S16" s="112">
         <f>ROUND(R16/90%,0)</f>
         <v>244</v>
       </c>
-      <c r="T16" s="116">
+      <c r="T16" s="112">
         <f>S16-R16</f>
         <v>24</v>
       </c>
-      <c r="V16" s="116">
+      <c r="V16" s="112">
         <v>106388</v>
       </c>
-      <c r="X16" s="116">
+      <c r="X16" s="112">
         <f>Y16-V16</f>
         <v>1037</v>
       </c>
-      <c r="Y16" s="116">
+      <c r="Y16" s="112">
         <v>107425</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="120">
+    <row r="17" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="116">
         <v>7</v>
       </c>
-      <c r="B17" s="133" t="s">
-        <v>222</v>
-      </c>
-      <c r="C17" s="122">
+      <c r="B17" s="129" t="s">
+        <v>375</v>
+      </c>
+      <c r="C17" s="118">
         <v>6.0999999999999999E-2</v>
       </c>
-      <c r="D17" s="123" t="s">
+      <c r="D17" s="119" t="s">
         <v>86</v>
       </c>
-      <c r="E17" s="123" t="s">
-        <v>148</v>
-      </c>
-      <c r="F17" s="124">
+      <c r="E17" s="119" t="s">
+        <v>147</v>
+      </c>
+      <c r="F17" s="120">
         <f>256700</f>
         <v>256700</v>
       </c>
-      <c r="G17" s="124">
+      <c r="G17" s="120">
         <v>0</v>
       </c>
-      <c r="H17" s="124">
+      <c r="H17" s="120">
         <f>5220-524</f>
         <v>4696</v>
       </c>
-      <c r="I17" s="124">
+      <c r="I17" s="120">
         <f t="shared" si="3"/>
         <v>4696</v>
       </c>
-      <c r="J17" s="124">
+      <c r="J17" s="120">
         <f>F17+I17</f>
         <v>261396</v>
       </c>
-      <c r="K17" s="123" t="s">
-        <v>258</v>
-      </c>
-      <c r="L17" s="125">
+      <c r="K17" s="119" t="s">
+        <v>257</v>
+      </c>
+      <c r="L17" s="121">
         <v>289741</v>
       </c>
-      <c r="S17" s="116">
+      <c r="S17" s="112">
         <f>8617-S16</f>
         <v>8373</v>
       </c>
-      <c r="T17" s="116">
+      <c r="T17" s="112">
         <f>861-T16</f>
         <v>837</v>
       </c>
-      <c r="V17" s="116">
+      <c r="V17" s="112">
         <v>584</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="120">
+    <row r="18" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="116">
         <v>8</v>
       </c>
-      <c r="B18" s="133">
+      <c r="B18" s="129">
         <v>101043101006109</v>
       </c>
-      <c r="C18" s="132">
+      <c r="C18" s="128">
         <v>7.2499999999999995E-2</v>
       </c>
-      <c r="D18" s="123" t="s">
+      <c r="D18" s="119" t="s">
         <v>86</v>
       </c>
-      <c r="E18" s="123" t="s">
-        <v>162</v>
-      </c>
-      <c r="F18" s="124">
+      <c r="E18" s="119" t="s">
+        <v>161</v>
+      </c>
+      <c r="F18" s="120">
         <v>277000</v>
       </c>
-      <c r="G18" s="124">
+      <c r="G18" s="120">
         <f>6946-696</f>
         <v>6250</v>
       </c>
-      <c r="H18" s="124">
+      <c r="H18" s="120">
         <f>21044-2106</f>
         <v>18938</v>
       </c>
-      <c r="I18" s="124">
+      <c r="I18" s="120">
         <f t="shared" si="3"/>
         <v>25188</v>
       </c>
-      <c r="J18" s="124">
+      <c r="J18" s="120">
         <f>F18+I18</f>
         <v>302188</v>
       </c>
-      <c r="K18" s="123" t="s">
-        <v>179</v>
-      </c>
-      <c r="L18" s="125">
+      <c r="K18" s="119" t="s">
+        <v>178</v>
+      </c>
+      <c r="L18" s="121">
         <v>341592</v>
       </c>
-      <c r="W18" s="116">
+      <c r="W18" s="112">
         <v>100000</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="120">
+    <row r="19" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="116">
         <v>9</v>
       </c>
-      <c r="B19" s="133" t="s">
-        <v>244</v>
-      </c>
-      <c r="C19" s="122">
+      <c r="B19" s="129" t="s">
+        <v>243</v>
+      </c>
+      <c r="C19" s="118">
         <v>6.0999999999999999E-2</v>
       </c>
-      <c r="D19" s="123" t="s">
+      <c r="D19" s="119" t="s">
         <v>86</v>
       </c>
-      <c r="E19" s="123" t="s">
-        <v>178</v>
-      </c>
-      <c r="F19" s="124">
+      <c r="E19" s="119" t="s">
+        <v>177</v>
+      </c>
+      <c r="F19" s="120">
         <v>106388</v>
       </c>
-      <c r="G19" s="124">
+      <c r="G19" s="120">
         <v>0</v>
       </c>
-      <c r="H19" s="124">
+      <c r="H19" s="120">
         <f>1154-117</f>
         <v>1037</v>
       </c>
-      <c r="I19" s="124">
+      <c r="I19" s="120">
         <f t="shared" si="3"/>
         <v>1037</v>
       </c>
-      <c r="J19" s="124">
+      <c r="J19" s="120">
         <f>F19+I19</f>
         <v>107425</v>
       </c>
-      <c r="K19" s="123" t="s">
-        <v>178</v>
-      </c>
-      <c r="L19" s="125">
+      <c r="K19" s="119" t="s">
+        <v>177</v>
+      </c>
+      <c r="L19" s="121">
         <v>112878</v>
       </c>
-      <c r="W19" s="116">
+      <c r="W19" s="112">
         <v>1134</v>
       </c>
     </row>
-    <row r="20" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="134">
+    <row r="20" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="130">
         <v>10</v>
       </c>
-      <c r="B20" s="133">
+      <c r="B20" s="129">
         <v>163734</v>
       </c>
-      <c r="C20" s="132">
+      <c r="C20" s="128">
         <v>7.2499999999999995E-2</v>
       </c>
-      <c r="D20" s="123" t="s">
-        <v>245</v>
-      </c>
-      <c r="E20" s="135" t="s">
-        <v>252</v>
-      </c>
-      <c r="F20" s="136">
+      <c r="D20" s="119" t="s">
+        <v>244</v>
+      </c>
+      <c r="E20" s="131" t="s">
+        <v>251</v>
+      </c>
+      <c r="F20" s="132">
         <v>377000</v>
       </c>
-      <c r="G20" s="124">
+      <c r="G20" s="120">
         <v>0</v>
       </c>
-      <c r="H20" s="136">
+      <c r="H20" s="132">
         <v>20233</v>
       </c>
-      <c r="I20" s="124">
+      <c r="I20" s="120">
         <f t="shared" si="3"/>
         <v>20233</v>
       </c>
-      <c r="J20" s="124">
+      <c r="J20" s="120">
         <f>F20+I20</f>
         <v>397233</v>
       </c>
-      <c r="K20" s="135" t="s">
-        <v>253</v>
-      </c>
-      <c r="L20" s="137">
+      <c r="K20" s="131" t="s">
+        <v>252</v>
+      </c>
+      <c r="L20" s="133">
         <v>405085</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="126"/>
-      <c r="B21" s="127"/>
-      <c r="C21" s="128"/>
-      <c r="D21" s="128"/>
-      <c r="E21" s="128"/>
-      <c r="F21" s="129">
+    <row r="21" spans="1:24" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="122"/>
+      <c r="B21" s="123"/>
+      <c r="C21" s="124"/>
+      <c r="D21" s="124"/>
+      <c r="E21" s="124"/>
+      <c r="F21" s="125">
         <f t="shared" ref="F21" si="4">SUM(F16:F20)</f>
         <v>1153092</v>
       </c>
-      <c r="G21" s="129">
+      <c r="G21" s="125">
         <f t="shared" ref="G21" si="5">SUM(G16:G20)</f>
         <v>6250</v>
       </c>
-      <c r="H21" s="129">
+      <c r="H21" s="125">
         <f t="shared" ref="H21" si="6">SUM(H16:H20)</f>
         <v>45100</v>
       </c>
-      <c r="I21" s="129">
+      <c r="I21" s="125">
         <f t="shared" ref="I21" si="7">SUM(I16:I20)</f>
         <v>51350</v>
       </c>
-      <c r="J21" s="129">
+      <c r="J21" s="125">
         <f t="shared" ref="J21:L21" si="8">SUM(J16:J20)</f>
         <v>1204442</v>
       </c>
-      <c r="K21" s="128"/>
-      <c r="L21" s="129">
+      <c r="K21" s="124"/>
+      <c r="L21" s="125">
         <f t="shared" si="8"/>
         <v>1293432</v>
       </c>
-      <c r="P21" s="130"/>
-      <c r="W21" s="116">
+      <c r="P21" s="126"/>
+      <c r="W21" s="112">
         <v>5838</v>
       </c>
     </row>
-    <row r="22" spans="1:24" ht="20.100000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="117"/>
-      <c r="B22" s="118" t="s">
+    <row r="22" spans="1:24" ht="20.100000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="113"/>
+      <c r="B22" s="114" t="s">
         <v>89</v>
       </c>
       <c r="F22" s="17"/>
@@ -6052,55 +6034,55 @@
       <c r="H22" s="17"/>
       <c r="I22" s="17"/>
       <c r="J22" s="17"/>
-      <c r="K22" s="72"/>
-      <c r="L22" s="119"/>
-    </row>
-    <row r="23" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="123">
+      <c r="K22" s="70"/>
+      <c r="L22" s="115"/>
+    </row>
+    <row r="23" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="119">
         <v>11</v>
       </c>
-      <c r="B23" s="133">
+      <c r="B23" s="129">
         <v>156876</v>
       </c>
-      <c r="C23" s="132">
+      <c r="C23" s="128">
         <v>6.8500000000000005E-2</v>
       </c>
-      <c r="D23" s="135" t="s">
-        <v>245</v>
-      </c>
-      <c r="E23" s="135" t="s">
-        <v>250</v>
-      </c>
-      <c r="F23" s="136">
+      <c r="D23" s="131" t="s">
+        <v>244</v>
+      </c>
+      <c r="E23" s="131" t="s">
+        <v>249</v>
+      </c>
+      <c r="F23" s="132">
         <v>4100</v>
       </c>
-      <c r="G23" s="136">
+      <c r="G23" s="132">
         <v>0</v>
       </c>
-      <c r="H23" s="136">
+      <c r="H23" s="132">
         <v>27</v>
       </c>
-      <c r="I23" s="124">
+      <c r="I23" s="120">
         <f>SUM(G23:H23)</f>
         <v>27</v>
       </c>
-      <c r="J23" s="124">
+      <c r="J23" s="120">
         <f>F23+I23</f>
         <v>4127</v>
       </c>
-      <c r="K23" s="135" t="s">
-        <v>251</v>
-      </c>
-      <c r="L23" s="137">
+      <c r="K23" s="131" t="s">
+        <v>250</v>
+      </c>
+      <c r="L23" s="133">
         <v>4388</v>
       </c>
     </row>
-    <row r="24" spans="1:24" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="126"/>
-      <c r="B24" s="127"/>
-      <c r="C24" s="128"/>
-      <c r="D24" s="128"/>
-      <c r="E24" s="128"/>
+    <row r="24" spans="1:24" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="122"/>
+      <c r="B24" s="123"/>
+      <c r="C24" s="124"/>
+      <c r="D24" s="124"/>
+      <c r="E24" s="124"/>
       <c r="F24" s="21">
         <f>SUM(F23:F23)</f>
         <v>4100</v>
@@ -6121,27 +6103,27 @@
         <f>SUM(J23:J23)</f>
         <v>4127</v>
       </c>
-      <c r="K24" s="128"/>
+      <c r="K24" s="124"/>
       <c r="L24" s="21">
         <f>SUM(L23:L23)</f>
         <v>4388</v>
       </c>
-      <c r="S24" s="116" t="e">
+      <c r="S24" s="112" t="e">
         <f>263-#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="T24" s="116" t="e">
+      <c r="T24" s="112" t="e">
         <f>28-#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="X24" s="116" t="e">
+      <c r="X24" s="112" t="e">
         <f>#REF!/90%</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="25" spans="1:24" ht="20.100000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="117"/>
-      <c r="B25" s="118" t="s">
+    <row r="25" spans="1:24" ht="20.100000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="113"/>
+      <c r="B25" s="114" t="s">
         <v>90</v>
       </c>
       <c r="F25" s="17"/>
@@ -6149,200 +6131,200 @@
       <c r="H25" s="17"/>
       <c r="I25" s="17"/>
       <c r="J25" s="17"/>
-      <c r="K25" s="72"/>
-      <c r="L25" s="119"/>
-      <c r="P25" s="130"/>
-    </row>
-    <row r="26" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="120">
+      <c r="K25" s="70"/>
+      <c r="L25" s="115"/>
+      <c r="P25" s="126"/>
+    </row>
+    <row r="26" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="116">
         <v>12</v>
       </c>
-      <c r="B26" s="133" t="s">
-        <v>228</v>
-      </c>
-      <c r="C26" s="131">
+      <c r="B26" s="129" t="s">
+        <v>227</v>
+      </c>
+      <c r="C26" s="127">
         <v>0.06</v>
       </c>
-      <c r="D26" s="123" t="s">
+      <c r="D26" s="119" t="s">
         <v>86</v>
       </c>
-      <c r="E26" s="123" t="s">
-        <v>181</v>
-      </c>
-      <c r="F26" s="124">
+      <c r="E26" s="119" t="s">
+        <v>180</v>
+      </c>
+      <c r="F26" s="120">
         <v>85162</v>
       </c>
-      <c r="G26" s="124">
+      <c r="G26" s="120">
         <v>0</v>
       </c>
-      <c r="H26" s="124">
+      <c r="H26" s="120">
         <f>1548-157</f>
         <v>1391</v>
       </c>
-      <c r="I26" s="124">
+      <c r="I26" s="120">
         <f t="shared" ref="I26:I29" si="9">SUM(G26:H26)</f>
         <v>1391</v>
       </c>
-      <c r="J26" s="124">
+      <c r="J26" s="120">
         <f>F26+I26</f>
         <v>86553</v>
       </c>
-      <c r="K26" s="123" t="s">
-        <v>227</v>
-      </c>
-      <c r="L26" s="125">
+      <c r="K26" s="119" t="s">
+        <v>226</v>
+      </c>
+      <c r="L26" s="121">
         <v>90388</v>
       </c>
     </row>
-    <row r="27" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="120">
+    <row r="27" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="116">
         <v>13</v>
       </c>
-      <c r="B27" s="133" t="s">
-        <v>241</v>
-      </c>
-      <c r="C27" s="132">
+      <c r="B27" s="129" t="s">
+        <v>240</v>
+      </c>
+      <c r="C27" s="128">
         <v>6.3500000000000001E-2</v>
       </c>
-      <c r="D27" s="123" t="s">
+      <c r="D27" s="119" t="s">
         <v>86</v>
       </c>
-      <c r="E27" s="123" t="s">
-        <v>183</v>
-      </c>
-      <c r="F27" s="124">
+      <c r="E27" s="119" t="s">
+        <v>182</v>
+      </c>
+      <c r="F27" s="120">
         <v>132988</v>
       </c>
-      <c r="G27" s="124">
+      <c r="G27" s="120">
         <v>0</v>
       </c>
-      <c r="H27" s="124">
+      <c r="H27" s="120">
         <f>5481-550</f>
         <v>4931</v>
       </c>
-      <c r="I27" s="124">
+      <c r="I27" s="120">
         <f t="shared" si="9"/>
         <v>4931</v>
       </c>
-      <c r="J27" s="124">
+      <c r="J27" s="120">
         <f>F27+I27</f>
         <v>137919</v>
       </c>
-      <c r="K27" s="123" t="s">
-        <v>231</v>
-      </c>
-      <c r="L27" s="125">
+      <c r="K27" s="119" t="s">
+        <v>230</v>
+      </c>
+      <c r="L27" s="121">
         <v>141433</v>
       </c>
     </row>
-    <row r="28" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="134">
+    <row r="28" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="130">
         <v>14</v>
       </c>
-      <c r="B28" s="133" t="s">
-        <v>230</v>
-      </c>
-      <c r="C28" s="132">
+      <c r="B28" s="129" t="s">
+        <v>229</v>
+      </c>
+      <c r="C28" s="128">
         <v>5.8500000000000003E-2</v>
       </c>
-      <c r="D28" s="123" t="s">
+      <c r="D28" s="119" t="s">
         <v>86</v>
       </c>
-      <c r="E28" s="123" t="s">
-        <v>182</v>
-      </c>
-      <c r="F28" s="124">
+      <c r="E28" s="119" t="s">
+        <v>181</v>
+      </c>
+      <c r="F28" s="120">
         <v>45393</v>
       </c>
-      <c r="G28" s="124">
+      <c r="G28" s="120">
         <v>0</v>
       </c>
-      <c r="H28" s="124">
+      <c r="H28" s="120">
         <f>533-50</f>
         <v>483</v>
       </c>
-      <c r="I28" s="124">
+      <c r="I28" s="120">
         <f t="shared" si="9"/>
         <v>483</v>
       </c>
-      <c r="J28" s="124">
+      <c r="J28" s="120">
         <f>F28+I28</f>
         <v>45876</v>
       </c>
-      <c r="K28" s="123" t="s">
-        <v>229</v>
-      </c>
-      <c r="L28" s="125">
+      <c r="K28" s="119" t="s">
+        <v>228</v>
+      </c>
+      <c r="L28" s="121">
         <v>48107</v>
       </c>
-      <c r="P28" s="116">
+      <c r="P28" s="112">
         <f>42640</f>
         <v>42640</v>
       </c>
-      <c r="Q28" s="116">
+      <c r="Q28" s="112">
         <f>43183</f>
         <v>43183</v>
       </c>
-      <c r="R28" s="116">
+      <c r="R28" s="112">
         <f>Q28-P28</f>
         <v>543</v>
       </c>
-      <c r="S28" s="116">
+      <c r="S28" s="112">
         <f>ROUND(R28/90%,0)</f>
         <v>603</v>
       </c>
-      <c r="T28" s="116">
+      <c r="T28" s="112">
         <f>S28-R28</f>
         <v>60</v>
       </c>
     </row>
-    <row r="29" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="134">
+    <row r="29" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="130">
         <v>15</v>
       </c>
-      <c r="B29" s="133">
+      <c r="B29" s="129">
         <v>101043031007357</v>
       </c>
-      <c r="C29" s="138">
+      <c r="C29" s="134">
         <v>6.25E-2</v>
       </c>
-      <c r="D29" s="123" t="s">
+      <c r="D29" s="119" t="s">
         <v>86</v>
       </c>
-      <c r="E29" s="135" t="s">
-        <v>242</v>
-      </c>
-      <c r="F29" s="136">
+      <c r="E29" s="131" t="s">
+        <v>241</v>
+      </c>
+      <c r="F29" s="132">
         <v>126000</v>
       </c>
-      <c r="G29" s="124">
+      <c r="G29" s="120">
         <v>0</v>
       </c>
-      <c r="H29" s="136">
+      <c r="H29" s="132">
         <f>1701-171</f>
         <v>1530</v>
       </c>
-      <c r="I29" s="124">
+      <c r="I29" s="120">
         <f t="shared" si="9"/>
         <v>1530</v>
       </c>
-      <c r="J29" s="124">
+      <c r="J29" s="120">
         <f>F29+I29</f>
         <v>127530</v>
       </c>
-      <c r="K29" s="135" t="s">
-        <v>243</v>
-      </c>
-      <c r="L29" s="137">
+      <c r="K29" s="131" t="s">
+        <v>242</v>
+      </c>
+      <c r="L29" s="133">
         <v>133875</v>
       </c>
     </row>
-    <row r="30" spans="1:24" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="126"/>
-      <c r="B30" s="127"/>
-      <c r="C30" s="128"/>
-      <c r="D30" s="128"/>
-      <c r="E30" s="128"/>
+    <row r="30" spans="1:24" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="122"/>
+      <c r="B30" s="123"/>
+      <c r="C30" s="124"/>
+      <c r="D30" s="124"/>
+      <c r="E30" s="124"/>
       <c r="F30" s="21">
         <f t="shared" ref="F30:L30" si="10">SUM(F26:F29)</f>
         <v>389543</v>
@@ -6363,24 +6345,24 @@
         <f t="shared" si="10"/>
         <v>397878</v>
       </c>
-      <c r="K30" s="128"/>
+      <c r="K30" s="124"/>
       <c r="L30" s="21">
         <f t="shared" si="10"/>
         <v>413803</v>
       </c>
-      <c r="P30" s="130"/>
-      <c r="S30" s="116">
+      <c r="P30" s="126"/>
+      <c r="S30" s="112">
         <f>2907-S28</f>
         <v>2304</v>
       </c>
-      <c r="T30" s="116">
+      <c r="T30" s="112">
         <f>290-T28</f>
         <v>230</v>
       </c>
     </row>
-    <row r="31" spans="1:24" ht="20.100000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="117"/>
-      <c r="B31" s="118" t="s">
+    <row r="31" spans="1:24" ht="20.100000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="113"/>
+      <c r="B31" s="114" t="s">
         <v>91</v>
       </c>
       <c r="F31" s="17"/>
@@ -6388,195 +6370,195 @@
       <c r="H31" s="17"/>
       <c r="I31" s="17"/>
       <c r="J31" s="17"/>
-      <c r="K31" s="72"/>
-      <c r="L31" s="119"/>
-    </row>
-    <row r="32" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="123">
+      <c r="K31" s="70"/>
+      <c r="L31" s="115"/>
+    </row>
+    <row r="32" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="119">
         <v>16</v>
       </c>
-      <c r="B32" s="121" t="s">
-        <v>236</v>
-      </c>
-      <c r="C32" s="132">
+      <c r="B32" s="117" t="s">
+        <v>235</v>
+      </c>
+      <c r="C32" s="128">
         <v>5.5800000000000002E-2</v>
       </c>
-      <c r="D32" s="123" t="s">
+      <c r="D32" s="119" t="s">
         <v>86</v>
       </c>
-      <c r="E32" s="123" t="s">
-        <v>175</v>
-      </c>
-      <c r="F32" s="124">
+      <c r="E32" s="119" t="s">
+        <v>174</v>
+      </c>
+      <c r="F32" s="120">
         <v>113321</v>
       </c>
-      <c r="G32" s="124">
+      <c r="G32" s="120">
         <v>0</v>
       </c>
-      <c r="H32" s="124">
+      <c r="H32" s="120">
         <f>55-7</f>
         <v>48</v>
       </c>
-      <c r="I32" s="124">
+      <c r="I32" s="120">
         <f>SUM(G32:H32)</f>
         <v>48</v>
       </c>
-      <c r="J32" s="124">
+      <c r="J32" s="120">
         <f>F32+I32</f>
         <v>113369</v>
       </c>
-      <c r="K32" s="123" t="s">
-        <v>237</v>
-      </c>
-      <c r="L32" s="125">
+      <c r="K32" s="119" t="s">
+        <v>236</v>
+      </c>
+      <c r="L32" s="121">
         <v>120097</v>
       </c>
-      <c r="P32" s="116">
+      <c r="P32" s="112">
         <v>106456</v>
       </c>
-      <c r="Q32" s="116">
+      <c r="Q32" s="112">
         <v>106510</v>
       </c>
-      <c r="R32" s="116">
+      <c r="R32" s="112">
         <f>Q32-P32</f>
         <v>54</v>
       </c>
-      <c r="S32" s="116">
+      <c r="S32" s="112">
         <f>ROUND(R32/90%,0)</f>
         <v>60</v>
       </c>
-      <c r="T32" s="116">
+      <c r="T32" s="112">
         <f>S32-R32</f>
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="123">
+    <row r="33" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="119">
         <v>17</v>
       </c>
-      <c r="B33" s="133">
+      <c r="B33" s="129">
         <v>101043021004998</v>
       </c>
-      <c r="C33" s="132">
+      <c r="C33" s="128">
         <v>6.25E-2</v>
       </c>
-      <c r="D33" s="123" t="s">
+      <c r="D33" s="119" t="s">
         <v>86</v>
       </c>
-      <c r="E33" s="135" t="s">
-        <v>239</v>
-      </c>
-      <c r="F33" s="136">
+      <c r="E33" s="131" t="s">
+        <v>238</v>
+      </c>
+      <c r="F33" s="132">
         <v>25000</v>
       </c>
-      <c r="G33" s="124">
+      <c r="G33" s="120">
         <v>0</v>
       </c>
-      <c r="H33" s="136">
+      <c r="H33" s="132">
         <f>842-87</f>
         <v>755</v>
       </c>
-      <c r="I33" s="124">
+      <c r="I33" s="120">
         <f t="shared" ref="I33:I35" si="11">SUM(G33:H33)</f>
         <v>755</v>
       </c>
-      <c r="J33" s="124">
+      <c r="J33" s="120">
         <f>F33+I33</f>
         <v>25755</v>
       </c>
-      <c r="K33" s="135" t="s">
-        <v>240</v>
-      </c>
-      <c r="L33" s="137">
+      <c r="K33" s="131" t="s">
+        <v>239</v>
+      </c>
+      <c r="L33" s="133">
         <v>26563</v>
       </c>
     </row>
-    <row r="34" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="123">
+    <row r="34" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="119">
         <v>18</v>
       </c>
-      <c r="B34" s="133">
+      <c r="B34" s="129">
         <v>156982</v>
       </c>
-      <c r="C34" s="132">
+      <c r="C34" s="128">
         <v>6.8500000000000005E-2</v>
       </c>
-      <c r="D34" s="123" t="s">
-        <v>245</v>
-      </c>
-      <c r="E34" s="135" t="s">
-        <v>248</v>
-      </c>
-      <c r="F34" s="136">
+      <c r="D34" s="119" t="s">
+        <v>244</v>
+      </c>
+      <c r="E34" s="131" t="s">
+        <v>247</v>
+      </c>
+      <c r="F34" s="132">
         <v>130000</v>
       </c>
-      <c r="G34" s="136">
+      <c r="G34" s="132">
         <v>0</v>
       </c>
-      <c r="H34" s="136">
+      <c r="H34" s="132">
         <v>220</v>
       </c>
-      <c r="I34" s="124">
+      <c r="I34" s="120">
         <f t="shared" si="11"/>
         <v>220</v>
       </c>
-      <c r="J34" s="124">
+      <c r="J34" s="120">
         <f>F34+I34</f>
         <v>130220</v>
       </c>
-      <c r="K34" s="135" t="s">
+      <c r="K34" s="131" t="s">
+        <v>248</v>
+      </c>
+      <c r="L34" s="133">
+        <v>139136</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="119">
+        <v>19</v>
+      </c>
+      <c r="B35" s="129">
+        <v>156877</v>
+      </c>
+      <c r="C35" s="128">
+        <v>6.8500000000000005E-2</v>
+      </c>
+      <c r="D35" s="119" t="s">
+        <v>244</v>
+      </c>
+      <c r="E35" s="131" t="s">
         <v>249</v>
       </c>
-      <c r="L34" s="137">
-        <v>139136</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="123">
-        <v>19</v>
-      </c>
-      <c r="B35" s="133">
-        <v>156877</v>
-      </c>
-      <c r="C35" s="132">
-        <v>6.8500000000000005E-2</v>
-      </c>
-      <c r="D35" s="123" t="s">
-        <v>245</v>
-      </c>
-      <c r="E35" s="135" t="s">
-        <v>250</v>
-      </c>
-      <c r="F35" s="136">
+      <c r="F35" s="132">
         <v>120000</v>
       </c>
-      <c r="G35" s="136">
+      <c r="G35" s="132">
         <v>0</v>
       </c>
-      <c r="H35" s="136">
+      <c r="H35" s="132">
         <v>788</v>
       </c>
-      <c r="I35" s="124">
+      <c r="I35" s="120">
         <f t="shared" si="11"/>
         <v>788</v>
       </c>
-      <c r="J35" s="124">
+      <c r="J35" s="120">
         <f>F35+I35</f>
         <v>120788</v>
       </c>
-      <c r="K35" s="135" t="s">
-        <v>251</v>
-      </c>
-      <c r="L35" s="137">
+      <c r="K35" s="131" t="s">
+        <v>250</v>
+      </c>
+      <c r="L35" s="133">
         <v>128434</v>
       </c>
     </row>
-    <row r="36" spans="1:20" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="139"/>
-      <c r="B36" s="139"/>
-      <c r="C36" s="140"/>
-      <c r="D36" s="140"/>
-      <c r="E36" s="128"/>
+    <row r="36" spans="1:20" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="135"/>
+      <c r="B36" s="135"/>
+      <c r="C36" s="136"/>
+      <c r="D36" s="136"/>
+      <c r="E36" s="124"/>
       <c r="F36" s="21">
         <f>SUM(F32:F35)</f>
         <v>388321</v>
@@ -6597,25 +6579,25 @@
         <f t="shared" si="12"/>
         <v>390132</v>
       </c>
-      <c r="K36" s="141"/>
+      <c r="K36" s="137"/>
       <c r="L36" s="21">
         <f t="shared" si="12"/>
         <v>414230</v>
       </c>
-      <c r="P36" s="130"/>
-      <c r="S36" s="116">
+      <c r="P36" s="126"/>
+      <c r="S36" s="112">
         <f>7171-S32</f>
         <v>7111</v>
       </c>
-      <c r="T36" s="116">
+      <c r="T36" s="112">
         <f>719-T32</f>
         <v>713</v>
       </c>
     </row>
-    <row r="37" spans="1:20" ht="20.100000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="118"/>
-      <c r="B37" s="118" t="s">
-        <v>174</v>
+    <row r="37" spans="1:20" ht="20.100000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="114"/>
+      <c r="B37" s="114" t="s">
+        <v>173</v>
       </c>
       <c r="F37" s="20"/>
       <c r="G37" s="20"/>
@@ -6623,57 +6605,57 @@
       <c r="I37" s="20"/>
       <c r="J37" s="20"/>
       <c r="K37" s="40"/>
-      <c r="L37" s="142"/>
-      <c r="P37" s="130"/>
-    </row>
-    <row r="38" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="120">
+      <c r="L37" s="138"/>
+      <c r="P37" s="126"/>
+    </row>
+    <row r="38" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="116">
         <v>20</v>
       </c>
-      <c r="B38" s="133" t="s">
-        <v>234</v>
-      </c>
-      <c r="C38" s="122">
+      <c r="B38" s="129" t="s">
+        <v>233</v>
+      </c>
+      <c r="C38" s="118">
         <v>6.25E-2</v>
       </c>
-      <c r="D38" s="123" t="s">
+      <c r="D38" s="119" t="s">
         <v>86</v>
       </c>
-      <c r="E38" s="123" t="s">
-        <v>177</v>
-      </c>
-      <c r="F38" s="124">
+      <c r="E38" s="119" t="s">
+        <v>176</v>
+      </c>
+      <c r="F38" s="120">
         <v>10645</v>
       </c>
-      <c r="G38" s="124">
+      <c r="G38" s="120">
         <v>0</v>
       </c>
-      <c r="H38" s="124">
+      <c r="H38" s="120">
         <f>258-20</f>
         <v>238</v>
       </c>
-      <c r="I38" s="124">
+      <c r="I38" s="120">
         <f>SUM(G38:H38)</f>
         <v>238</v>
       </c>
-      <c r="J38" s="124">
+      <c r="J38" s="120">
         <f>F38+I38</f>
         <v>10883</v>
       </c>
-      <c r="K38" s="123" t="s">
-        <v>235</v>
-      </c>
-      <c r="L38" s="125">
+      <c r="K38" s="119" t="s">
+        <v>234</v>
+      </c>
+      <c r="L38" s="121">
         <v>11310</v>
       </c>
-      <c r="P38" s="130"/>
-    </row>
-    <row r="39" spans="1:20" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="126"/>
-      <c r="B39" s="127"/>
-      <c r="C39" s="128"/>
-      <c r="D39" s="128"/>
-      <c r="E39" s="128"/>
+      <c r="P38" s="126"/>
+    </row>
+    <row r="39" spans="1:20" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="122"/>
+      <c r="B39" s="123"/>
+      <c r="C39" s="124"/>
+      <c r="D39" s="124"/>
+      <c r="E39" s="124"/>
       <c r="F39" s="21">
         <f>SUM(F38)</f>
         <v>10645</v>
@@ -6694,32 +6676,32 @@
         <f t="shared" si="13"/>
         <v>10883</v>
       </c>
-      <c r="K39" s="141"/>
-      <c r="L39" s="129">
+      <c r="K39" s="137"/>
+      <c r="L39" s="125">
         <f t="shared" si="13"/>
         <v>11310</v>
       </c>
-      <c r="P39" s="130"/>
-    </row>
-    <row r="40" spans="1:20" ht="9.9499999999999993" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="117"/>
+      <c r="P39" s="126"/>
+    </row>
+    <row r="40" spans="1:20" ht="9.9" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="113"/>
       <c r="F40" s="17"/>
       <c r="G40" s="17"/>
       <c r="H40" s="17"/>
       <c r="I40" s="17"/>
       <c r="J40" s="17"/>
       <c r="K40" s="40"/>
-      <c r="L40" s="144"/>
-      <c r="P40" s="130"/>
-    </row>
-    <row r="41" spans="1:20" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="126"/>
-      <c r="B41" s="145" t="s">
+      <c r="L40" s="140"/>
+      <c r="P40" s="126"/>
+    </row>
+    <row r="41" spans="1:20" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="122"/>
+      <c r="B41" s="141" t="s">
         <v>92</v>
       </c>
-      <c r="C41" s="128"/>
-      <c r="D41" s="128"/>
-      <c r="E41" s="128"/>
+      <c r="C41" s="124"/>
+      <c r="D41" s="124"/>
+      <c r="E41" s="124"/>
       <c r="F41" s="21">
         <f>SUM(F8,F14,F21,F24,F30,F36,F39)</f>
         <v>2353314</v>
@@ -6740,25 +6722,25 @@
         <f>SUM(J8,J14,J21,J24,J30,J36,J39)</f>
         <v>2428003</v>
       </c>
-      <c r="K41" s="141"/>
-      <c r="L41" s="129">
+      <c r="K41" s="137"/>
+      <c r="L41" s="125">
         <f>SUM(L8,L14,L21,L24,L30,L36,L39)</f>
         <v>2570950</v>
       </c>
     </row>
-    <row r="42" spans="1:20" ht="9.9499999999999993" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="146"/>
-      <c r="B42" s="147"/>
-      <c r="C42" s="148"/>
-      <c r="D42" s="148"/>
-      <c r="E42" s="148"/>
-      <c r="F42" s="149"/>
-      <c r="G42" s="149"/>
-      <c r="H42" s="149"/>
-      <c r="I42" s="149"/>
-      <c r="J42" s="149"/>
-      <c r="K42" s="150"/>
-      <c r="L42" s="151"/>
+    <row r="42" spans="1:20" ht="9.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="142"/>
+      <c r="B42" s="143"/>
+      <c r="C42" s="144"/>
+      <c r="D42" s="144"/>
+      <c r="E42" s="144"/>
+      <c r="F42" s="145"/>
+      <c r="G42" s="145"/>
+      <c r="H42" s="145"/>
+      <c r="I42" s="145"/>
+      <c r="J42" s="145"/>
+      <c r="K42" s="146"/>
+      <c r="L42" s="147"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6767,29 +6749,29 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="65" fitToHeight="0" orientation="landscape" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="65" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J45"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.28515625" style="26" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" style="26" customWidth="1"/>
-    <col min="3" max="3" width="47.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="5" customWidth="1"/>
-    <col min="5" max="5" width="21.7109375" style="5" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" style="26" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" style="26" customWidth="1"/>
+    <col min="3" max="3" width="47.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.6640625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="21.6640625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="186" t="s">
+    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.3">
+      <c r="A1" s="188" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="186"/>
-      <c r="C1" s="186"/>
-      <c r="D1" s="186"/>
+      <c r="B1" s="188"/>
+      <c r="C1" s="188"/>
+      <c r="D1" s="188"/>
       <c r="E1" s="60"/>
       <c r="F1" s="60"/>
       <c r="G1" s="60"/>
@@ -6797,13 +6779,13 @@
       <c r="I1" s="60"/>
       <c r="J1" s="60"/>
     </row>
-    <row r="2" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="187" t="s">
+    <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.3">
+      <c r="A2" s="189" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="187"/>
-      <c r="C2" s="187"/>
-      <c r="D2" s="187"/>
+      <c r="B2" s="189"/>
+      <c r="C2" s="189"/>
+      <c r="D2" s="189"/>
       <c r="E2" s="60"/>
       <c r="F2" s="60"/>
       <c r="G2" s="60"/>
@@ -6811,135 +6793,135 @@
       <c r="I2" s="60"/>
       <c r="J2" s="60"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="189" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="191" t="s">
+        <v>107</v>
+      </c>
+      <c r="B3" s="191"/>
+      <c r="C3" s="191"/>
+      <c r="D3" s="191"/>
+    </row>
+    <row r="4" spans="1:10" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="190" t="s">
+        <v>198</v>
+      </c>
+      <c r="B5" s="190"/>
+      <c r="C5" s="190"/>
+      <c r="D5" s="190"/>
+    </row>
+    <row r="6" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="149" t="s">
         <v>108</v>
       </c>
-      <c r="B3" s="189"/>
-      <c r="C3" s="189"/>
-      <c r="D3" s="189"/>
-    </row>
-    <row r="4" spans="1:10" ht="10.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="188" t="s">
-        <v>199</v>
-      </c>
-      <c r="B5" s="188"/>
-      <c r="C5" s="188"/>
-      <c r="D5" s="188"/>
-    </row>
-    <row r="6" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="156" t="s">
+      <c r="B6" s="150" t="s">
+        <v>164</v>
+      </c>
+      <c r="C6" s="149" t="s">
         <v>109</v>
       </c>
-      <c r="B6" s="157" t="s">
-        <v>165</v>
-      </c>
-      <c r="C6" s="156" t="s">
-        <v>110</v>
-      </c>
-      <c r="D6" s="157" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D6" s="150" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="61">
         <v>1</v>
       </c>
-      <c r="B7" s="155">
+      <c r="B7" s="148">
         <v>0</v>
       </c>
       <c r="C7" s="62" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D7" s="63">
         <v>17061</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="27">
         <v>2</v>
       </c>
-      <c r="B8" s="70">
+      <c r="B8" s="69">
         <v>102</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D8" s="30">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="27">
         <v>3</v>
       </c>
-      <c r="B9" s="70">
+      <c r="B9" s="69">
         <v>15250</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D9" s="30">
         <f>530+15720</f>
         <v>16250</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="27">
         <v>4</v>
       </c>
-      <c r="B10" s="70">
+      <c r="B10" s="69">
         <v>10000</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D10" s="30">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="50"/>
       <c r="B11" s="52">
         <f>SUM(B7:B10)</f>
         <v>25352</v>
       </c>
-      <c r="C11" s="160" t="s">
-        <v>375</v>
+      <c r="C11" s="153" t="s">
+        <v>372</v>
       </c>
       <c r="D11" s="52">
         <f>SUM(D7:D10)</f>
         <v>33311</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="188" t="s">
-        <v>200</v>
-      </c>
-      <c r="B13" s="188"/>
-      <c r="C13" s="188"/>
-      <c r="D13" s="188"/>
-    </row>
-    <row r="14" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="156" t="s">
-        <v>109</v>
-      </c>
-      <c r="B14" s="158" t="str">
+    <row r="12" spans="1:10" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="190" t="s">
+        <v>199</v>
+      </c>
+      <c r="B13" s="190"/>
+      <c r="C13" s="190"/>
+      <c r="D13" s="190"/>
+    </row>
+    <row r="14" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="149" t="s">
+        <v>108</v>
+      </c>
+      <c r="B14" s="151" t="str">
         <f>B6</f>
         <v>FY 2024-25</v>
       </c>
-      <c r="C14" s="156" t="s">
-        <v>112</v>
-      </c>
-      <c r="D14" s="158" t="str">
+      <c r="C14" s="149" t="s">
+        <v>111</v>
+      </c>
+      <c r="D14" s="151" t="str">
         <f>D6</f>
         <v>FY 2025-26</v>
       </c>
       <c r="E14"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="61">
         <v>1</v>
       </c>
@@ -6954,7 +6936,7 @@
       </c>
       <c r="E15"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="27">
         <v>2</v>
       </c>
@@ -6962,7 +6944,7 @@
         <v>4561</v>
       </c>
       <c r="C16" s="29" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D16" s="30">
         <f>Workings!D9</f>
@@ -6970,15 +6952,15 @@
       </c>
       <c r="E16"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="27">
         <v>3</v>
       </c>
-      <c r="B17" s="30">
-        <v>6600</v>
+      <c r="B17" s="30" t="s">
+        <v>375</v>
       </c>
       <c r="C17" s="29" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D17" s="30">
         <f>5000+8000</f>
@@ -6986,7 +6968,7 @@
       </c>
       <c r="E17"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="27">
         <v>4</v>
       </c>
@@ -6994,7 +6976,7 @@
         <v>4080</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D18" s="30">
         <f>4080*2</f>
@@ -7002,14 +6984,14 @@
       </c>
       <c r="E18"/>
     </row>
-    <row r="19" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="50"/>
       <c r="B19" s="52">
         <f>SUM(B15:B18)</f>
-        <v>18641</v>
-      </c>
-      <c r="C19" s="160" t="s">
-        <v>375</v>
+        <v>12041</v>
+      </c>
+      <c r="C19" s="153" t="s">
+        <v>372</v>
       </c>
       <c r="D19" s="52">
         <f>SUM(D15:D18)</f>
@@ -7017,48 +6999,39 @@
       </c>
       <c r="E19"/>
     </row>
-    <row r="20" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="1:5" s="74" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="192" t="s">
-        <v>116</v>
-      </c>
-      <c r="B21" s="192"/>
-      <c r="C21" s="192"/>
-      <c r="D21" s="192"/>
-      <c r="E21" s="5"/>
-    </row>
-    <row r="22" spans="1:5" s="74" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="69"/>
-      <c r="B22" s="69"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-    </row>
-    <row r="23" spans="1:5" ht="8.65" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="1:5" s="74" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="190" t="s">
-        <v>201</v>
-      </c>
-      <c r="B24" s="190"/>
-      <c r="C24" s="190"/>
-      <c r="D24" s="190"/>
-      <c r="E24" s="5"/>
-    </row>
-    <row r="25" spans="1:5" s="74" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="156" t="s">
+    <row r="20" spans="1:5" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="184" t="s">
+        <v>115</v>
+      </c>
+      <c r="B21" s="184"/>
+      <c r="C21" s="184"/>
+      <c r="D21" s="184"/>
+    </row>
+    <row r="23" spans="1:5" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="182" t="s">
+        <v>200</v>
+      </c>
+      <c r="B24" s="182"/>
+      <c r="C24" s="182"/>
+      <c r="D24" s="182"/>
+    </row>
+    <row r="25" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="149" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="156" t="s">
+      <c r="B25" s="149" t="s">
+        <v>117</v>
+      </c>
+      <c r="C25" s="149" t="s">
         <v>118</v>
       </c>
-      <c r="C25" s="156" t="s">
-        <v>119</v>
-      </c>
-      <c r="D25" s="159" t="s">
+      <c r="D25" s="152" t="s">
         <v>24</v>
       </c>
-      <c r="E25" s="5"/>
-    </row>
-    <row r="26" spans="1:5" s="74" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="61">
         <v>1</v>
       </c>
@@ -7066,14 +7039,13 @@
         <v>204</v>
       </c>
       <c r="C26" s="62" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D26" s="63">
         <v>5828</v>
       </c>
-      <c r="E26" s="5"/>
-    </row>
-    <row r="27" spans="1:5" s="74" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="27">
         <v>2</v>
       </c>
@@ -7081,14 +7053,13 @@
         <v>301</v>
       </c>
       <c r="C27" s="29" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D27" s="30">
         <v>14477</v>
       </c>
-      <c r="E27" s="5"/>
-    </row>
-    <row r="28" spans="1:5" s="74" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="27">
         <v>3</v>
       </c>
@@ -7096,14 +7067,13 @@
         <v>504</v>
       </c>
       <c r="C28" s="29" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D28" s="30">
         <v>11287</v>
       </c>
-      <c r="E28" s="5"/>
-    </row>
-    <row r="29" spans="1:5" s="74" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="27">
         <v>4</v>
       </c>
@@ -7111,91 +7081,78 @@
         <v>705</v>
       </c>
       <c r="C29" s="29" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D29" s="30">
         <v>12376</v>
       </c>
-      <c r="E29" s="5"/>
-    </row>
-    <row r="30" spans="1:5" s="74" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="191" t="s">
-        <v>375</v>
-      </c>
-      <c r="B30" s="191"/>
-      <c r="C30" s="191"/>
+    </row>
+    <row r="30" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="183" t="s">
+        <v>372</v>
+      </c>
+      <c r="B30" s="183"/>
+      <c r="C30" s="183"/>
       <c r="D30" s="52">
         <f>SUM(D26:D29)</f>
         <v>43968</v>
       </c>
-      <c r="E30" s="5"/>
-    </row>
-    <row r="31" spans="1:5" s="74" customFormat="1" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="69"/>
-      <c r="B31" s="69"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-    </row>
-    <row r="32" spans="1:5" s="74" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="69"/>
-      <c r="B32" s="69"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="5"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:5" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="59" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B33" s="28"/>
       <c r="E33"/>
     </row>
-    <row r="34" spans="1:5" ht="10.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" ht="10.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34"/>
       <c r="B34"/>
       <c r="E34"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="193" t="s">
-        <v>202</v>
-      </c>
-      <c r="B35" s="194"/>
-      <c r="C35" s="194"/>
-      <c r="D35" s="195"/>
-      <c r="E35" s="154"/>
-    </row>
-    <row r="36" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="156" t="s">
-        <v>109</v>
-      </c>
-      <c r="B36" s="158" t="s">
-        <v>165</v>
-      </c>
-      <c r="C36" s="156" t="s">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="185" t="s">
+        <v>201</v>
+      </c>
+      <c r="B35" s="186"/>
+      <c r="C35" s="186"/>
+      <c r="D35" s="187"/>
+      <c r="E35" s="68"/>
+    </row>
+    <row r="36" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="149" t="s">
+        <v>108</v>
+      </c>
+      <c r="B36" s="151" t="s">
+        <v>164</v>
+      </c>
+      <c r="C36" s="149" t="s">
+        <v>122</v>
+      </c>
+      <c r="D36" s="151" t="s">
+        <v>197</v>
+      </c>
+      <c r="E36" s="149" t="s">
         <v>123</v>
       </c>
-      <c r="D36" s="158" t="s">
-        <v>198</v>
-      </c>
-      <c r="E36" s="156" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="61">
         <v>1</v>
       </c>
-      <c r="B37" s="155">
+      <c r="B37" s="148">
         <v>2844</v>
       </c>
       <c r="C37" s="62" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D37" s="63">
         <v>0</v>
       </c>
       <c r="E37" s="62"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="27">
         <v>2</v>
       </c>
@@ -7203,17 +7160,17 @@
         <v>24477</v>
       </c>
       <c r="C38" s="29" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D38" s="30">
         <f>Workings!D33</f>
         <v>37113</v>
       </c>
       <c r="E38" s="29" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="27">
         <v>3</v>
       </c>
@@ -7221,17 +7178,17 @@
         <v>8463</v>
       </c>
       <c r="C39" s="29" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D39" s="30">
         <f>Workings!D27</f>
         <v>2269</v>
       </c>
       <c r="E39" s="29" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="27">
         <v>4</v>
       </c>
@@ -7239,17 +7196,17 @@
         <v>3952</v>
       </c>
       <c r="C40" s="29" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D40" s="30">
         <f>Workings!D21</f>
         <v>3373</v>
       </c>
       <c r="E40" s="29" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="27">
         <v>5</v>
       </c>
@@ -7257,17 +7214,17 @@
         <v>79958</v>
       </c>
       <c r="C41" s="29" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D41" s="30">
         <f>Workings!D15</f>
         <v>93949</v>
       </c>
       <c r="E41" s="29" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="27">
         <v>6</v>
       </c>
@@ -7275,17 +7232,17 @@
         <v>15251</v>
       </c>
       <c r="C42" s="29" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D42" s="30">
         <f>Workings!D45</f>
         <v>16741</v>
       </c>
       <c r="E42" s="29" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="27">
         <v>7</v>
       </c>
@@ -7293,31 +7250,31 @@
         <v>4098</v>
       </c>
       <c r="C43" s="29" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D43" s="30">
         <f>Workings!D39</f>
         <v>3498</v>
       </c>
       <c r="E43" s="29" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="50"/>
       <c r="B44" s="51">
         <f>SUM(B37:B43)</f>
         <v>139043</v>
       </c>
-      <c r="C44" s="160" t="s">
-        <v>375</v>
+      <c r="C44" s="153" t="s">
+        <v>372</v>
       </c>
       <c r="D44" s="52">
         <f>SUM(D37:D43)</f>
         <v>156943</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:5" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A24:D24"/>
@@ -7337,59 +7294,59 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B2:M24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="43.7109375" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="4.6640625" customWidth="1"/>
+    <col min="3" max="3" width="43.6640625" customWidth="1"/>
     <col min="4" max="4" width="14" style="2" customWidth="1"/>
-    <col min="6" max="6" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.6640625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B2" s="196" t="s">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B2" s="192" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="196"/>
-      <c r="D2" s="196"/>
-    </row>
-    <row r="3" spans="2:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="C2" s="192"/>
+      <c r="D2" s="192"/>
+    </row>
+    <row r="3" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="F3" s="66" t="s">
+        <v>208</v>
+      </c>
+      <c r="G3" s="66" t="s">
+        <v>138</v>
+      </c>
+      <c r="H3" s="66" t="s">
+        <v>117</v>
+      </c>
+      <c r="I3" s="66" t="s">
         <v>209</v>
       </c>
-      <c r="G3" s="66" t="s">
+      <c r="J3" s="67" t="s">
+        <v>135</v>
+      </c>
+      <c r="K3" s="67" t="s">
+        <v>136</v>
+      </c>
+      <c r="L3" s="66" t="s">
         <v>139</v>
       </c>
-      <c r="H3" s="66" t="s">
-        <v>118</v>
-      </c>
-      <c r="I3" s="66" t="s">
-        <v>210</v>
-      </c>
-      <c r="J3" s="67" t="s">
-        <v>136</v>
-      </c>
-      <c r="K3" s="67" t="s">
-        <v>137</v>
-      </c>
-      <c r="L3" s="66" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B4" s="197" t="s">
-        <v>203</v>
-      </c>
-      <c r="C4" s="197"/>
-      <c r="D4" s="197"/>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B4" s="193" t="s">
+        <v>202</v>
+      </c>
+      <c r="C4" s="193"/>
+      <c r="D4" s="193"/>
       <c r="F4" s="27">
         <v>1</v>
       </c>
@@ -7397,7 +7354,7 @@
         <v>46084</v>
       </c>
       <c r="H4" s="29" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I4" s="29">
         <v>948491</v>
@@ -7410,7 +7367,7 @@
       </c>
       <c r="L4" s="29"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
       <c r="D5" s="9" t="s">
         <v>24</v>
       </c>
@@ -7421,7 +7378,7 @@
         <v>46105</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I5" s="29">
         <v>948498</v>
@@ -7436,7 +7393,7 @@
         <v>46117</v>
       </c>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>25</v>
       </c>
@@ -7450,7 +7407,7 @@
         <v>46109</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I6" s="29">
         <v>948503</v>
@@ -7465,7 +7422,7 @@
         <v>46119</v>
       </c>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
       <c r="F7" s="27">
         <v>4</v>
       </c>
@@ -7473,7 +7430,7 @@
         <v>46109</v>
       </c>
       <c r="H7" s="29" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I7" s="29">
         <v>948501</v>
@@ -7488,12 +7445,12 @@
         <v>46116</v>
       </c>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D8" s="2">
         <f>K12</f>
@@ -7506,7 +7463,7 @@
         <v>46109</v>
       </c>
       <c r="H8" s="29" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I8" s="29">
         <v>948502</v>
@@ -7522,7 +7479,7 @@
       </c>
       <c r="M8" s="48"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
       <c r="E9" s="4"/>
       <c r="F9" s="27">
         <v>6</v>
@@ -7531,7 +7488,7 @@
         <v>46109</v>
       </c>
       <c r="H9" s="29" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I9" s="29">
         <v>948504</v>
@@ -7546,12 +7503,12 @@
         <v>46114</v>
       </c>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D10" s="2">
         <f>-J12</f>
@@ -7564,7 +7521,7 @@
         <v>46109</v>
       </c>
       <c r="H10" s="29" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I10" s="29">
         <v>948505</v>
@@ -7579,7 +7536,7 @@
         <v>46119</v>
       </c>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
       <c r="F11" s="27">
         <v>8</v>
       </c>
@@ -7587,7 +7544,7 @@
         <v>46110</v>
       </c>
       <c r="H11" s="29" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I11" s="29">
         <v>948500</v>
@@ -7602,7 +7559,7 @@
         <v>46132</v>
       </c>
     </row>
-    <row r="12" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="8" t="s">
         <v>26</v>
       </c>
@@ -7625,20 +7582,20 @@
       </c>
       <c r="L12" s="46"/>
     </row>
-    <row r="13" spans="2:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B14" s="197" t="s">
-        <v>208</v>
-      </c>
-      <c r="C14" s="197"/>
-      <c r="D14" s="197"/>
-    </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:13" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B14" s="193" t="s">
+        <v>207</v>
+      </c>
+      <c r="C14" s="193"/>
+      <c r="D14" s="193"/>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.3">
       <c r="D15" s="9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>25</v>
       </c>
@@ -7646,31 +7603,31 @@
         <v>12373.19</v>
       </c>
     </row>
-    <row r="18" spans="2:4" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:4" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D18" s="2">
         <f>K22</f>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C20" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D20" s="2">
         <f>-J22</f>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="8" t="s">
         <v>26</v>
       </c>
@@ -7680,7 +7637,7 @@
         <v>12373.19</v>
       </c>
     </row>
-    <row r="24" spans="2:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="2:4" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B2:D2"/>
@@ -7692,25 +7649,25 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:K47"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" style="65" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.7109375" style="2"/>
-    <col min="7" max="8" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.44140625" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" style="65" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" style="2"/>
+    <col min="7" max="8" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="25" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="24">
         <v>45723</v>
       </c>
@@ -7727,7 +7684,7 @@
       <c r="G2" s="24"/>
       <c r="H2" s="24"/>
       <c r="I2" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J2">
         <v>90</v>
@@ -7736,7 +7693,7 @@
         <v>17105</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="24">
         <v>45723</v>
       </c>
@@ -7752,7 +7709,7 @@
         <v>4561</v>
       </c>
       <c r="I3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J3">
         <v>24</v>
@@ -7762,7 +7719,7 @@
         <v>4561</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="24">
         <v>45748</v>
       </c>
@@ -7778,7 +7735,7 @@
         <v>12544</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="24">
         <f>B4</f>
         <v>45813</v>
@@ -7794,7 +7751,7 @@
         <v>17029</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="24">
         <f>B5</f>
         <v>45904</v>
@@ -7810,7 +7767,7 @@
         <v>17126</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="24">
         <f>B6</f>
         <v>45995</v>
@@ -7826,7 +7783,7 @@
         <v>17061</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="24"/>
       <c r="B8" s="24"/>
       <c r="C8" s="5">
@@ -7838,7 +7795,7 @@
         <v>63760</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="24">
         <f>B7</f>
         <v>46086</v>
@@ -7855,10 +7812,10 @@
         <v>4890</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="24"/>
       <c r="B10" s="24"/>
       <c r="C10" s="5">
@@ -7870,17 +7827,17 @@
         <v>68650</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="24"/>
       <c r="B11" s="24"/>
       <c r="C11" s="5"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="25" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="24">
         <v>45748</v>
       </c>
@@ -7895,7 +7852,7 @@
         <v>89069</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="24">
         <v>46023</v>
       </c>
@@ -7910,7 +7867,7 @@
         <v>124696</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="24">
         <v>46113</v>
       </c>
@@ -7926,10 +7883,10 @@
         <v>93949</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="24">
         <v>45748</v>
       </c>
@@ -7945,12 +7902,12 @@
         <v>119816</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="25" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="24">
         <v>45748</v>
       </c>
@@ -7965,7 +7922,7 @@
         <v>3980</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="24">
         <v>45976</v>
       </c>
@@ -7980,7 +7937,7 @@
         <v>5400</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="24">
         <v>46113</v>
       </c>
@@ -7996,10 +7953,10 @@
         <v>3373</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="24">
         <v>45748</v>
       </c>
@@ -8015,12 +7972,12 @@
         <v>6007</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="25" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="24">
         <v>45748</v>
       </c>
@@ -8035,7 +7992,7 @@
         <v>2263</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="24">
         <v>45959</v>
       </c>
@@ -8050,7 +8007,7 @@
         <v>14750</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="24">
         <v>46113</v>
       </c>
@@ -8066,10 +8023,10 @@
         <v>2269</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="24">
         <v>45748</v>
       </c>
@@ -8085,12 +8042,12 @@
         <v>14744</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="25" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="24">
         <v>45748</v>
       </c>
@@ -8105,7 +8062,7 @@
         <v>35347</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="24">
         <v>45926</v>
       </c>
@@ -8120,7 +8077,7 @@
         <v>76102</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="24">
         <v>46113</v>
       </c>
@@ -8136,10 +8093,10 @@
         <v>37113</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="24">
         <v>45748</v>
       </c>
@@ -8155,12 +8112,12 @@
         <v>74336</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="25" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="24">
         <v>45748</v>
       </c>
@@ -8175,7 +8132,7 @@
         <v>4128</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="24">
         <v>45976</v>
       </c>
@@ -8191,7 +8148,7 @@
         <v>5600</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="24">
         <v>46113</v>
       </c>
@@ -8207,12 +8164,12 @@
         <v>3498</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G39" s="65"/>
       <c r="H39" s="65"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="24">
         <v>45748</v>
       </c>
@@ -8228,12 +8185,12 @@
         <v>6230</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="25" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="24">
         <v>45748</v>
       </c>
@@ -8248,7 +8205,7 @@
         <v>16311</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="24">
         <v>46059</v>
       </c>
@@ -8263,7 +8220,7 @@
         <v>19648</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="24">
         <v>46113</v>
       </c>
@@ -8279,10 +8236,10 @@
         <v>16741</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="24">
         <v>46059</v>
       </c>
@@ -8298,7 +8255,7 @@
         <v>2907</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="24">
         <v>45748</v>
       </c>
@@ -8320,854 +8277,851 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:K36"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="77.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="77.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="6" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.33203125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="6" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="22" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="29" max="32" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="32" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="197" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="193" t="s">
+        <v>263</v>
+      </c>
+      <c r="B1" s="194"/>
+      <c r="C1" s="194"/>
+      <c r="D1" s="194"/>
+      <c r="E1" s="194"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="72" t="s">
         <v>264</v>
       </c>
-      <c r="B1" s="198"/>
-      <c r="C1" s="198"/>
-      <c r="D1" s="198"/>
-      <c r="E1" s="198"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="75" t="s">
+      <c r="B2" s="72" t="s">
+        <v>138</v>
+      </c>
+      <c r="C2" s="72" t="s">
         <v>265</v>
       </c>
-      <c r="B2" s="75" t="s">
-        <v>139</v>
-      </c>
-      <c r="C2" s="75" t="s">
+      <c r="D2" s="72" t="s">
+        <v>136</v>
+      </c>
+      <c r="E2" s="72" t="s">
+        <v>356</v>
+      </c>
+      <c r="F2" s="72" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>266</v>
       </c>
-      <c r="D2" s="75" t="s">
-        <v>137</v>
-      </c>
-      <c r="E2" s="75" t="s">
-        <v>357</v>
-      </c>
-      <c r="F2" s="75" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>267</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>268</v>
       </c>
-      <c r="C3" t="s">
-        <v>269</v>
-      </c>
-      <c r="D3" s="77">
+      <c r="D3" s="74">
         <v>2351</v>
       </c>
       <c r="E3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F3" t="s">
         <v>86</v>
       </c>
-      <c r="H3" s="78" t="s">
-        <v>361</v>
-      </c>
-      <c r="I3" s="78" t="s">
+      <c r="H3" s="75" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I3" s="75" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>269</v>
+      </c>
+      <c r="B4" t="s">
         <v>270</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>271</v>
       </c>
-      <c r="C4" t="s">
-        <v>272</v>
-      </c>
-      <c r="D4" s="77">
+      <c r="D4" s="74">
         <v>20233</v>
       </c>
       <c r="E4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F4" t="s">
-        <v>245</v>
-      </c>
-      <c r="H4" s="78" t="s">
-        <v>358</v>
+        <v>244</v>
+      </c>
+      <c r="H4" s="75" t="s">
+        <v>357</v>
       </c>
       <c r="I4" t="s">
         <v>86</v>
       </c>
       <c r="J4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K4" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B5" t="s">
         <v>273</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>274</v>
       </c>
-      <c r="C5" t="s">
-        <v>275</v>
-      </c>
-      <c r="D5" s="77">
+      <c r="D5" s="74">
         <v>3114</v>
       </c>
       <c r="E5" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F5" t="s">
         <v>86</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="I5" s="79">
+        <v>354</v>
+      </c>
+      <c r="I5">
         <v>546</v>
       </c>
-      <c r="J5" s="79">
+      <c r="J5">
         <v>27</v>
       </c>
-      <c r="K5" s="79">
+      <c r="K5">
         <v>573</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>275</v>
+      </c>
+      <c r="B6" t="s">
         <v>276</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>277</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" s="74">
+        <v>5180</v>
+      </c>
+      <c r="E6" t="s">
+        <v>352</v>
+      </c>
+      <c r="F6" t="s">
+        <v>244</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="I6">
+        <v>8465</v>
+      </c>
+      <c r="J6">
+        <v>1008</v>
+      </c>
+      <c r="K6">
+        <v>9473</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>278</v>
       </c>
-      <c r="D6" s="77">
-        <v>5180</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="B7" t="s">
+        <v>279</v>
+      </c>
+      <c r="C7" t="s">
+        <v>280</v>
+      </c>
+      <c r="D7" s="73">
+        <v>433</v>
+      </c>
+      <c r="E7" t="s">
         <v>353</v>
-      </c>
-      <c r="F6" t="s">
-        <v>245</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="I6" s="79">
-        <v>8465</v>
-      </c>
-      <c r="J6" s="79">
-        <v>1008</v>
-      </c>
-      <c r="K6" s="79">
-        <v>9473</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>279</v>
-      </c>
-      <c r="B7" t="s">
-        <v>280</v>
-      </c>
-      <c r="C7" t="s">
-        <v>281</v>
-      </c>
-      <c r="D7" s="76">
-        <v>433</v>
-      </c>
-      <c r="E7" t="s">
-        <v>354</v>
       </c>
       <c r="F7" t="s">
         <v>86</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="I7" s="79">
+        <v>350</v>
+      </c>
+      <c r="I7">
         <v>15754</v>
       </c>
-      <c r="J7" s="79"/>
-      <c r="K7" s="79">
+      <c r="K7">
         <v>15754</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>281</v>
+      </c>
+      <c r="B8" t="s">
         <v>282</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>283</v>
       </c>
-      <c r="C8" t="s">
-        <v>284</v>
-      </c>
-      <c r="D8" s="77">
+      <c r="D8" s="74">
         <v>12053</v>
       </c>
       <c r="E8" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F8" t="s">
         <v>86</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="I8" s="79">
+        <v>349</v>
+      </c>
+      <c r="I8">
         <v>54439</v>
       </c>
-      <c r="J8" s="79">
+      <c r="J8">
         <v>20233</v>
       </c>
-      <c r="K8" s="79">
+      <c r="K8">
         <v>74672</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>284</v>
+      </c>
+      <c r="B9" t="s">
         <v>285</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>286</v>
       </c>
-      <c r="C9" t="s">
-        <v>287</v>
-      </c>
-      <c r="D9" s="77">
+      <c r="D9" s="74">
         <v>4035</v>
       </c>
       <c r="E9" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F9" t="s">
         <v>86</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="I9" s="79">
+        <v>355</v>
+      </c>
+      <c r="I9">
         <v>1282</v>
       </c>
-      <c r="J9" s="79"/>
-      <c r="K9" s="79">
+      <c r="K9">
         <v>1282</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>287</v>
+      </c>
+      <c r="B10" t="s">
+        <v>285</v>
+      </c>
+      <c r="C10" t="s">
         <v>288</v>
       </c>
-      <c r="B10" t="s">
-        <v>286</v>
-      </c>
-      <c r="C10" t="s">
-        <v>289</v>
-      </c>
-      <c r="D10" s="77">
+      <c r="D10" s="74">
         <v>4035</v>
       </c>
       <c r="E10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F10" t="s">
         <v>86</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="I10" s="79">
+        <v>353</v>
+      </c>
+      <c r="I10">
         <v>691</v>
       </c>
-      <c r="J10" s="79"/>
-      <c r="K10" s="79">
+      <c r="K10">
         <v>691</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>289</v>
+      </c>
+      <c r="B11" t="s">
         <v>290</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>291</v>
       </c>
-      <c r="C11" t="s">
-        <v>292</v>
-      </c>
-      <c r="D11" s="77">
+      <c r="D11" s="74">
         <v>2456</v>
       </c>
       <c r="E11" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F11" t="s">
         <v>86</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="I11" s="79">
+        <v>352</v>
+      </c>
+      <c r="I11">
         <v>20559</v>
       </c>
-      <c r="J11" s="79">
+      <c r="J11">
         <v>5180</v>
       </c>
-      <c r="K11" s="79">
+      <c r="K11">
         <v>25739</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>292</v>
+      </c>
+      <c r="B12" t="s">
+        <v>290</v>
+      </c>
+      <c r="C12" t="s">
         <v>293</v>
       </c>
-      <c r="B12" t="s">
-        <v>291</v>
-      </c>
-      <c r="C12" t="s">
-        <v>294</v>
-      </c>
-      <c r="D12" s="77">
+      <c r="D12" s="74">
         <v>2456</v>
       </c>
       <c r="E12" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F12" t="s">
         <v>86</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="I12" s="79">
+        <v>358</v>
+      </c>
+      <c r="I12">
         <v>101736</v>
       </c>
-      <c r="J12" s="79">
+      <c r="J12">
         <v>26448</v>
       </c>
-      <c r="K12" s="79">
+      <c r="K12">
         <v>128184</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>294</v>
+      </c>
+      <c r="B13" t="s">
         <v>295</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>296</v>
       </c>
-      <c r="C13" t="s">
-        <v>297</v>
-      </c>
-      <c r="D13" s="77">
+      <c r="D13" s="74">
         <v>5838</v>
       </c>
       <c r="E13" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F13" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>297</v>
+      </c>
+      <c r="B14" t="s">
         <v>298</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>299</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" s="73">
+        <v>788</v>
+      </c>
+      <c r="E14" t="s">
+        <v>351</v>
+      </c>
+      <c r="F14" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>300</v>
       </c>
-      <c r="D14" s="76">
-        <v>788</v>
-      </c>
-      <c r="E14" t="s">
-        <v>352</v>
-      </c>
-      <c r="F14" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="B15" t="s">
+        <v>298</v>
+      </c>
+      <c r="C15" t="s">
         <v>301</v>
       </c>
-      <c r="B15" t="s">
-        <v>299</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="D15" s="73">
+        <v>27</v>
+      </c>
+      <c r="E15" t="s">
+        <v>354</v>
+      </c>
+      <c r="F15" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>302</v>
       </c>
-      <c r="D15" s="76">
-        <v>27</v>
-      </c>
-      <c r="E15" t="s">
-        <v>355</v>
-      </c>
-      <c r="F15" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="B16" t="s">
         <v>303</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>304</v>
       </c>
-      <c r="C16" t="s">
-        <v>305</v>
-      </c>
-      <c r="D16" s="77">
+      <c r="D16" s="74">
         <v>8909</v>
       </c>
       <c r="E16" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F16" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>305</v>
+      </c>
+      <c r="B17" t="s">
         <v>306</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>307</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" s="73">
+        <v>220</v>
+      </c>
+      <c r="E17" t="s">
+        <v>351</v>
+      </c>
+      <c r="F17" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>308</v>
       </c>
-      <c r="D17" s="76">
-        <v>220</v>
-      </c>
-      <c r="E17" t="s">
-        <v>352</v>
-      </c>
-      <c r="F17" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="B18" t="s">
+        <v>306</v>
+      </c>
+      <c r="C18" t="s">
         <v>309</v>
       </c>
-      <c r="B18" t="s">
-        <v>307</v>
-      </c>
-      <c r="C18" t="s">
-        <v>310</v>
-      </c>
-      <c r="D18" s="76">
+      <c r="D18" s="73">
         <v>276</v>
       </c>
       <c r="E18" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F18" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>310</v>
+      </c>
+      <c r="B19" t="s">
+        <v>306</v>
+      </c>
+      <c r="C19" t="s">
         <v>311</v>
       </c>
-      <c r="B19" t="s">
-        <v>307</v>
-      </c>
-      <c r="C19" t="s">
-        <v>312</v>
-      </c>
-      <c r="D19" s="76">
+      <c r="D19" s="73">
         <v>270</v>
       </c>
       <c r="E19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F19" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>312</v>
+      </c>
+      <c r="B20" t="s">
         <v>313</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>314</v>
       </c>
-      <c r="C20" t="s">
-        <v>315</v>
-      </c>
-      <c r="D20" s="77">
+      <c r="D20" s="74">
         <v>1262</v>
       </c>
       <c r="E20" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F20" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>315</v>
+      </c>
+      <c r="B21" t="s">
         <v>316</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>317</v>
       </c>
-      <c r="C21" t="s">
-        <v>318</v>
-      </c>
-      <c r="D21" s="77">
+      <c r="D21" s="74">
         <v>7568</v>
       </c>
       <c r="E21" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F21" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>318</v>
+      </c>
+      <c r="B22" t="s">
         <v>319</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>320</v>
       </c>
-      <c r="C22" t="s">
-        <v>321</v>
-      </c>
-      <c r="D22" s="76">
+      <c r="D22" s="73">
         <v>258</v>
       </c>
       <c r="E22" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F22" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>321</v>
+      </c>
+      <c r="B23" t="s">
+        <v>319</v>
+      </c>
+      <c r="C23" t="s">
         <v>322</v>
       </c>
-      <c r="B23" t="s">
-        <v>320</v>
-      </c>
-      <c r="C23" t="s">
-        <v>323</v>
-      </c>
-      <c r="D23" s="76">
+      <c r="D23" s="73">
         <v>842</v>
       </c>
       <c r="E23" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F23" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>323</v>
+      </c>
+      <c r="B24" t="s">
+        <v>319</v>
+      </c>
+      <c r="C24" t="s">
         <v>324</v>
       </c>
-      <c r="B24" t="s">
-        <v>320</v>
-      </c>
-      <c r="C24" t="s">
-        <v>325</v>
-      </c>
-      <c r="D24" s="76">
+      <c r="D24" s="73">
         <v>55</v>
       </c>
       <c r="E24" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F24" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>325</v>
+      </c>
+      <c r="B25" t="s">
+        <v>319</v>
+      </c>
+      <c r="C25" t="s">
         <v>326</v>
       </c>
-      <c r="B25" t="s">
-        <v>320</v>
-      </c>
-      <c r="C25" t="s">
-        <v>327</v>
-      </c>
-      <c r="D25" s="77">
+      <c r="D25" s="74">
         <v>1701</v>
       </c>
       <c r="E25" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F25" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>327</v>
+      </c>
+      <c r="B26" t="s">
+        <v>319</v>
+      </c>
+      <c r="C26" t="s">
         <v>328</v>
       </c>
-      <c r="B26" t="s">
-        <v>320</v>
-      </c>
-      <c r="C26" t="s">
-        <v>329</v>
-      </c>
-      <c r="D26" s="76">
+      <c r="D26" s="73">
         <v>533</v>
       </c>
       <c r="E26" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F26" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>329</v>
+      </c>
+      <c r="B27" t="s">
+        <v>319</v>
+      </c>
+      <c r="C27" t="s">
         <v>330</v>
       </c>
-      <c r="B27" t="s">
-        <v>320</v>
-      </c>
-      <c r="C27" t="s">
-        <v>331</v>
-      </c>
-      <c r="D27" s="77">
+      <c r="D27" s="74">
         <v>5481</v>
       </c>
       <c r="E27" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F27" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>331</v>
+      </c>
+      <c r="B28" t="s">
+        <v>319</v>
+      </c>
+      <c r="C28" t="s">
         <v>332</v>
       </c>
-      <c r="B28" t="s">
-        <v>320</v>
-      </c>
-      <c r="C28" t="s">
-        <v>333</v>
-      </c>
-      <c r="D28" s="77">
+      <c r="D28" s="74">
         <v>1548</v>
       </c>
       <c r="E28" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F28" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>333</v>
+      </c>
+      <c r="B29" t="s">
+        <v>319</v>
+      </c>
+      <c r="C29" t="s">
         <v>334</v>
       </c>
-      <c r="B29" t="s">
-        <v>320</v>
-      </c>
-      <c r="C29" t="s">
-        <v>335</v>
-      </c>
-      <c r="D29" s="77">
+      <c r="D29" s="74">
         <v>1154</v>
       </c>
       <c r="E29" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F29" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>335</v>
+      </c>
+      <c r="B30" t="s">
+        <v>319</v>
+      </c>
+      <c r="C30" t="s">
         <v>336</v>
       </c>
-      <c r="B30" t="s">
-        <v>320</v>
-      </c>
-      <c r="C30" t="s">
-        <v>337</v>
-      </c>
-      <c r="D30" s="77">
+      <c r="D30" s="74">
         <v>21044</v>
       </c>
       <c r="E30" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F30" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>337</v>
+      </c>
+      <c r="B31" t="s">
+        <v>319</v>
+      </c>
+      <c r="C31" t="s">
         <v>338</v>
       </c>
-      <c r="B31" t="s">
-        <v>320</v>
-      </c>
-      <c r="C31" t="s">
-        <v>339</v>
-      </c>
-      <c r="D31" s="77">
+      <c r="D31" s="74">
         <v>5220</v>
       </c>
       <c r="E31" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F31" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>339</v>
+      </c>
+      <c r="B32" t="s">
+        <v>319</v>
+      </c>
+      <c r="C32" t="s">
         <v>340</v>
       </c>
-      <c r="B32" t="s">
-        <v>320</v>
-      </c>
-      <c r="C32" t="s">
-        <v>341</v>
-      </c>
-      <c r="D32" s="76">
+      <c r="D32" s="73">
         <v>221</v>
       </c>
       <c r="E32" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F32" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>341</v>
+      </c>
+      <c r="B33" t="s">
+        <v>319</v>
+      </c>
+      <c r="C33" t="s">
         <v>342</v>
       </c>
-      <c r="B33" t="s">
-        <v>320</v>
-      </c>
-      <c r="C33" t="s">
-        <v>343</v>
-      </c>
-      <c r="D33" s="77">
+      <c r="D33" s="74">
         <v>6522</v>
       </c>
       <c r="E33" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F33" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>343</v>
+      </c>
+      <c r="B34" t="s">
+        <v>319</v>
+      </c>
+      <c r="C34" t="s">
         <v>344</v>
       </c>
-      <c r="B34" t="s">
-        <v>320</v>
-      </c>
-      <c r="C34" t="s">
-        <v>345</v>
-      </c>
-      <c r="D34" s="76">
+      <c r="D34" s="73">
         <v>533</v>
       </c>
       <c r="E34" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F34" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>345</v>
+      </c>
+      <c r="B35" t="s">
+        <v>319</v>
+      </c>
+      <c r="C35" t="s">
         <v>346</v>
       </c>
-      <c r="B35" t="s">
-        <v>320</v>
-      </c>
-      <c r="C35" t="s">
-        <v>347</v>
-      </c>
-      <c r="D35" s="77">
+      <c r="D35" s="74">
         <v>1548</v>
       </c>
       <c r="E35" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F35" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>347</v>
+      </c>
+      <c r="B36" t="s">
+        <v>319</v>
+      </c>
+      <c r="C36" t="s">
         <v>348</v>
       </c>
-      <c r="B36" t="s">
-        <v>320</v>
-      </c>
-      <c r="C36" t="s">
-        <v>349</v>
-      </c>
-      <c r="D36" s="76">
+      <c r="D36" s="73">
         <v>20</v>
       </c>
       <c r="E36" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F36" t="s">
         <v>86</v>
@@ -9183,77 +9137,77 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:P29"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.28515625" style="72" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" style="143" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.28515625" style="72" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.28515625" style="72" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.28515625" style="72" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.33203125" style="70" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.44140625" style="139" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.33203125" style="70" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.33203125" style="70" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.33203125" style="70" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5546875" style="10" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="10" style="10" customWidth="1"/>
-    <col min="10" max="10" width="12.5703125" style="10" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.28515625" style="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.7109375" style="72" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="8.7109375" style="116" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="18.42578125" style="116" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="7" style="116" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="5" style="116" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.7109375" style="116" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.28515625" style="116"/>
+    <col min="10" max="10" width="12.5546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" style="70" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="8.6640625" style="112" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="18.44140625" style="112" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="7" style="112" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="5" style="112" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.6640625" style="112" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.33203125" style="112"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B1" s="184" t="s">
+    <row r="1" spans="1:15" ht="18" x14ac:dyDescent="0.3">
+      <c r="B1" s="180" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="184"/>
-      <c r="H1" s="184"/>
-      <c r="I1" s="184"/>
-      <c r="J1" s="184"/>
-      <c r="K1" s="184"/>
-      <c r="L1" s="184"/>
-    </row>
-    <row r="2" spans="1:15" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="72" t="s">
+      <c r="C1" s="180"/>
+      <c r="D1" s="180"/>
+      <c r="E1" s="180"/>
+      <c r="F1" s="180"/>
+      <c r="G1" s="180"/>
+      <c r="H1" s="180"/>
+      <c r="I1" s="180"/>
+      <c r="J1" s="180"/>
+      <c r="K1" s="180"/>
+      <c r="L1" s="180"/>
+    </row>
+    <row r="2" spans="1:15" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="70" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="152"/>
-      <c r="C2" s="152"/>
-      <c r="D2" s="152"/>
-      <c r="E2" s="152"/>
-      <c r="F2" s="152"/>
-      <c r="G2" s="152"/>
-      <c r="H2" s="152"/>
-      <c r="I2" s="152"/>
-      <c r="J2" s="152"/>
-      <c r="K2" s="152"/>
-      <c r="L2" s="152"/>
-    </row>
-    <row r="3" spans="1:15" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A3" s="185" t="s">
-        <v>204</v>
-      </c>
-      <c r="B3" s="185"/>
-      <c r="C3" s="185"/>
-      <c r="D3" s="185"/>
-      <c r="E3" s="185"/>
-      <c r="F3" s="185"/>
-      <c r="G3" s="185"/>
-      <c r="H3" s="185"/>
-      <c r="I3" s="185"/>
-      <c r="J3" s="185"/>
-      <c r="K3" s="185"/>
-      <c r="L3" s="185"/>
-    </row>
-    <row r="4" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
+    </row>
+    <row r="3" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A3" s="181" t="s">
+        <v>203</v>
+      </c>
+      <c r="B3" s="181"/>
+      <c r="C3" s="181"/>
+      <c r="D3" s="181"/>
+      <c r="E3" s="181"/>
+      <c r="F3" s="181"/>
+      <c r="G3" s="181"/>
+      <c r="H3" s="181"/>
+      <c r="I3" s="181"/>
+      <c r="J3" s="181"/>
+      <c r="K3" s="181"/>
+      <c r="L3" s="181"/>
+    </row>
+    <row r="4" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="40"/>
       <c r="C4" s="40"/>
       <c r="D4" s="40"/>
@@ -9264,1007 +9218,1007 @@
       <c r="I4" s="40"/>
       <c r="J4" s="40"/>
       <c r="K4" s="44"/>
-      <c r="L4" s="153" t="s">
+      <c r="L4" s="76" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:15" s="72" customFormat="1" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="161" t="s">
+    <row r="5" spans="1:15" s="70" customFormat="1" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="154" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="162" t="s">
+      <c r="B5" s="155" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="162" t="s">
+      <c r="C5" s="155" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="162" t="s">
+      <c r="D5" s="155" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="162" t="s">
+      <c r="E5" s="155" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="163" t="s">
+      <c r="F5" s="156" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="163" t="s">
-        <v>161</v>
-      </c>
-      <c r="H5" s="163" t="s">
-        <v>217</v>
-      </c>
-      <c r="I5" s="163" t="s">
-        <v>221</v>
-      </c>
-      <c r="J5" s="163" t="s">
+      <c r="G5" s="156" t="s">
+        <v>160</v>
+      </c>
+      <c r="H5" s="156" t="s">
+        <v>216</v>
+      </c>
+      <c r="I5" s="156" t="s">
+        <v>220</v>
+      </c>
+      <c r="J5" s="156" t="s">
         <v>10</v>
       </c>
-      <c r="K5" s="162" t="s">
+      <c r="K5" s="155" t="s">
         <v>6</v>
       </c>
-      <c r="L5" s="164" t="s">
+      <c r="L5" s="157" t="s">
         <v>8</v>
       </c>
-      <c r="O5" s="72" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="120">
+      <c r="O5" s="70" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="116">
         <v>1</v>
       </c>
-      <c r="B6" s="121" t="s">
+      <c r="B6" s="117" t="s">
+        <v>222</v>
+      </c>
+      <c r="C6" s="118">
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="D6" s="119" t="s">
+        <v>86</v>
+      </c>
+      <c r="E6" s="119" t="s">
         <v>223</v>
       </c>
-      <c r="C6" s="122">
-        <v>6.0999999999999999E-2</v>
-      </c>
-      <c r="D6" s="123" t="s">
+      <c r="F6" s="120">
+        <v>17000</v>
+      </c>
+      <c r="G6" s="120">
+        <v>0</v>
+      </c>
+      <c r="H6" s="120">
+        <v>0</v>
+      </c>
+      <c r="I6" s="120">
+        <f t="shared" ref="I6:I20" si="0">SUM(G6:H6)</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="120">
+        <f t="shared" ref="J6:J20" si="1">F6+I6</f>
+        <v>17000</v>
+      </c>
+      <c r="K6" s="119" t="s">
+        <v>224</v>
+      </c>
+      <c r="L6" s="121">
+        <v>17000</v>
+      </c>
+      <c r="O6" s="112" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="116">
+        <v>2</v>
+      </c>
+      <c r="B7" s="117" t="s">
+        <v>225</v>
+      </c>
+      <c r="C7" s="127">
+        <v>0.06</v>
+      </c>
+      <c r="D7" s="119" t="s">
         <v>86</v>
       </c>
-      <c r="E6" s="123" t="s">
-        <v>224</v>
-      </c>
-      <c r="F6" s="124">
-        <v>17000</v>
-      </c>
-      <c r="G6" s="124">
+      <c r="E7" s="119" t="s">
+        <v>180</v>
+      </c>
+      <c r="F7" s="120">
+        <v>85162</v>
+      </c>
+      <c r="G7" s="120">
         <v>0</v>
       </c>
-      <c r="H6" s="124">
-        <v>0</v>
-      </c>
-      <c r="I6" s="124">
-        <f>SUM(G6:H6)</f>
-        <v>0</v>
-      </c>
-      <c r="J6" s="124">
-        <f>F6+I6</f>
-        <v>17000</v>
-      </c>
-      <c r="K6" s="123" t="s">
-        <v>225</v>
-      </c>
-      <c r="L6" s="125">
-        <v>17000</v>
-      </c>
-      <c r="O6" s="116" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="120">
-        <v>2</v>
-      </c>
-      <c r="B7" s="121" t="s">
-        <v>226</v>
-      </c>
-      <c r="C7" s="131">
-        <v>0.06</v>
-      </c>
-      <c r="D7" s="123" t="s">
-        <v>86</v>
-      </c>
-      <c r="E7" s="123" t="s">
-        <v>181</v>
-      </c>
-      <c r="F7" s="124">
-        <v>85162</v>
-      </c>
-      <c r="G7" s="124">
-        <v>0</v>
-      </c>
-      <c r="H7" s="124">
+      <c r="H7" s="120">
         <f>1548-157</f>
         <v>1391</v>
       </c>
-      <c r="I7" s="124">
-        <f>SUM(G7:H7)</f>
+      <c r="I7" s="120">
+        <f t="shared" si="0"/>
         <v>1391</v>
       </c>
-      <c r="J7" s="124">
-        <f>F7+I7</f>
+      <c r="J7" s="120">
+        <f t="shared" si="1"/>
         <v>86553</v>
       </c>
-      <c r="K7" s="123" t="s">
-        <v>227</v>
-      </c>
-      <c r="L7" s="125">
+      <c r="K7" s="119" t="s">
+        <v>226</v>
+      </c>
+      <c r="L7" s="121">
         <v>90388</v>
       </c>
-      <c r="O7" s="118" t="s">
+      <c r="O7" s="114" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="120">
+    <row r="8" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="116">
         <v>3</v>
       </c>
-      <c r="B8" s="121" t="s">
-        <v>163</v>
-      </c>
-      <c r="C8" s="132">
+      <c r="B8" s="117" t="s">
+        <v>162</v>
+      </c>
+      <c r="C8" s="128">
         <v>5.8500000000000003E-2</v>
       </c>
-      <c r="D8" s="123" t="s">
+      <c r="D8" s="119" t="s">
         <v>86</v>
       </c>
-      <c r="E8" s="123" t="s">
-        <v>182</v>
-      </c>
-      <c r="F8" s="124">
+      <c r="E8" s="119" t="s">
+        <v>181</v>
+      </c>
+      <c r="F8" s="120">
         <v>45393</v>
       </c>
-      <c r="G8" s="124">
+      <c r="G8" s="120">
         <v>0</v>
       </c>
-      <c r="H8" s="124">
+      <c r="H8" s="120">
         <f>533-50</f>
         <v>483</v>
       </c>
-      <c r="I8" s="124">
-        <f>SUM(G8:H8)</f>
+      <c r="I8" s="120">
+        <f t="shared" si="0"/>
         <v>483</v>
       </c>
-      <c r="J8" s="124">
-        <f>F8+I8</f>
+      <c r="J8" s="120">
+        <f t="shared" si="1"/>
         <v>45876</v>
       </c>
-      <c r="K8" s="123" t="s">
-        <v>229</v>
-      </c>
-      <c r="L8" s="125">
+      <c r="K8" s="119" t="s">
+        <v>228</v>
+      </c>
+      <c r="L8" s="121">
         <v>48107</v>
       </c>
-      <c r="O8" s="118" t="s">
+      <c r="O8" s="114" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="120">
+    <row r="9" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="116">
         <v>4</v>
       </c>
-      <c r="B9" s="133" t="s">
-        <v>232</v>
-      </c>
-      <c r="C9" s="122">
+      <c r="B9" s="129" t="s">
+        <v>231</v>
+      </c>
+      <c r="C9" s="118">
         <v>6.6000000000000003E-2</v>
       </c>
-      <c r="D9" s="123" t="s">
+      <c r="D9" s="119" t="s">
         <v>86</v>
       </c>
-      <c r="E9" s="123" t="s">
-        <v>180</v>
-      </c>
-      <c r="F9" s="124">
+      <c r="E9" s="119" t="s">
+        <v>179</v>
+      </c>
+      <c r="F9" s="120">
         <v>134058</v>
       </c>
-      <c r="G9" s="124">
+      <c r="G9" s="120">
         <v>0</v>
       </c>
-      <c r="H9" s="124">
+      <c r="H9" s="120">
         <f>6522-648</f>
         <v>5874</v>
       </c>
-      <c r="I9" s="124">
-        <f>SUM(G9:H9)</f>
+      <c r="I9" s="120">
+        <f t="shared" si="0"/>
         <v>5874</v>
       </c>
-      <c r="J9" s="124">
-        <f>F9+I9</f>
+      <c r="J9" s="120">
+        <f t="shared" si="1"/>
         <v>139932</v>
       </c>
-      <c r="K9" s="123" t="s">
-        <v>233</v>
-      </c>
-      <c r="L9" s="125">
+      <c r="K9" s="119" t="s">
+        <v>232</v>
+      </c>
+      <c r="L9" s="121">
         <v>142906</v>
       </c>
-      <c r="O9" s="118" t="s">
+      <c r="O9" s="114" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="134">
+    <row r="10" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="130">
         <v>5</v>
       </c>
-      <c r="B10" s="121" t="s">
-        <v>218</v>
-      </c>
-      <c r="C10" s="132">
+      <c r="B10" s="117" t="s">
+        <v>217</v>
+      </c>
+      <c r="C10" s="128">
         <v>5.8500000000000003E-2</v>
       </c>
-      <c r="D10" s="123" t="s">
+      <c r="D10" s="119" t="s">
         <v>86</v>
       </c>
-      <c r="E10" s="135" t="s">
-        <v>176</v>
-      </c>
-      <c r="F10" s="136">
+      <c r="E10" s="131" t="s">
+        <v>175</v>
+      </c>
+      <c r="F10" s="132">
         <v>136004</v>
       </c>
-      <c r="G10" s="124">
+      <c r="G10" s="120">
         <v>0</v>
       </c>
-      <c r="H10" s="136">
+      <c r="H10" s="132">
         <f>221-25</f>
         <v>196</v>
       </c>
-      <c r="I10" s="124">
-        <f>SUM(G10:H10)</f>
+      <c r="I10" s="120">
+        <f t="shared" si="0"/>
         <v>196</v>
       </c>
-      <c r="J10" s="124">
-        <f>F10+I10</f>
+      <c r="J10" s="120">
+        <f t="shared" si="1"/>
         <v>136200</v>
       </c>
-      <c r="K10" s="135" t="s">
-        <v>219</v>
-      </c>
-      <c r="L10" s="137">
+      <c r="K10" s="131" t="s">
+        <v>218</v>
+      </c>
+      <c r="L10" s="133">
         <v>144136</v>
       </c>
-      <c r="O10" s="118" t="s">
+      <c r="O10" s="114" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="120">
+    <row r="11" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="116">
         <v>6</v>
       </c>
-      <c r="B11" s="133" t="s">
-        <v>222</v>
-      </c>
-      <c r="C11" s="122">
+      <c r="B11" s="129" t="s">
+        <v>221</v>
+      </c>
+      <c r="C11" s="118">
         <v>6.0999999999999999E-2</v>
       </c>
-      <c r="D11" s="123" t="s">
+      <c r="D11" s="119" t="s">
         <v>86</v>
       </c>
-      <c r="E11" s="123" t="s">
-        <v>148</v>
-      </c>
-      <c r="F11" s="124">
+      <c r="E11" s="119" t="s">
+        <v>147</v>
+      </c>
+      <c r="F11" s="120">
         <f>256700</f>
         <v>256700</v>
       </c>
-      <c r="G11" s="124">
+      <c r="G11" s="120">
         <v>0</v>
       </c>
-      <c r="H11" s="124">
+      <c r="H11" s="120">
         <f>5220-524</f>
         <v>4696</v>
       </c>
-      <c r="I11" s="124">
-        <f>SUM(G11:H11)</f>
+      <c r="I11" s="120">
+        <f t="shared" si="0"/>
         <v>4696</v>
       </c>
-      <c r="J11" s="124">
-        <f>F11+I11</f>
+      <c r="J11" s="120">
+        <f t="shared" si="1"/>
         <v>261396</v>
       </c>
-      <c r="K11" s="123" t="s">
-        <v>258</v>
-      </c>
-      <c r="L11" s="125">
+      <c r="K11" s="119" t="s">
+        <v>257</v>
+      </c>
+      <c r="L11" s="121">
         <v>289741</v>
       </c>
-      <c r="O11" s="118" t="s">
+      <c r="O11" s="114" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="120">
+    <row r="12" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="116">
         <v>7</v>
       </c>
-      <c r="B12" s="133">
+      <c r="B12" s="129">
         <v>101043101006109</v>
       </c>
-      <c r="C12" s="132">
+      <c r="C12" s="128">
         <v>7.2499999999999995E-2</v>
       </c>
-      <c r="D12" s="123" t="s">
+      <c r="D12" s="119" t="s">
         <v>86</v>
       </c>
-      <c r="E12" s="123" t="s">
-        <v>162</v>
-      </c>
-      <c r="F12" s="124">
+      <c r="E12" s="119" t="s">
+        <v>161</v>
+      </c>
+      <c r="F12" s="120">
         <v>277000</v>
       </c>
-      <c r="G12" s="124">
+      <c r="G12" s="120">
         <f>6946-696</f>
         <v>6250</v>
       </c>
-      <c r="H12" s="124">
+      <c r="H12" s="120">
         <f>21044-2106</f>
         <v>18938</v>
       </c>
-      <c r="I12" s="124">
-        <f>SUM(G12:H12)</f>
+      <c r="I12" s="120">
+        <f t="shared" si="0"/>
         <v>25188</v>
       </c>
-      <c r="J12" s="124">
-        <f>F12+I12</f>
+      <c r="J12" s="120">
+        <f t="shared" si="1"/>
         <v>302188</v>
       </c>
-      <c r="K12" s="123" t="s">
-        <v>179</v>
-      </c>
-      <c r="L12" s="125">
+      <c r="K12" s="119" t="s">
+        <v>178</v>
+      </c>
+      <c r="L12" s="121">
         <v>341592</v>
       </c>
-      <c r="O12" s="118" t="s">
+      <c r="O12" s="114" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="120">
+    <row r="13" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="116">
         <v>8</v>
       </c>
-      <c r="B13" s="133" t="s">
-        <v>244</v>
-      </c>
-      <c r="C13" s="122">
+      <c r="B13" s="129" t="s">
+        <v>243</v>
+      </c>
+      <c r="C13" s="118">
         <v>6.0999999999999999E-2</v>
       </c>
-      <c r="D13" s="123" t="s">
+      <c r="D13" s="119" t="s">
         <v>86</v>
       </c>
-      <c r="E13" s="123" t="s">
-        <v>178</v>
-      </c>
-      <c r="F13" s="124">
+      <c r="E13" s="119" t="s">
+        <v>177</v>
+      </c>
+      <c r="F13" s="120">
         <v>106388</v>
       </c>
-      <c r="G13" s="124">
+      <c r="G13" s="120">
         <v>0</v>
       </c>
-      <c r="H13" s="124">
+      <c r="H13" s="120">
         <f>1154-117</f>
         <v>1037</v>
       </c>
-      <c r="I13" s="124">
-        <f>SUM(G13:H13)</f>
+      <c r="I13" s="120">
+        <f t="shared" si="0"/>
         <v>1037</v>
       </c>
-      <c r="J13" s="124">
-        <f>F13+I13</f>
+      <c r="J13" s="120">
+        <f t="shared" si="1"/>
         <v>107425</v>
       </c>
-      <c r="K13" s="123" t="s">
-        <v>178</v>
-      </c>
-      <c r="L13" s="125">
+      <c r="K13" s="119" t="s">
+        <v>177</v>
+      </c>
+      <c r="L13" s="121">
         <v>112878</v>
       </c>
-      <c r="O13" s="118" t="s">
+      <c r="O13" s="114" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="120">
+    <row r="14" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="116">
         <v>9</v>
       </c>
-      <c r="B14" s="133" t="s">
-        <v>228</v>
-      </c>
-      <c r="C14" s="131">
+      <c r="B14" s="129" t="s">
+        <v>227</v>
+      </c>
+      <c r="C14" s="127">
         <v>0.06</v>
       </c>
-      <c r="D14" s="123" t="s">
+      <c r="D14" s="119" t="s">
         <v>86</v>
       </c>
-      <c r="E14" s="123" t="s">
-        <v>181</v>
-      </c>
-      <c r="F14" s="124">
+      <c r="E14" s="119" t="s">
+        <v>180</v>
+      </c>
+      <c r="F14" s="120">
         <v>85162</v>
       </c>
-      <c r="G14" s="124">
+      <c r="G14" s="120">
         <v>0</v>
       </c>
-      <c r="H14" s="124">
+      <c r="H14" s="120">
         <f>1548-157</f>
         <v>1391</v>
       </c>
-      <c r="I14" s="124">
-        <f>SUM(G14:H14)</f>
+      <c r="I14" s="120">
+        <f t="shared" si="0"/>
         <v>1391</v>
       </c>
-      <c r="J14" s="124">
-        <f>F14+I14</f>
+      <c r="J14" s="120">
+        <f t="shared" si="1"/>
         <v>86553</v>
       </c>
-      <c r="K14" s="123" t="s">
-        <v>227</v>
-      </c>
-      <c r="L14" s="125">
+      <c r="K14" s="119" t="s">
+        <v>226</v>
+      </c>
+      <c r="L14" s="121">
         <v>90388</v>
       </c>
-      <c r="O14" s="118" t="s">
+      <c r="O14" s="114" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="134">
+    <row r="15" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="130">
         <v>10</v>
       </c>
-      <c r="B15" s="133" t="s">
-        <v>241</v>
-      </c>
-      <c r="C15" s="132">
+      <c r="B15" s="129" t="s">
+        <v>240</v>
+      </c>
+      <c r="C15" s="128">
         <v>6.3500000000000001E-2</v>
       </c>
-      <c r="D15" s="123" t="s">
+      <c r="D15" s="119" t="s">
         <v>86</v>
       </c>
-      <c r="E15" s="135" t="s">
-        <v>183</v>
-      </c>
-      <c r="F15" s="136">
+      <c r="E15" s="131" t="s">
+        <v>182</v>
+      </c>
+      <c r="F15" s="132">
         <v>132988</v>
       </c>
-      <c r="G15" s="124">
+      <c r="G15" s="120">
         <v>0</v>
       </c>
-      <c r="H15" s="136">
+      <c r="H15" s="132">
         <f>5481-550</f>
         <v>4931</v>
       </c>
-      <c r="I15" s="124">
-        <f>SUM(G15:H15)</f>
+      <c r="I15" s="120">
+        <f t="shared" si="0"/>
         <v>4931</v>
       </c>
-      <c r="J15" s="124">
-        <f>F15+I15</f>
+      <c r="J15" s="120">
+        <f t="shared" si="1"/>
         <v>137919</v>
       </c>
-      <c r="K15" s="135" t="s">
-        <v>231</v>
-      </c>
-      <c r="L15" s="137">
+      <c r="K15" s="131" t="s">
+        <v>230</v>
+      </c>
+      <c r="L15" s="133">
         <v>141433</v>
       </c>
-      <c r="O15" s="118" t="s">
+      <c r="O15" s="114" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="123">
+    <row r="16" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="119">
         <v>11</v>
       </c>
-      <c r="B16" s="133" t="s">
-        <v>230</v>
-      </c>
-      <c r="C16" s="132">
+      <c r="B16" s="129" t="s">
+        <v>229</v>
+      </c>
+      <c r="C16" s="128">
         <v>5.8500000000000003E-2</v>
       </c>
-      <c r="D16" s="135" t="s">
+      <c r="D16" s="131" t="s">
         <v>86</v>
       </c>
-      <c r="E16" s="135" t="s">
-        <v>182</v>
-      </c>
-      <c r="F16" s="136">
+      <c r="E16" s="131" t="s">
+        <v>181</v>
+      </c>
+      <c r="F16" s="132">
         <v>45393</v>
       </c>
-      <c r="G16" s="136">
+      <c r="G16" s="132">
         <v>0</v>
       </c>
-      <c r="H16" s="136">
+      <c r="H16" s="132">
         <f>533-50</f>
         <v>483</v>
       </c>
-      <c r="I16" s="124">
-        <f>SUM(G16:H16)</f>
+      <c r="I16" s="120">
+        <f t="shared" si="0"/>
         <v>483</v>
       </c>
-      <c r="J16" s="124">
-        <f>F16+I16</f>
+      <c r="J16" s="120">
+        <f t="shared" si="1"/>
         <v>45876</v>
       </c>
-      <c r="K16" s="135" t="s">
-        <v>229</v>
-      </c>
-      <c r="L16" s="137">
+      <c r="K16" s="131" t="s">
+        <v>228</v>
+      </c>
+      <c r="L16" s="133">
         <v>48107</v>
       </c>
-      <c r="O16" s="118" t="s">
+      <c r="O16" s="114" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="120">
+    <row r="17" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="116">
         <v>12</v>
       </c>
-      <c r="B17" s="133">
+      <c r="B17" s="129">
         <v>101043031007357</v>
       </c>
-      <c r="C17" s="132">
+      <c r="C17" s="128">
         <v>6.25E-2</v>
       </c>
-      <c r="D17" s="123" t="s">
+      <c r="D17" s="119" t="s">
         <v>86</v>
       </c>
-      <c r="E17" s="123" t="s">
-        <v>242</v>
-      </c>
-      <c r="F17" s="124">
+      <c r="E17" s="119" t="s">
+        <v>241</v>
+      </c>
+      <c r="F17" s="120">
         <v>126000</v>
       </c>
-      <c r="G17" s="124">
+      <c r="G17" s="120">
         <v>0</v>
       </c>
-      <c r="H17" s="124">
+      <c r="H17" s="120">
         <f>1701-171</f>
         <v>1530</v>
       </c>
-      <c r="I17" s="124">
-        <f>SUM(G17:H17)</f>
+      <c r="I17" s="120">
+        <f t="shared" si="0"/>
         <v>1530</v>
       </c>
-      <c r="J17" s="124">
-        <f>F17+I17</f>
+      <c r="J17" s="120">
+        <f t="shared" si="1"/>
         <v>127530</v>
       </c>
-      <c r="K17" s="123" t="s">
-        <v>243</v>
-      </c>
-      <c r="L17" s="125">
+      <c r="K17" s="119" t="s">
+        <v>242</v>
+      </c>
+      <c r="L17" s="121">
         <v>133875</v>
       </c>
-      <c r="O17" s="118" t="s">
+      <c r="O17" s="114" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="120">
+    <row r="18" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="116">
         <v>13</v>
       </c>
-      <c r="B18" s="121" t="s">
-        <v>236</v>
-      </c>
-      <c r="C18" s="132">
+      <c r="B18" s="117" t="s">
+        <v>235</v>
+      </c>
+      <c r="C18" s="128">
         <v>5.5800000000000002E-2</v>
       </c>
-      <c r="D18" s="123" t="s">
+      <c r="D18" s="119" t="s">
         <v>86</v>
       </c>
-      <c r="E18" s="123" t="s">
-        <v>175</v>
-      </c>
-      <c r="F18" s="124">
+      <c r="E18" s="119" t="s">
+        <v>174</v>
+      </c>
+      <c r="F18" s="120">
         <v>113321</v>
       </c>
-      <c r="G18" s="124">
+      <c r="G18" s="120">
         <v>0</v>
       </c>
-      <c r="H18" s="124">
+      <c r="H18" s="120">
         <f>55-7</f>
         <v>48</v>
       </c>
-      <c r="I18" s="124">
-        <f>SUM(G18:H18)</f>
+      <c r="I18" s="120">
+        <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="J18" s="124">
-        <f>F18+I18</f>
+      <c r="J18" s="120">
+        <f t="shared" si="1"/>
         <v>113369</v>
       </c>
-      <c r="K18" s="123" t="s">
-        <v>237</v>
-      </c>
-      <c r="L18" s="125">
+      <c r="K18" s="119" t="s">
+        <v>236</v>
+      </c>
+      <c r="L18" s="121">
         <v>120097</v>
       </c>
-      <c r="O18" s="118" t="s">
+      <c r="O18" s="114" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="134">
+    <row r="19" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="130">
         <v>14</v>
       </c>
-      <c r="B19" s="133">
+      <c r="B19" s="129">
         <v>101043021004998</v>
       </c>
-      <c r="C19" s="132">
+      <c r="C19" s="128">
         <v>6.25E-2</v>
       </c>
-      <c r="D19" s="123" t="s">
+      <c r="D19" s="119" t="s">
         <v>86</v>
       </c>
-      <c r="E19" s="123" t="s">
-        <v>239</v>
-      </c>
-      <c r="F19" s="124">
+      <c r="E19" s="119" t="s">
+        <v>238</v>
+      </c>
+      <c r="F19" s="120">
         <v>25000</v>
       </c>
-      <c r="G19" s="124">
+      <c r="G19" s="120">
         <v>0</v>
       </c>
-      <c r="H19" s="124">
+      <c r="H19" s="120">
         <f>842-87</f>
         <v>755</v>
       </c>
-      <c r="I19" s="124">
-        <f>SUM(G19:H19)</f>
+      <c r="I19" s="120">
+        <f t="shared" si="0"/>
         <v>755</v>
       </c>
-      <c r="J19" s="124">
-        <f>F19+I19</f>
+      <c r="J19" s="120">
+        <f t="shared" si="1"/>
         <v>25755</v>
       </c>
-      <c r="K19" s="123" t="s">
-        <v>240</v>
-      </c>
-      <c r="L19" s="125">
+      <c r="K19" s="119" t="s">
+        <v>239</v>
+      </c>
+      <c r="L19" s="121">
         <v>26563</v>
       </c>
-      <c r="O19" s="118" t="s">
+      <c r="O19" s="114" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="134">
+    <row r="20" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="130">
         <v>15</v>
       </c>
-      <c r="B20" s="133" t="s">
-        <v>234</v>
-      </c>
-      <c r="C20" s="199">
+      <c r="B20" s="129" t="s">
+        <v>233</v>
+      </c>
+      <c r="C20" s="158">
         <v>6.25E-2</v>
       </c>
-      <c r="D20" s="123" t="s">
+      <c r="D20" s="119" t="s">
         <v>86</v>
       </c>
-      <c r="E20" s="135" t="s">
-        <v>177</v>
-      </c>
-      <c r="F20" s="136">
+      <c r="E20" s="131" t="s">
+        <v>176</v>
+      </c>
+      <c r="F20" s="132">
         <v>10645</v>
       </c>
-      <c r="G20" s="124">
+      <c r="G20" s="120">
         <v>0</v>
       </c>
-      <c r="H20" s="136">
+      <c r="H20" s="132">
         <f>258-20</f>
         <v>238</v>
       </c>
-      <c r="I20" s="124">
-        <f>SUM(G20:H20)</f>
+      <c r="I20" s="120">
+        <f t="shared" si="0"/>
         <v>238</v>
       </c>
-      <c r="J20" s="124">
-        <f>F20+I20</f>
+      <c r="J20" s="120">
+        <f t="shared" si="1"/>
         <v>10883</v>
       </c>
-      <c r="K20" s="135" t="s">
-        <v>235</v>
-      </c>
-      <c r="L20" s="137">
+      <c r="K20" s="131" t="s">
+        <v>234</v>
+      </c>
+      <c r="L20" s="133">
         <v>11310</v>
       </c>
-      <c r="O20" s="118" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="135"/>
-      <c r="B21" s="133"/>
-      <c r="C21" s="199"/>
-      <c r="D21" s="123"/>
-      <c r="E21" s="135"/>
-      <c r="F21" s="201">
+      <c r="O20" s="114" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="131"/>
+      <c r="B21" s="129"/>
+      <c r="C21" s="158"/>
+      <c r="D21" s="119"/>
+      <c r="E21" s="131"/>
+      <c r="F21" s="160">
         <f>SUM(F6:F20)</f>
         <v>1596214</v>
       </c>
-      <c r="G21" s="201">
-        <f t="shared" ref="G21:L21" si="0">SUM(G6:G20)</f>
+      <c r="G21" s="160">
+        <f t="shared" ref="G21:L21" si="2">SUM(G6:G20)</f>
         <v>6250</v>
       </c>
-      <c r="H21" s="201">
-        <f t="shared" si="0"/>
+      <c r="H21" s="160">
+        <f t="shared" si="2"/>
         <v>41991</v>
       </c>
-      <c r="I21" s="201">
-        <f t="shared" si="0"/>
+      <c r="I21" s="160">
+        <f t="shared" si="2"/>
         <v>48241</v>
       </c>
-      <c r="J21" s="201">
-        <f t="shared" si="0"/>
+      <c r="J21" s="160">
+        <f t="shared" si="2"/>
         <v>1644455</v>
       </c>
-      <c r="K21" s="201">
-        <f t="shared" si="0"/>
+      <c r="K21" s="160">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L21" s="201">
-        <f t="shared" si="0"/>
+      <c r="L21" s="160">
+        <f t="shared" si="2"/>
         <v>1758521</v>
       </c>
-      <c r="O21" s="118"/>
-    </row>
-    <row r="22" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="123">
+      <c r="O21" s="114"/>
+    </row>
+    <row r="22" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="119">
         <v>16</v>
       </c>
-      <c r="B22" s="133">
+      <c r="B22" s="129">
         <v>163971</v>
       </c>
-      <c r="C22" s="132">
+      <c r="C22" s="128">
         <v>7.2499999999999995E-2</v>
       </c>
-      <c r="D22" s="123" t="s">
+      <c r="D22" s="119" t="s">
+        <v>244</v>
+      </c>
+      <c r="E22" s="119" t="s">
         <v>245</v>
       </c>
-      <c r="E22" s="123" t="s">
-        <v>246</v>
-      </c>
-      <c r="F22" s="124">
+      <c r="F22" s="120">
         <v>126000</v>
       </c>
-      <c r="G22" s="124">
+      <c r="G22" s="120">
         <v>0</v>
       </c>
-      <c r="H22" s="124">
+      <c r="H22" s="120">
         <v>5180</v>
       </c>
-      <c r="I22" s="124">
+      <c r="I22" s="120">
         <f>SUM(G22:H22)</f>
         <v>5180</v>
       </c>
-      <c r="J22" s="124">
+      <c r="J22" s="120">
         <f>F22+I22</f>
         <v>131180</v>
       </c>
-      <c r="K22" s="123" t="s">
-        <v>247</v>
-      </c>
-      <c r="L22" s="125">
+      <c r="K22" s="119" t="s">
+        <v>246</v>
+      </c>
+      <c r="L22" s="121">
         <v>135386</v>
       </c>
-      <c r="O22" s="118" t="s">
+      <c r="O22" s="114" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="123">
+    <row r="23" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="119">
         <v>17</v>
       </c>
-      <c r="B23" s="133">
+      <c r="B23" s="129">
         <v>163734</v>
       </c>
-      <c r="C23" s="132">
+      <c r="C23" s="128">
         <v>7.2499999999999995E-2</v>
       </c>
-      <c r="D23" s="123" t="s">
-        <v>245</v>
-      </c>
-      <c r="E23" s="135" t="s">
-        <v>252</v>
-      </c>
-      <c r="F23" s="136">
+      <c r="D23" s="119" t="s">
+        <v>244</v>
+      </c>
+      <c r="E23" s="131" t="s">
+        <v>251</v>
+      </c>
+      <c r="F23" s="132">
         <v>377000</v>
       </c>
-      <c r="G23" s="124">
+      <c r="G23" s="120">
         <v>0</v>
       </c>
-      <c r="H23" s="136">
+      <c r="H23" s="132">
         <v>20233</v>
       </c>
-      <c r="I23" s="124">
+      <c r="I23" s="120">
         <f>SUM(G23:H23)</f>
         <v>20233</v>
       </c>
-      <c r="J23" s="124">
+      <c r="J23" s="120">
         <f>F23+I23</f>
         <v>397233</v>
       </c>
-      <c r="K23" s="135" t="s">
-        <v>253</v>
-      </c>
-      <c r="L23" s="137">
+      <c r="K23" s="131" t="s">
+        <v>252</v>
+      </c>
+      <c r="L23" s="133">
         <v>405085</v>
       </c>
-      <c r="O23" s="118" t="s">
+      <c r="O23" s="114" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="123">
+    <row r="24" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="119">
         <v>18</v>
       </c>
-      <c r="B24" s="133">
+      <c r="B24" s="129">
         <v>156876</v>
       </c>
-      <c r="C24" s="132">
+      <c r="C24" s="128">
         <v>6.8500000000000005E-2</v>
       </c>
-      <c r="D24" s="123" t="s">
-        <v>245</v>
-      </c>
-      <c r="E24" s="135" t="s">
-        <v>250</v>
-      </c>
-      <c r="F24" s="136">
+      <c r="D24" s="119" t="s">
+        <v>244</v>
+      </c>
+      <c r="E24" s="131" t="s">
+        <v>249</v>
+      </c>
+      <c r="F24" s="132">
         <v>4100</v>
       </c>
-      <c r="G24" s="136">
+      <c r="G24" s="132">
         <v>0</v>
       </c>
-      <c r="H24" s="136">
+      <c r="H24" s="132">
         <v>27</v>
       </c>
-      <c r="I24" s="124">
+      <c r="I24" s="120">
         <f>SUM(G24:H24)</f>
         <v>27</v>
       </c>
-      <c r="J24" s="124">
+      <c r="J24" s="120">
         <f>F24+I24</f>
         <v>4127</v>
       </c>
-      <c r="K24" s="135" t="s">
-        <v>251</v>
-      </c>
-      <c r="L24" s="137">
+      <c r="K24" s="131" t="s">
+        <v>250</v>
+      </c>
+      <c r="L24" s="133">
         <v>4388</v>
       </c>
-      <c r="O24" s="118" t="s">
+      <c r="O24" s="114" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="123">
+    <row r="25" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="119">
         <v>19</v>
       </c>
-      <c r="B25" s="133">
+      <c r="B25" s="129">
         <v>156982</v>
       </c>
-      <c r="C25" s="132">
+      <c r="C25" s="128">
         <v>6.8500000000000005E-2</v>
       </c>
-      <c r="D25" s="123" t="s">
-        <v>245</v>
-      </c>
-      <c r="E25" s="135" t="s">
-        <v>248</v>
-      </c>
-      <c r="F25" s="136">
+      <c r="D25" s="119" t="s">
+        <v>244</v>
+      </c>
+      <c r="E25" s="131" t="s">
+        <v>247</v>
+      </c>
+      <c r="F25" s="132">
         <v>130000</v>
       </c>
-      <c r="G25" s="136">
+      <c r="G25" s="132">
         <v>0</v>
       </c>
-      <c r="H25" s="136">
+      <c r="H25" s="132">
         <v>220</v>
       </c>
-      <c r="I25" s="124">
+      <c r="I25" s="120">
         <f>SUM(G25:H25)</f>
         <v>220</v>
       </c>
-      <c r="J25" s="124">
+      <c r="J25" s="120">
         <f>F25+I25</f>
         <v>130220</v>
       </c>
-      <c r="K25" s="135" t="s">
+      <c r="K25" s="131" t="s">
+        <v>248</v>
+      </c>
+      <c r="L25" s="133">
+        <v>139136</v>
+      </c>
+      <c r="O25" s="114" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="116">
+        <v>20</v>
+      </c>
+      <c r="B26" s="129">
+        <v>156877</v>
+      </c>
+      <c r="C26" s="128">
+        <v>6.8500000000000005E-2</v>
+      </c>
+      <c r="D26" s="119" t="s">
+        <v>244</v>
+      </c>
+      <c r="E26" s="119" t="s">
         <v>249</v>
       </c>
-      <c r="L25" s="137">
-        <v>139136</v>
-      </c>
-      <c r="O25" s="118" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="120">
-        <v>20</v>
-      </c>
-      <c r="B26" s="133">
-        <v>156877</v>
-      </c>
-      <c r="C26" s="132">
-        <v>6.8500000000000005E-2</v>
-      </c>
-      <c r="D26" s="123" t="s">
-        <v>245</v>
-      </c>
-      <c r="E26" s="123" t="s">
-        <v>250</v>
-      </c>
-      <c r="F26" s="124">
+      <c r="F26" s="120">
         <v>120000</v>
       </c>
-      <c r="G26" s="124">
+      <c r="G26" s="120">
         <v>0</v>
       </c>
-      <c r="H26" s="124">
+      <c r="H26" s="120">
         <v>788</v>
       </c>
-      <c r="I26" s="124">
+      <c r="I26" s="120">
         <f>SUM(G26:H26)</f>
         <v>788</v>
       </c>
-      <c r="J26" s="124">
+      <c r="J26" s="120">
         <f>F26+I26</f>
         <v>120788</v>
       </c>
-      <c r="K26" s="123" t="s">
-        <v>251</v>
-      </c>
-      <c r="L26" s="125">
+      <c r="K26" s="119" t="s">
+        <v>250</v>
+      </c>
+      <c r="L26" s="121">
         <v>128434</v>
       </c>
-      <c r="O26" s="118" t="s">
+      <c r="O26" s="114" t="s">
         <v>91</v>
       </c>
-      <c r="P26" s="130"/>
-    </row>
-    <row r="27" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="134"/>
-      <c r="B27" s="200"/>
-      <c r="C27" s="138"/>
-      <c r="D27" s="135"/>
-      <c r="E27" s="135"/>
-      <c r="F27" s="201">
+      <c r="P26" s="126"/>
+    </row>
+    <row r="27" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="130"/>
+      <c r="B27" s="159"/>
+      <c r="C27" s="134"/>
+      <c r="D27" s="131"/>
+      <c r="E27" s="131"/>
+      <c r="F27" s="160">
         <f>SUM(F22:F26)</f>
         <v>757100</v>
       </c>
-      <c r="G27" s="201">
-        <f t="shared" ref="G27:L27" si="1">SUM(G22:G26)</f>
+      <c r="G27" s="160">
+        <f t="shared" ref="G27:L27" si="3">SUM(G22:G26)</f>
         <v>0</v>
       </c>
-      <c r="H27" s="201">
-        <f t="shared" si="1"/>
+      <c r="H27" s="160">
+        <f t="shared" si="3"/>
         <v>26448</v>
       </c>
-      <c r="I27" s="201">
-        <f t="shared" si="1"/>
+      <c r="I27" s="160">
+        <f t="shared" si="3"/>
         <v>26448</v>
       </c>
-      <c r="J27" s="201">
-        <f t="shared" si="1"/>
+      <c r="J27" s="160">
+        <f t="shared" si="3"/>
         <v>783548</v>
       </c>
-      <c r="K27" s="201">
-        <f t="shared" si="1"/>
+      <c r="K27" s="160">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L27" s="201">
-        <f t="shared" si="1"/>
+      <c r="L27" s="160">
+        <f t="shared" si="3"/>
         <v>812429</v>
       </c>
-      <c r="O27" s="118"/>
-      <c r="P27" s="130"/>
-    </row>
-    <row r="28" spans="1:16" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="126"/>
-      <c r="B28" s="127"/>
-      <c r="C28" s="128"/>
-      <c r="D28" s="128"/>
-      <c r="E28" s="128"/>
+      <c r="O27" s="114"/>
+      <c r="P27" s="126"/>
+    </row>
+    <row r="28" spans="1:16" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="122"/>
+      <c r="B28" s="123"/>
+      <c r="C28" s="124"/>
+      <c r="D28" s="124"/>
+      <c r="E28" s="124"/>
       <c r="F28" s="21"/>
       <c r="G28" s="21"/>
       <c r="H28" s="21"/>
@@ -10272,11 +10226,11 @@
       <c r="J28" s="21"/>
       <c r="K28" s="21"/>
       <c r="L28" s="21"/>
-      <c r="P28" s="130"/>
-    </row>
-    <row r="29" spans="1:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+      <c r="P28" s="126"/>
+    </row>
+    <row r="29" spans="1:16" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <sortState ref="B7:O25">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:O25">
     <sortCondition ref="D7:D25"/>
   </sortState>
   <mergeCells count="2">
@@ -10285,6 +10239,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.39370078740157483" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="65" fitToHeight="0" orientation="landscape" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="65" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>